--- a/AAII_Financials/Quarterly/SSBI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SSBI_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="92">
   <si>
     <t>SSBI</t>
   </si>
@@ -656,232 +656,239 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44104</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43921</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43830</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43738</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43555</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43465</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43373</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43281</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43190</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43100</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43008</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>42916</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42825</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42735</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42643</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>14900</v>
+      </c>
+      <c r="E8" s="3">
         <v>15600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>14600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>14200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>12500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>11300</v>
-      </c>
-      <c r="I8" s="3">
-        <v>10900</v>
       </c>
       <c r="J8" s="3">
         <v>10900</v>
       </c>
       <c r="K8" s="3">
+        <v>10900</v>
+      </c>
+      <c r="L8" s="3">
         <v>10600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>10100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>10400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>10100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>9200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>8800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>8300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>8000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>7600</v>
-      </c>
-      <c r="T8" s="3">
-        <v>7200</v>
       </c>
       <c r="U8" s="3">
         <v>7200</v>
       </c>
       <c r="V8" s="3">
+        <v>7200</v>
+      </c>
+      <c r="W8" s="3">
         <v>6800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>6600</v>
-      </c>
-      <c r="X8" s="3">
-        <v>6100</v>
       </c>
       <c r="Y8" s="3">
         <v>6100</v>
       </c>
       <c r="Z8" s="3">
+        <v>6100</v>
+      </c>
+      <c r="AA8" s="3">
         <v>5700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>5200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>5000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>4800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>5000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>4800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>5100</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -972,8 +979,11 @@
       <c r="AF9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1064,8 +1074,11 @@
       <c r="AF10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1098,8 +1111,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1190,8 +1204,11 @@
       <c r="AF12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,8 +1299,11 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1374,8 +1394,11 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1466,8 +1489,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,91 +1523,92 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E17" s="3">
         <v>6000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>5000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>400</v>
-      </c>
-      <c r="AD17" s="3">
-        <v>300</v>
       </c>
       <c r="AE17" s="3">
         <v>300</v>
@@ -1589,100 +1616,106 @@
       <c r="AF17" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG17" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>9600</v>
+        <v>7900</v>
       </c>
       <c r="E18" s="3">
         <v>9600</v>
       </c>
       <c r="F18" s="3">
+        <v>9600</v>
+      </c>
+      <c r="G18" s="3">
         <v>10600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>10200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>9300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>9800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>8900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>9600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>9000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>8800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>8300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>7300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>6700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>5900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>6000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>5500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>5300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>5500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>5400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>5500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>5100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>5200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>4700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>4400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>4500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>4400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>4700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>4500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,82 +1748,83 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E20" s="3">
         <v>-5300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-3800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-4300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-4400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-2900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-4400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-3700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-4200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-3500</v>
-      </c>
-      <c r="M20" s="3">
-        <v>-4100</v>
       </c>
       <c r="N20" s="3">
         <v>-4100</v>
       </c>
       <c r="O20" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="P20" s="3">
         <v>-3100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-2500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-3300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-2700</v>
-      </c>
-      <c r="T20" s="3">
-        <v>-3700</v>
       </c>
       <c r="U20" s="3">
         <v>-3700</v>
       </c>
       <c r="V20" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="W20" s="3">
         <v>-3800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-3500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-3000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-2800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-3400</v>
-      </c>
-      <c r="AA20" s="3">
-        <v>-2900</v>
       </c>
       <c r="AB20" s="3">
         <v>-2900</v>
@@ -1799,58 +1833,61 @@
         <v>-2900</v>
       </c>
       <c r="AD20" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="AE20" s="3">
         <v>-2700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-2500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-2700</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E21" s="3">
         <v>4400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>5900</v>
       </c>
-      <c r="F21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H21" s="3">
+      <c r="H21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I21" s="3">
         <v>6500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>5100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>5300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>5700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>5600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>4400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>4000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>4800</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>5</v>
       </c>
@@ -1893,14 +1930,17 @@
       <c r="AD21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AE21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF21" s="3">
         <v>2100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1991,123 +2031,129 @@
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E23" s="3">
         <v>4300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>5800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>6300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>5700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>6400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>5400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>5200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>5400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>5500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>4700</v>
-      </c>
-      <c r="N23" s="3">
-        <v>4200</v>
       </c>
       <c r="O23" s="3">
         <v>4200</v>
       </c>
       <c r="P23" s="3">
+        <v>4200</v>
+      </c>
+      <c r="Q23" s="3">
         <v>3200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>3400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>2600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>2900</v>
-      </c>
-      <c r="T23" s="3">
-        <v>1700</v>
       </c>
       <c r="U23" s="3">
         <v>1700</v>
       </c>
       <c r="V23" s="3">
+        <v>1700</v>
+      </c>
+      <c r="W23" s="3">
         <v>1600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>2000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>2100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>2400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1500</v>
-      </c>
-      <c r="AD23" s="3">
-        <v>2000</v>
       </c>
       <c r="AE23" s="3">
         <v>2000</v>
       </c>
       <c r="AF23" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AG23" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>700</v>
+      </c>
+      <c r="E24" s="3">
         <v>1300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1700</v>
-      </c>
-      <c r="F24" s="3">
-        <v>1800</v>
       </c>
       <c r="G24" s="3">
         <v>1800</v>
       </c>
       <c r="H24" s="3">
+        <v>1800</v>
+      </c>
+      <c r="I24" s="3">
         <v>1900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1500</v>
-      </c>
-      <c r="J24" s="3">
-        <v>1600</v>
       </c>
       <c r="K24" s="3">
         <v>1600</v>
@@ -2116,67 +2162,70 @@
         <v>1600</v>
       </c>
       <c r="M24" s="3">
+        <v>1600</v>
+      </c>
+      <c r="N24" s="3">
         <v>1400</v>
-      </c>
-      <c r="N24" s="3">
-        <v>1200</v>
       </c>
       <c r="O24" s="3">
         <v>1200</v>
       </c>
       <c r="P24" s="3">
+        <v>1200</v>
+      </c>
+      <c r="Q24" s="3">
         <v>900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1000</v>
-      </c>
-      <c r="R24" s="3">
-        <v>800</v>
       </c>
       <c r="S24" s="3">
         <v>800</v>
       </c>
       <c r="T24" s="3">
+        <v>800</v>
+      </c>
+      <c r="U24" s="3">
         <v>500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>300</v>
-      </c>
-      <c r="V24" s="3">
-        <v>500</v>
       </c>
       <c r="W24" s="3">
         <v>500</v>
       </c>
       <c r="X24" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="Y24" s="3">
         <v>600</v>
       </c>
       <c r="Z24" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AA24" s="3">
         <v>500</v>
       </c>
       <c r="AB24" s="3">
+        <v>500</v>
+      </c>
+      <c r="AC24" s="3">
         <v>700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>600</v>
-      </c>
-      <c r="AD24" s="3">
-        <v>800</v>
       </c>
       <c r="AE24" s="3">
         <v>800</v>
       </c>
       <c r="AF24" s="3">
+        <v>800</v>
+      </c>
+      <c r="AG24" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,192 +2316,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E26" s="3">
         <v>3000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>4100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>4600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>4000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>4500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>3900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>3700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>3800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>3900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>3300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>3000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>2400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>2000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1100</v>
-      </c>
-      <c r="W26" s="3">
-        <v>1500</v>
       </c>
       <c r="X26" s="3">
         <v>1500</v>
       </c>
       <c r="Y26" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Z26" s="3">
         <v>1700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1000</v>
-      </c>
-      <c r="AB26" s="3">
-        <v>900</v>
       </c>
       <c r="AC26" s="3">
         <v>900</v>
       </c>
       <c r="AD26" s="3">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="AE26" s="3">
         <v>1200</v>
       </c>
       <c r="AF26" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AG26" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E27" s="3">
         <v>3000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>4100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>4600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>4000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>4500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>3900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>3700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>3800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>3900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>3300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>3000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1100</v>
-      </c>
-      <c r="W27" s="3">
-        <v>1500</v>
       </c>
       <c r="X27" s="3">
         <v>1500</v>
       </c>
       <c r="Y27" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Z27" s="3">
         <v>1700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1000</v>
-      </c>
-      <c r="AB27" s="3">
-        <v>900</v>
       </c>
       <c r="AC27" s="3">
         <v>900</v>
       </c>
       <c r="AD27" s="3">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="AE27" s="3">
         <v>1200</v>
       </c>
       <c r="AF27" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AG27" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2601,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2593,8 +2654,8 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>5</v>
+      <c r="S29" s="3">
+        <v>0</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>5</v>
@@ -2614,12 +2675,12 @@
       <c r="Y29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="Z29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA29" s="3">
         <v>-300</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2635,8 +2696,11 @@
       <c r="AF29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2791,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,82 +2886,85 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E32" s="3">
         <v>5300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>3800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>4300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>4400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>2900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>4400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>3700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>4200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>3500</v>
-      </c>
-      <c r="M32" s="3">
-        <v>4100</v>
       </c>
       <c r="N32" s="3">
         <v>4100</v>
       </c>
       <c r="O32" s="3">
+        <v>4100</v>
+      </c>
+      <c r="P32" s="3">
         <v>3100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>3500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>2500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>3300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>2700</v>
-      </c>
-      <c r="T32" s="3">
-        <v>3700</v>
       </c>
       <c r="U32" s="3">
         <v>3700</v>
       </c>
       <c r="V32" s="3">
+        <v>3700</v>
+      </c>
+      <c r="W32" s="3">
         <v>3800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>3500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>3000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>2800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>3400</v>
-      </c>
-      <c r="AA32" s="3">
-        <v>2900</v>
       </c>
       <c r="AB32" s="3">
         <v>2900</v>
@@ -2903,108 +2973,114 @@
         <v>2900</v>
       </c>
       <c r="AD32" s="3">
+        <v>2900</v>
+      </c>
+      <c r="AE32" s="3">
         <v>2700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>2500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E33" s="3">
         <v>3000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>4100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>4600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>4000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>4500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>3900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>3700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>3800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>3900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>3300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>3000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1100</v>
-      </c>
-      <c r="W33" s="3">
-        <v>1500</v>
       </c>
       <c r="X33" s="3">
         <v>1500</v>
       </c>
       <c r="Y33" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Z33" s="3">
         <v>1700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1000</v>
-      </c>
-      <c r="AB33" s="3">
-        <v>900</v>
       </c>
       <c r="AC33" s="3">
         <v>900</v>
       </c>
       <c r="AD33" s="3">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="AE33" s="3">
         <v>1200</v>
       </c>
       <c r="AF33" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AG33" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3171,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E35" s="3">
         <v>3000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>4100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>4600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>4000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>4500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>3900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>3700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>3800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>3900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>3300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>3000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1100</v>
-      </c>
-      <c r="W35" s="3">
-        <v>1500</v>
       </c>
       <c r="X35" s="3">
         <v>1500</v>
       </c>
       <c r="Y35" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Z35" s="3">
         <v>1700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1000</v>
-      </c>
-      <c r="AB35" s="3">
-        <v>900</v>
       </c>
       <c r="AC35" s="3">
         <v>900</v>
       </c>
       <c r="AD35" s="3">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="AE35" s="3">
         <v>1200</v>
       </c>
       <c r="AF35" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AG35" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44104</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43921</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43830</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43738</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43555</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43465</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43373</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43281</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43190</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43100</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43008</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>42916</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42825</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42735</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42643</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3403,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,123 +3438,127 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>86600</v>
+      </c>
+      <c r="E41" s="3">
         <v>112400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>116600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>75200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>42800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>36600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>65900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>40700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>37800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>56100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>46900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>30800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>24300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>68000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>36500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>38300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>37000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>12100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>18600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>21700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>20900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>23700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>18900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>68800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>20400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>20200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>20800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>24200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>20100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>21800</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>13900</v>
+      </c>
+      <c r="E42" s="3">
         <v>14100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>13500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>13600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>13700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>13800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>13500</v>
-      </c>
-      <c r="J42" s="3">
-        <v>4300</v>
       </c>
       <c r="K42" s="3">
         <v>4300</v>
@@ -3477,7 +3567,7 @@
         <v>4300</v>
       </c>
       <c r="M42" s="3">
-        <v>3400</v>
+        <v>4300</v>
       </c>
       <c r="N42" s="3">
         <v>3400</v>
@@ -3489,7 +3579,7 @@
         <v>3400</v>
       </c>
       <c r="Q42" s="3">
-        <v>3300</v>
+        <v>3400</v>
       </c>
       <c r="R42" s="3">
         <v>3300</v>
@@ -3501,7 +3591,7 @@
         <v>3300</v>
       </c>
       <c r="U42" s="3">
-        <v>3100</v>
+        <v>3300</v>
       </c>
       <c r="V42" s="3">
         <v>3100</v>
@@ -3513,7 +3603,7 @@
         <v>3100</v>
       </c>
       <c r="Y42" s="3">
-        <v>5100</v>
+        <v>3100</v>
       </c>
       <c r="Z42" s="3">
         <v>5100</v>
@@ -3522,22 +3612,25 @@
         <v>5100</v>
       </c>
       <c r="AB42" s="3">
+        <v>5100</v>
+      </c>
+      <c r="AC42" s="3">
         <v>4800</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>5200</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>5300</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>4900</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3628,8 +3721,11 @@
       <c r="AF43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3720,8 +3816,11 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3812,8 +3911,11 @@
       <c r="AF45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3904,8 +4006,11 @@
       <c r="AF46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3996,52 +4101,55 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E48" s="3">
         <v>6600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>6800</v>
-      </c>
-      <c r="F48" s="3">
-        <v>5500</v>
       </c>
       <c r="G48" s="3">
         <v>5500</v>
       </c>
       <c r="H48" s="3">
+        <v>5500</v>
+      </c>
+      <c r="I48" s="3">
         <v>6500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>7000</v>
-      </c>
-      <c r="L48" s="3">
-        <v>7200</v>
       </c>
       <c r="M48" s="3">
         <v>7200</v>
       </c>
       <c r="N48" s="3">
+        <v>7200</v>
+      </c>
+      <c r="O48" s="3">
         <v>7300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>7000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>6200</v>
-      </c>
-      <c r="Q48" s="3">
-        <v>6300</v>
       </c>
       <c r="R48" s="3">
         <v>6300</v>
@@ -4053,43 +4161,46 @@
         <v>6300</v>
       </c>
       <c r="U48" s="3">
+        <v>6300</v>
+      </c>
+      <c r="V48" s="3">
         <v>6400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>5800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>5300</v>
-      </c>
-      <c r="X48" s="3">
-        <v>5200</v>
       </c>
       <c r="Y48" s="3">
         <v>5200</v>
       </c>
       <c r="Z48" s="3">
-        <v>5300</v>
+        <v>5200</v>
       </c>
       <c r="AA48" s="3">
         <v>5300</v>
       </c>
       <c r="AB48" s="3">
+        <v>5300</v>
+      </c>
+      <c r="AC48" s="3">
         <v>5400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>5500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>5400</v>
-      </c>
-      <c r="AE48" s="3">
-        <v>5500</v>
       </c>
       <c r="AF48" s="3">
         <v>5500</v>
       </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3">
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4180,8 +4291,11 @@
       <c r="AF49" s="3">
         <v>4100</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3">
+        <v>4100</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4386,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,8 +4481,11 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4456,8 +4576,11 @@
       <c r="AF52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,100 +4671,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1142200</v>
+      </c>
+      <c r="E54" s="3">
         <v>1161400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1147000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1113000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1043800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>980800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>982300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>958100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>922600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>901600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>886100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>865900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>833800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>850700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>721600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>696000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>680800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>635600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>626300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>622100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>595200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>586000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>577000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>610900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>539000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>537500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>524500</v>
-      </c>
-      <c r="AD54" s="3">
-        <v>513700</v>
       </c>
       <c r="AE54" s="3">
         <v>513700</v>
       </c>
       <c r="AF54" s="3">
+        <v>513700</v>
+      </c>
+      <c r="AG54" s="3">
         <v>518300</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4803,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,100 +4838,104 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E57" s="3">
         <v>7100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>10200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>6100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>6600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>4400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>5600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4300</v>
-      </c>
-      <c r="R57" s="3">
-        <v>3300</v>
       </c>
       <c r="S57" s="3">
         <v>3300</v>
       </c>
       <c r="T57" s="3">
+        <v>3300</v>
+      </c>
+      <c r="U57" s="3">
         <v>3500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>3200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>8100</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4892,50 +5026,53 @@
       <c r="AF58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E59" s="3">
         <v>1200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1300</v>
       </c>
-      <c r="F59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H59" s="3">
+      <c r="H59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I59" s="3">
         <v>1000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1400</v>
-      </c>
-      <c r="M59" s="3">
-        <v>1300</v>
       </c>
       <c r="N59" s="3">
         <v>1300</v>
       </c>
       <c r="O59" s="3">
+        <v>1300</v>
+      </c>
+      <c r="P59" s="3">
         <v>900</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>5</v>
       </c>
@@ -4951,8 +5088,8 @@
       <c r="U59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V59" s="3">
-        <v>0</v>
+      <c r="V59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="W59" s="3">
         <v>0</v>
@@ -4984,8 +5121,11 @@
       <c r="AF59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5076,8 +5216,11 @@
       <c r="AF60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5133,7 +5276,7 @@
         <v>5900</v>
       </c>
       <c r="U61" s="3">
-        <v>0</v>
+        <v>5900</v>
       </c>
       <c r="V61" s="3">
         <v>0</v>
@@ -5168,8 +5311,11 @@
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5260,8 +5406,11 @@
       <c r="AF62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5501,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5596,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,100 +5691,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1048700</v>
+      </c>
+      <c r="E66" s="3">
         <v>1067000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1054400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1024500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>959400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>896100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>898600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>873800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>840600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>822700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>810600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>790200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>760400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>779400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>653400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>628600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>614300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>570900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>562900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>560600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>534700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>525800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>517300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>551200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>478500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>477000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>465200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>455100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>453400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>458800</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5823,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +5916,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6011,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5938,8 +6106,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,100 +6201,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>67900</v>
+      </c>
+      <c r="E72" s="3">
         <v>66800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>64700</v>
       </c>
-      <c r="F72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G72" s="3">
+      <c r="G72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H72" s="3">
         <v>57600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>54500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>50800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>47600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>44800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>41700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>38500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>37500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>35300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>33100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>31600</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S72" s="3">
+      <c r="S72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T72" s="3">
         <v>28800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>27500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>27000</v>
       </c>
-      <c r="V72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W72" s="3">
+      <c r="W72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X72" s="3">
         <v>25900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>25200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>24400</v>
       </c>
-      <c r="Z72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA72" s="3">
+      <c r="AA72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB72" s="3">
         <v>23600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>23300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>23100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>22800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>22200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>21600</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6391,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6486,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,100 +6581,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>93400</v>
+      </c>
+      <c r="E76" s="3">
         <v>94400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>92700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>88500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>84400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>84700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>83700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>84300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>82000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>79000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>75500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>75600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>73400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>71200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>68200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>67300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>66500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>64700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>63400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>61500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>60500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>60200</v>
-      </c>
-      <c r="Y76" s="3">
-        <v>59700</v>
       </c>
       <c r="Z76" s="3">
         <v>59700</v>
       </c>
       <c r="AA76" s="3">
+        <v>59700</v>
+      </c>
+      <c r="AB76" s="3">
         <v>60500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>60400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>59300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>58600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>60300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>59500</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6771,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44104</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43921</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43830</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43738</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43555</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43465</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43373</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43281</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43190</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43100</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43008</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>42916</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42825</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42735</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42643</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E81" s="3">
         <v>3000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>4100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>4600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>4000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>4500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>3900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>3700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>3800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>3900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>3300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>3000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1100</v>
-      </c>
-      <c r="W81" s="3">
-        <v>1500</v>
       </c>
       <c r="X81" s="3">
         <v>1500</v>
       </c>
       <c r="Y81" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Z81" s="3">
         <v>1700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1000</v>
-      </c>
-      <c r="AB81" s="3">
-        <v>900</v>
       </c>
       <c r="AC81" s="3">
         <v>900</v>
       </c>
       <c r="AD81" s="3">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="AE81" s="3">
         <v>1200</v>
       </c>
       <c r="AF81" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AG81" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,8 +7003,9 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6816,39 +7015,39 @@
       <c r="E83" s="3">
         <v>100</v>
       </c>
-      <c r="F83" s="3" t="s">
-        <v>5</v>
+      <c r="F83" s="3">
+        <v>100</v>
       </c>
       <c r="G83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H83" s="3">
+      <c r="H83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I83" s="3">
         <v>100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>-300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>-300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>-200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>600</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q83" s="3" t="s">
         <v>5</v>
       </c>
@@ -6861,8 +7060,8 @@
       <c r="T83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U83" s="3">
-        <v>0</v>
+      <c r="U83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="V83" s="3">
         <v>0</v>
@@ -6888,17 +7087,20 @@
       <c r="AC83" s="3">
         <v>0</v>
       </c>
-      <c r="AD83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE83" s="3">
-        <v>100</v>
+      <c r="AD83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AF83" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7191,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7286,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7381,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7476,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,50 +7571,53 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E89" s="3">
         <v>3700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-2800</v>
       </c>
-      <c r="F89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H89" s="3">
+      <c r="H89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I89" s="3">
         <v>34000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-29500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>46600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>5400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1700</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q89" s="3" t="s">
         <v>5</v>
       </c>
@@ -7413,8 +7630,8 @@
       <c r="T89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U89" s="3">
-        <v>0</v>
+      <c r="U89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="V89" s="3">
         <v>0</v>
@@ -7440,17 +7657,20 @@
       <c r="AC89" s="3">
         <v>0</v>
       </c>
-      <c r="AD89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE89" s="3">
+      <c r="AD89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF89" s="3">
         <v>1900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,8 +7703,9 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7492,13 +7713,13 @@
         <v>0</v>
       </c>
       <c r="E91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F91" s="3">
         <v>-100</v>
       </c>
       <c r="G91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H91" s="3">
         <v>0</v>
@@ -7510,23 +7731,23 @@
         <v>0</v>
       </c>
       <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
         <v>-100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-400</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q91" s="3" t="s">
         <v>5</v>
       </c>
@@ -7539,8 +7760,8 @@
       <c r="T91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
+      <c r="U91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="V91" s="3">
         <v>0</v>
@@ -7566,17 +7787,20 @@
       <c r="AC91" s="3">
         <v>0</v>
       </c>
-      <c r="AD91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE91" s="3">
-        <v>0</v>
+      <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AF91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +7891,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,50 +7986,53 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-16700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>7600</v>
       </c>
-      <c r="F94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H94" s="3">
+      <c r="H94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I94" s="3">
         <v>-8000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>102600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-74000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-45500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>161400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-25200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-143500</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q94" s="3" t="s">
         <v>5</v>
       </c>
@@ -7815,8 +8045,8 @@
       <c r="T94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
+      <c r="U94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="V94" s="3">
         <v>0</v>
@@ -7842,17 +8072,20 @@
       <c r="AC94" s="3">
         <v>0</v>
       </c>
-      <c r="AD94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE94" s="3">
+      <c r="AD94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF94" s="3">
         <v>-2900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>10700</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8118,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7897,38 +8131,38 @@
         <v>-800</v>
       </c>
       <c r="F96" s="3">
-        <v>0</v>
+        <v>-800</v>
       </c>
       <c r="G96" s="3">
         <v>0</v>
       </c>
       <c r="H96" s="3">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3">
         <v>-800</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>2200</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-800</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-2200</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-700</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>2200</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-700</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-2200</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
         <v>0</v>
       </c>
@@ -7972,13 +8206,16 @@
         <v>0</v>
       </c>
       <c r="AE96" s="3">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="AF96" s="3">
         <v>-600</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>-600</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8306,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8401,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,50 +8496,53 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-18300</v>
+      </c>
+      <c r="E100" s="3">
         <v>8800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>34200</v>
       </c>
-      <c r="F100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H100" s="3">
+      <c r="H100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I100" s="3">
         <v>-2700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-57800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>30300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>47100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>10900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-137100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>29700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>127700</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q100" s="3" t="s">
         <v>5</v>
       </c>
@@ -8309,8 +8555,8 @@
       <c r="T100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
+      <c r="U100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="V100" s="3">
         <v>0</v>
@@ -8336,17 +8582,20 @@
       <c r="AC100" s="3">
         <v>0</v>
       </c>
-      <c r="AD100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE100" s="3">
+      <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF100" s="3">
         <v>-1100</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-10700</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8437,50 +8686,53 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-25800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-4200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>39000</v>
       </c>
-      <c r="F102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H102" s="3">
+      <c r="H102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I102" s="3">
         <v>-29300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>15300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>2900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>6900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>9200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>23600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>6600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-14000</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q102" s="3" t="s">
         <v>5</v>
       </c>
@@ -8493,8 +8745,8 @@
       <c r="T102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U102" s="3">
-        <v>0</v>
+      <c r="U102" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="V102" s="3">
         <v>0</v>
@@ -8520,13 +8772,16 @@
       <c r="AC102" s="3">
         <v>0</v>
       </c>
-      <c r="AD102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE102" s="3">
+      <c r="AD102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF102" s="3">
         <v>-2100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SSBI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SSBI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="92">
   <si>
     <t>SSBI</t>
   </si>
@@ -656,239 +656,245 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E8" s="3">
         <v>14900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>15600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>14600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>14200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>12500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>11300</v>
-      </c>
-      <c r="J8" s="3">
-        <v>10900</v>
       </c>
       <c r="K8" s="3">
         <v>10900</v>
       </c>
       <c r="L8" s="3">
+        <v>10900</v>
+      </c>
+      <c r="M8" s="3">
         <v>10600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>10100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>10400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>10100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>9200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>8800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>8300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>8000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>7600</v>
-      </c>
-      <c r="U8" s="3">
-        <v>7200</v>
       </c>
       <c r="V8" s="3">
         <v>7200</v>
       </c>
       <c r="W8" s="3">
+        <v>7200</v>
+      </c>
+      <c r="X8" s="3">
         <v>6800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>6600</v>
-      </c>
-      <c r="Y8" s="3">
-        <v>6100</v>
       </c>
       <c r="Z8" s="3">
         <v>6100</v>
       </c>
       <c r="AA8" s="3">
+        <v>6100</v>
+      </c>
+      <c r="AB8" s="3">
         <v>5700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>5200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>5000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>4800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>5000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>4800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>5100</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -982,8 +988,11 @@
       <c r="AG9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1077,8 +1086,11 @@
       <c r="AG10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1112,8 +1124,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1207,8 +1220,11 @@
       <c r="AG12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1302,8 +1318,11 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1397,8 +1416,11 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1492,8 +1514,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1524,94 +1549,95 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E17" s="3">
         <v>7000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>6000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>5000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>400</v>
-      </c>
-      <c r="AE17" s="3">
-        <v>300</v>
       </c>
       <c r="AF17" s="3">
         <v>300</v>
@@ -1619,8 +1645,11 @@
       <c r="AG17" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH17" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1628,94 +1657,97 @@
         <v>7900</v>
       </c>
       <c r="E18" s="3">
-        <v>9600</v>
+        <v>7900</v>
       </c>
       <c r="F18" s="3">
         <v>9600</v>
       </c>
       <c r="G18" s="3">
+        <v>9600</v>
+      </c>
+      <c r="H18" s="3">
         <v>10600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>10200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>9300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>9800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>8900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>9600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>9000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>8800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>8300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>7300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>6700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>5900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>6000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>5500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>5300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>5500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>5400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>5500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>5100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>5200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>4700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>4400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>4500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>4400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>4700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>4500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1749,85 +1781,86 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="E20" s="3">
         <v>-5400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-5300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-3800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-4300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-4400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-2900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-4400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-3700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-4200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-3500</v>
-      </c>
-      <c r="N20" s="3">
-        <v>-4100</v>
       </c>
       <c r="O20" s="3">
         <v>-4100</v>
       </c>
       <c r="P20" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-3500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-2500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-3300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-2700</v>
-      </c>
-      <c r="U20" s="3">
-        <v>-3700</v>
       </c>
       <c r="V20" s="3">
         <v>-3700</v>
       </c>
       <c r="W20" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="X20" s="3">
         <v>-3800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-3500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-3000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-2800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-3400</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>-2900</v>
       </c>
       <c r="AC20" s="3">
         <v>-2900</v>
@@ -1836,61 +1869,64 @@
         <v>-2900</v>
       </c>
       <c r="AE20" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="AF20" s="3">
         <v>-2700</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-2500</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-2700</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E21" s="3">
         <v>2600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>4400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>5900</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>5</v>
+      <c r="H21" s="3">
+        <v>6400</v>
       </c>
       <c r="I21" s="3">
+        <v>5800</v>
+      </c>
+      <c r="J21" s="3">
         <v>6500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>5100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>5300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>5700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>5600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>4400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>4000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>4800</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>5</v>
       </c>
@@ -1933,14 +1969,17 @@
       <c r="AE21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AF21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG21" s="3">
         <v>2100</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2034,129 +2073,135 @@
       <c r="AG22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E23" s="3">
         <v>2500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>4300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>5800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>6300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>5700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>6400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>5400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>5200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>5400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>5500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>4700</v>
-      </c>
-      <c r="O23" s="3">
-        <v>4200</v>
       </c>
       <c r="P23" s="3">
         <v>4200</v>
       </c>
       <c r="Q23" s="3">
+        <v>4200</v>
+      </c>
+      <c r="R23" s="3">
         <v>3200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>3400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>2600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2900</v>
-      </c>
-      <c r="U23" s="3">
-        <v>1700</v>
       </c>
       <c r="V23" s="3">
         <v>1700</v>
       </c>
       <c r="W23" s="3">
+        <v>1700</v>
+      </c>
+      <c r="X23" s="3">
         <v>1600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>2000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>2100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>2400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1500</v>
-      </c>
-      <c r="AE23" s="3">
-        <v>2000</v>
       </c>
       <c r="AF23" s="3">
         <v>2000</v>
       </c>
       <c r="AG23" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AH23" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>800</v>
+      </c>
+      <c r="E24" s="3">
         <v>700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1700</v>
-      </c>
-      <c r="G24" s="3">
-        <v>1800</v>
       </c>
       <c r="H24" s="3">
         <v>1800</v>
       </c>
       <c r="I24" s="3">
+        <v>1800</v>
+      </c>
+      <c r="J24" s="3">
         <v>1900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1500</v>
-      </c>
-      <c r="K24" s="3">
-        <v>1600</v>
       </c>
       <c r="L24" s="3">
         <v>1600</v>
@@ -2165,67 +2210,70 @@
         <v>1600</v>
       </c>
       <c r="N24" s="3">
+        <v>1600</v>
+      </c>
+      <c r="O24" s="3">
         <v>1400</v>
-      </c>
-      <c r="O24" s="3">
-        <v>1200</v>
       </c>
       <c r="P24" s="3">
         <v>1200</v>
       </c>
       <c r="Q24" s="3">
+        <v>1200</v>
+      </c>
+      <c r="R24" s="3">
         <v>900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1000</v>
-      </c>
-      <c r="S24" s="3">
-        <v>800</v>
       </c>
       <c r="T24" s="3">
         <v>800</v>
       </c>
       <c r="U24" s="3">
+        <v>800</v>
+      </c>
+      <c r="V24" s="3">
         <v>500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>300</v>
-      </c>
-      <c r="W24" s="3">
-        <v>500</v>
       </c>
       <c r="X24" s="3">
         <v>500</v>
       </c>
       <c r="Y24" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="Z24" s="3">
         <v>600</v>
       </c>
       <c r="AA24" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AB24" s="3">
         <v>500</v>
       </c>
       <c r="AC24" s="3">
+        <v>500</v>
+      </c>
+      <c r="AD24" s="3">
         <v>700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>600</v>
-      </c>
-      <c r="AE24" s="3">
-        <v>800</v>
       </c>
       <c r="AF24" s="3">
         <v>800</v>
       </c>
       <c r="AG24" s="3">
+        <v>800</v>
+      </c>
+      <c r="AH24" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2319,198 +2367,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E26" s="3">
         <v>1800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>3000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>4100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>4600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>4000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>4500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>3900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>3700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>3800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>3900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>3300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>3000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>2200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>2400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>2000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1100</v>
-      </c>
-      <c r="X26" s="3">
-        <v>1500</v>
       </c>
       <c r="Y26" s="3">
         <v>1500</v>
       </c>
       <c r="Z26" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AA26" s="3">
         <v>1700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1000</v>
-      </c>
-      <c r="AC26" s="3">
-        <v>900</v>
       </c>
       <c r="AD26" s="3">
         <v>900</v>
       </c>
       <c r="AE26" s="3">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="AF26" s="3">
         <v>1200</v>
       </c>
       <c r="AG26" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AH26" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E27" s="3">
         <v>1800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>3000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>4100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>4600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>4000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>4500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>3900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>3700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>3800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>3900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>3300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>3000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>2400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>2000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1100</v>
-      </c>
-      <c r="X27" s="3">
-        <v>1500</v>
       </c>
       <c r="Y27" s="3">
         <v>1500</v>
       </c>
       <c r="Z27" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AA27" s="3">
         <v>1700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1000</v>
-      </c>
-      <c r="AC27" s="3">
-        <v>900</v>
       </c>
       <c r="AD27" s="3">
         <v>900</v>
       </c>
       <c r="AE27" s="3">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="AF27" s="3">
         <v>1200</v>
       </c>
       <c r="AG27" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AH27" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2604,8 +2661,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2657,8 +2717,8 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>5</v>
+      <c r="T29" s="3">
+        <v>0</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>5</v>
@@ -2678,12 +2738,12 @@
       <c r="Z29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB29" s="3">
         <v>-300</v>
       </c>
-      <c r="AB29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AC29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2699,8 +2759,11 @@
       <c r="AG29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2794,8 +2857,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2889,85 +2955,88 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E32" s="3">
         <v>5400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>5300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>3800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>4300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>4400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>2900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>4400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>3700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>4200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>3500</v>
-      </c>
-      <c r="N32" s="3">
-        <v>4100</v>
       </c>
       <c r="O32" s="3">
         <v>4100</v>
       </c>
       <c r="P32" s="3">
+        <v>4100</v>
+      </c>
+      <c r="Q32" s="3">
         <v>3100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>3500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>2500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>3300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>2700</v>
-      </c>
-      <c r="U32" s="3">
-        <v>3700</v>
       </c>
       <c r="V32" s="3">
         <v>3700</v>
       </c>
       <c r="W32" s="3">
+        <v>3700</v>
+      </c>
+      <c r="X32" s="3">
         <v>3800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>3500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>3000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>2800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>3400</v>
-      </c>
-      <c r="AB32" s="3">
-        <v>2900</v>
       </c>
       <c r="AC32" s="3">
         <v>2900</v>
@@ -2976,111 +3045,117 @@
         <v>2900</v>
       </c>
       <c r="AE32" s="3">
+        <v>2900</v>
+      </c>
+      <c r="AF32" s="3">
         <v>2700</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>2500</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E33" s="3">
         <v>1800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>3000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>4100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>4600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>4000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>4500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>3900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>3700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>3800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>3900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>3300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>3000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>2400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>2000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1100</v>
-      </c>
-      <c r="X33" s="3">
-        <v>1500</v>
       </c>
       <c r="Y33" s="3">
         <v>1500</v>
       </c>
       <c r="Z33" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AA33" s="3">
         <v>1700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1000</v>
-      </c>
-      <c r="AC33" s="3">
-        <v>900</v>
       </c>
       <c r="AD33" s="3">
         <v>900</v>
       </c>
       <c r="AE33" s="3">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="AF33" s="3">
         <v>1200</v>
       </c>
       <c r="AG33" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AH33" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3174,203 +3249,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E35" s="3">
         <v>1800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>3000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>4100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>4600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>4000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>4500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>3900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>3700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>3800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>3900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>3300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>3000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>2400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>2000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1100</v>
-      </c>
-      <c r="X35" s="3">
-        <v>1500</v>
       </c>
       <c r="Y35" s="3">
         <v>1500</v>
       </c>
       <c r="Z35" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AA35" s="3">
         <v>1700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1000</v>
-      </c>
-      <c r="AC35" s="3">
-        <v>900</v>
       </c>
       <c r="AD35" s="3">
         <v>900</v>
       </c>
       <c r="AE35" s="3">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="AF35" s="3">
         <v>1200</v>
       </c>
       <c r="AG35" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AH35" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3404,8 +3488,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3439,103 +3524,107 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>57800</v>
+      </c>
+      <c r="E41" s="3">
         <v>86600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>112400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>116600</v>
       </c>
-      <c r="G41" s="3">
-        <v>75200</v>
-      </c>
       <c r="H41" s="3">
+        <v>77600</v>
+      </c>
+      <c r="I41" s="3">
         <v>42800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>36600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>65900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>40700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>37800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>56100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>46900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>30800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>24300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>68000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>36500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>38300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>37000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>12100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>18600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>21700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>20900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>23700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>18900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>68800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>20400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>20200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>20800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>24200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>20100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>21800</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3543,25 +3632,25 @@
         <v>13900</v>
       </c>
       <c r="E42" s="3">
+        <v>13900</v>
+      </c>
+      <c r="F42" s="3">
         <v>14100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>13500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>13600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>13700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>13800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>13500</v>
-      </c>
-      <c r="K42" s="3">
-        <v>4300</v>
       </c>
       <c r="L42" s="3">
         <v>4300</v>
@@ -3570,7 +3659,7 @@
         <v>4300</v>
       </c>
       <c r="N42" s="3">
-        <v>3400</v>
+        <v>4300</v>
       </c>
       <c r="O42" s="3">
         <v>3400</v>
@@ -3582,7 +3671,7 @@
         <v>3400</v>
       </c>
       <c r="R42" s="3">
-        <v>3300</v>
+        <v>3400</v>
       </c>
       <c r="S42" s="3">
         <v>3300</v>
@@ -3594,7 +3683,7 @@
         <v>3300</v>
       </c>
       <c r="V42" s="3">
-        <v>3100</v>
+        <v>3300</v>
       </c>
       <c r="W42" s="3">
         <v>3100</v>
@@ -3606,7 +3695,7 @@
         <v>3100</v>
       </c>
       <c r="Z42" s="3">
-        <v>5100</v>
+        <v>3100</v>
       </c>
       <c r="AA42" s="3">
         <v>5100</v>
@@ -3615,22 +3704,25 @@
         <v>5100</v>
       </c>
       <c r="AC42" s="3">
+        <v>5100</v>
+      </c>
+      <c r="AD42" s="3">
         <v>4800</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>5200</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>5300</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>4900</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3724,8 +3816,11 @@
       <c r="AG43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3819,8 +3914,11 @@
       <c r="AG44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3914,8 +4012,11 @@
       <c r="AG45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -4009,8 +4110,11 @@
       <c r="AG46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4104,55 +4208,58 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E48" s="3">
         <v>6400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>6600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>6800</v>
       </c>
-      <c r="G48" s="3">
-        <v>5500</v>
-      </c>
       <c r="H48" s="3">
-        <v>5500</v>
+        <v>6800</v>
       </c>
       <c r="I48" s="3">
+        <v>7000</v>
+      </c>
+      <c r="J48" s="3">
         <v>6500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>7000</v>
-      </c>
-      <c r="M48" s="3">
-        <v>7200</v>
       </c>
       <c r="N48" s="3">
         <v>7200</v>
       </c>
       <c r="O48" s="3">
+        <v>7200</v>
+      </c>
+      <c r="P48" s="3">
         <v>7300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>7000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>6200</v>
-      </c>
-      <c r="R48" s="3">
-        <v>6300</v>
       </c>
       <c r="S48" s="3">
         <v>6300</v>
@@ -4164,43 +4271,46 @@
         <v>6300</v>
       </c>
       <c r="V48" s="3">
+        <v>6300</v>
+      </c>
+      <c r="W48" s="3">
         <v>6400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>5800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>5300</v>
-      </c>
-      <c r="Y48" s="3">
-        <v>5200</v>
       </c>
       <c r="Z48" s="3">
         <v>5200</v>
       </c>
       <c r="AA48" s="3">
-        <v>5300</v>
+        <v>5200</v>
       </c>
       <c r="AB48" s="3">
         <v>5300</v>
       </c>
       <c r="AC48" s="3">
+        <v>5300</v>
+      </c>
+      <c r="AD48" s="3">
         <v>5400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>5500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>5400</v>
-      </c>
-      <c r="AF48" s="3">
-        <v>5500</v>
       </c>
       <c r="AG48" s="3">
         <v>5500</v>
       </c>
-    </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH48" s="3">
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4294,8 +4404,11 @@
       <c r="AG49" s="3">
         <v>4100</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3">
+        <v>4100</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4389,8 +4502,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4484,8 +4600,11 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4579,8 +4698,11 @@
       <c r="AG52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4674,103 +4796,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1122500</v>
+      </c>
+      <c r="E54" s="3">
         <v>1142200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1161400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1147000</v>
       </c>
-      <c r="G54" s="3">
-        <v>1113000</v>
-      </c>
       <c r="H54" s="3">
+        <v>1115300</v>
+      </c>
+      <c r="I54" s="3">
         <v>1043800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>980800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>982300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>958100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>922600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>901600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>886100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>865900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>833800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>850700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>721600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>696000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>680800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>635600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>626300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>622100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>595200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>586000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>577000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>610900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>539000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>537500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>524500</v>
-      </c>
-      <c r="AE54" s="3">
-        <v>513700</v>
       </c>
       <c r="AF54" s="3">
         <v>513700</v>
       </c>
       <c r="AG54" s="3">
+        <v>513700</v>
+      </c>
+      <c r="AH54" s="3">
         <v>518300</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4804,8 +4932,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4839,103 +4968,107 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E57" s="3">
         <v>6500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>7100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4000</v>
       </c>
-      <c r="G57" s="3">
-        <v>10200</v>
-      </c>
       <c r="H57" s="3">
-        <v>6100</v>
+        <v>11100</v>
       </c>
       <c r="I57" s="3">
+        <v>4600</v>
+      </c>
+      <c r="J57" s="3">
         <v>4700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>4500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>6600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>5600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>4300</v>
-      </c>
-      <c r="S57" s="3">
-        <v>3300</v>
       </c>
       <c r="T57" s="3">
         <v>3300</v>
       </c>
       <c r="U57" s="3">
+        <v>3300</v>
+      </c>
+      <c r="V57" s="3">
         <v>3500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>3200</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>8100</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5029,53 +5162,56 @@
       <c r="AG58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1300</v>
       </c>
-      <c r="G59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>5</v>
+      <c r="H59" s="3">
+        <v>1400</v>
       </c>
       <c r="I59" s="3">
+        <v>1500</v>
+      </c>
+      <c r="J59" s="3">
         <v>1000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1400</v>
-      </c>
-      <c r="N59" s="3">
-        <v>1300</v>
       </c>
       <c r="O59" s="3">
         <v>1300</v>
       </c>
       <c r="P59" s="3">
+        <v>1300</v>
+      </c>
+      <c r="Q59" s="3">
         <v>900</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>5</v>
       </c>
@@ -5091,8 +5227,8 @@
       <c r="V59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W59" s="3">
-        <v>0</v>
+      <c r="W59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="X59" s="3">
         <v>0</v>
@@ -5124,8 +5260,11 @@
       <c r="AG59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5219,8 +5358,11 @@
       <c r="AG60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5279,7 +5421,7 @@
         <v>5900</v>
       </c>
       <c r="V61" s="3">
-        <v>0</v>
+        <v>5900</v>
       </c>
       <c r="W61" s="3">
         <v>0</v>
@@ -5314,8 +5456,11 @@
       <c r="AG61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5409,8 +5554,11 @@
       <c r="AG62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5504,8 +5652,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5599,8 +5750,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5694,103 +5848,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1024800</v>
+      </c>
+      <c r="E66" s="3">
         <v>1048700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1067000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1054400</v>
       </c>
-      <c r="G66" s="3">
-        <v>1024500</v>
-      </c>
       <c r="H66" s="3">
+        <v>1026800</v>
+      </c>
+      <c r="I66" s="3">
         <v>959400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>896100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>898600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>873800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>840600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>822700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>810600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>790200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>760400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>779400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>653400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>628600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>614300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>570900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>562900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>560600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>534700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>525800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>517300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>551200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>478500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>477000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>465200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>455100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>453400</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>458800</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5824,8 +5984,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5919,8 +6080,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6014,8 +6178,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6109,8 +6276,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6204,103 +6374,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>69000</v>
+      </c>
+      <c r="E72" s="3">
         <v>67900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>66800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>64700</v>
       </c>
-      <c r="G72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H72" s="3">
+        <v>61400</v>
+      </c>
+      <c r="I72" s="3">
         <v>57600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>54500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>50800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>47600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>44800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>41700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>38500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>37500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>35300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>33100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>31600</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T72" s="3">
+      <c r="T72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U72" s="3">
         <v>28800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>27500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>27000</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X72" s="3">
+      <c r="X72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y72" s="3">
         <v>25900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>25200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>24400</v>
       </c>
-      <c r="AA72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB72" s="3">
+      <c r="AB72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC72" s="3">
         <v>23600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>23300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>23100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>22800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>22200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>21600</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6394,8 +6570,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6489,8 +6668,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6584,103 +6766,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>97700</v>
+      </c>
+      <c r="E76" s="3">
         <v>93400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>94400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>92700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>88500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>84400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>84700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>83700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>84300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>82000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>79000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>75500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>75600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>73400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>71200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>68200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>67300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>66500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>64700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>63400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>61500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>60500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>60200</v>
-      </c>
-      <c r="Z76" s="3">
-        <v>59700</v>
       </c>
       <c r="AA76" s="3">
         <v>59700</v>
       </c>
       <c r="AB76" s="3">
+        <v>59700</v>
+      </c>
+      <c r="AC76" s="3">
         <v>60500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>60400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>59300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>58600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>60300</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>59500</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6774,203 +6962,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E81" s="3">
         <v>1800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>3000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>4100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>4600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>4000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>4500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>3900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>3700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>3800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>3900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>3300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>3000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>2400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>2000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1100</v>
-      </c>
-      <c r="X81" s="3">
-        <v>1500</v>
       </c>
       <c r="Y81" s="3">
         <v>1500</v>
       </c>
       <c r="Z81" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AA81" s="3">
         <v>1700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1000</v>
-      </c>
-      <c r="AC81" s="3">
-        <v>900</v>
       </c>
       <c r="AD81" s="3">
         <v>900</v>
       </c>
       <c r="AE81" s="3">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="AF81" s="3">
         <v>1200</v>
       </c>
       <c r="AG81" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AH81" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7004,8 +7201,9 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7018,39 +7216,39 @@
       <c r="F83" s="3">
         <v>100</v>
       </c>
-      <c r="G83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>5</v>
+      <c r="G83" s="3">
+        <v>100</v>
+      </c>
+      <c r="H83" s="3">
+        <v>100</v>
       </c>
       <c r="I83" s="3">
         <v>100</v>
       </c>
       <c r="J83" s="3">
+        <v>100</v>
+      </c>
+      <c r="K83" s="3">
         <v>-300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>-300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>-200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>600</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R83" s="3" t="s">
         <v>5</v>
       </c>
@@ -7063,8 +7261,8 @@
       <c r="U83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V83" s="3">
-        <v>0</v>
+      <c r="V83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="W83" s="3">
         <v>0</v>
@@ -7090,17 +7288,20 @@
       <c r="AD83" s="3">
         <v>0</v>
       </c>
-      <c r="AE83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF83" s="3">
-        <v>100</v>
+      <c r="AE83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AG83" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH83" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7194,8 +7395,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7289,8 +7493,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7384,8 +7591,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7479,8 +7689,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7574,53 +7787,56 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-2400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>3700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-2800</v>
       </c>
-      <c r="G89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>5</v>
+      <c r="H89" s="3">
+        <v>7500</v>
       </c>
       <c r="I89" s="3">
+        <v>-50300</v>
+      </c>
+      <c r="J89" s="3">
         <v>34000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-29500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>46600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>5400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1700</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>5</v>
       </c>
@@ -7633,8 +7849,8 @@
       <c r="U89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V89" s="3">
-        <v>0</v>
+      <c r="V89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="W89" s="3">
         <v>0</v>
@@ -7660,17 +7876,20 @@
       <c r="AD89" s="3">
         <v>0</v>
       </c>
-      <c r="AE89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF89" s="3">
+      <c r="AE89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG89" s="3">
         <v>1900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7704,53 +7923,54 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
       </c>
       <c r="F91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G91" s="3">
         <v>-100</v>
       </c>
       <c r="H91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
       </c>
       <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
         <v>-100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-400</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R91" s="3" t="s">
         <v>5</v>
       </c>
@@ -7763,8 +7983,8 @@
       <c r="U91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
+      <c r="V91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="W91" s="3">
         <v>0</v>
@@ -7790,17 +8010,20 @@
       <c r="AD91" s="3">
         <v>0</v>
       </c>
-      <c r="AE91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF91" s="3">
-        <v>0</v>
+      <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AG91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7894,8 +8117,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7989,53 +8215,56 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-5200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-16700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>7600</v>
       </c>
-      <c r="G94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>5</v>
+      <c r="H94" s="3">
+        <v>-33000</v>
       </c>
       <c r="I94" s="3">
+        <v>-59300</v>
+      </c>
+      <c r="J94" s="3">
         <v>-8000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>102600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-74000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-45500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>161400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-25200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-143500</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R94" s="3" t="s">
         <v>5</v>
       </c>
@@ -8048,8 +8277,8 @@
       <c r="U94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
+      <c r="V94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="W94" s="3">
         <v>0</v>
@@ -8075,17 +8304,20 @@
       <c r="AD94" s="3">
         <v>0</v>
       </c>
-      <c r="AE94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF94" s="3">
+      <c r="AE94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG94" s="3">
         <v>-2900</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>10700</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8119,8 +8351,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8134,38 +8367,38 @@
         <v>-800</v>
       </c>
       <c r="G96" s="3">
-        <v>0</v>
+        <v>-800</v>
       </c>
       <c r="H96" s="3">
-        <v>0</v>
+        <v>-800</v>
       </c>
       <c r="I96" s="3">
         <v>-800</v>
       </c>
       <c r="J96" s="3">
+        <v>-800</v>
+      </c>
+      <c r="K96" s="3">
         <v>2200</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-800</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-2200</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-700</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>2200</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-700</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
         <v>0</v>
       </c>
@@ -8209,13 +8442,16 @@
         <v>0</v>
       </c>
       <c r="AF96" s="3">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="AG96" s="3">
         <v>-600</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>-600</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8309,8 +8545,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8404,8 +8643,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8499,53 +8741,56 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-22000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-18300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>8800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>34200</v>
       </c>
-      <c r="G100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>5</v>
+      <c r="H100" s="3">
+        <v>60200</v>
       </c>
       <c r="I100" s="3">
+        <v>63300</v>
+      </c>
+      <c r="J100" s="3">
         <v>-2700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-57800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>30300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>47100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>10900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-137100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>29700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>127700</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>5</v>
       </c>
@@ -8558,8 +8803,8 @@
       <c r="U100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
+      <c r="V100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="W100" s="3">
         <v>0</v>
@@ -8585,17 +8830,20 @@
       <c r="AD100" s="3">
         <v>0</v>
       </c>
-      <c r="AE100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF100" s="3">
+      <c r="AE100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG100" s="3">
         <v>-1100</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-10700</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8689,53 +8937,56 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-28800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-25800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-4200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>39000</v>
       </c>
-      <c r="G102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>5</v>
+      <c r="H102" s="3">
+        <v>34700</v>
       </c>
       <c r="I102" s="3">
+        <v>6200</v>
+      </c>
+      <c r="J102" s="3">
         <v>-29300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>15300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>2900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>6900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>9200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>23600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>6600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-14000</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R102" s="3" t="s">
         <v>5</v>
       </c>
@@ -8748,8 +8999,8 @@
       <c r="U102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V102" s="3">
-        <v>0</v>
+      <c r="V102" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="W102" s="3">
         <v>0</v>
@@ -8775,13 +9026,16 @@
       <c r="AD102" s="3">
         <v>0</v>
       </c>
-      <c r="AE102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF102" s="3">
+      <c r="AE102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG102" s="3">
         <v>-2100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SSBI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SSBI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="92">
   <si>
     <t>SSBI</t>
   </si>
@@ -656,245 +656,252 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>14500</v>
+      </c>
+      <c r="E8" s="3">
         <v>15000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>14900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>15600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>14600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>14200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>12500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>11300</v>
-      </c>
-      <c r="K8" s="3">
-        <v>10900</v>
       </c>
       <c r="L8" s="3">
         <v>10900</v>
       </c>
       <c r="M8" s="3">
+        <v>10900</v>
+      </c>
+      <c r="N8" s="3">
         <v>10600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>10100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>10400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>10100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>9200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>8800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>8300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>8000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>7600</v>
-      </c>
-      <c r="V8" s="3">
-        <v>7200</v>
       </c>
       <c r="W8" s="3">
         <v>7200</v>
       </c>
       <c r="X8" s="3">
+        <v>7200</v>
+      </c>
+      <c r="Y8" s="3">
         <v>6800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>6600</v>
-      </c>
-      <c r="Z8" s="3">
-        <v>6100</v>
       </c>
       <c r="AA8" s="3">
         <v>6100</v>
       </c>
       <c r="AB8" s="3">
+        <v>6100</v>
+      </c>
+      <c r="AC8" s="3">
         <v>5700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>5200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>5000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>4800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>5000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>4800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>5100</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -991,8 +998,11 @@
       <c r="AH9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1089,8 +1099,11 @@
       <c r="AH10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1125,8 +1138,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1223,8 +1237,11 @@
       <c r="AH12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1321,8 +1338,11 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1419,8 +1439,11 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1517,8 +1540,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,97 +1576,98 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E17" s="3">
         <v>7100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>7000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>6000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>5000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>400</v>
-      </c>
-      <c r="AF17" s="3">
-        <v>300</v>
       </c>
       <c r="AG17" s="3">
         <v>300</v>
@@ -1648,106 +1675,112 @@
       <c r="AH17" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI17" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>7900</v>
+        <v>7500</v>
       </c>
       <c r="E18" s="3">
         <v>7900</v>
       </c>
       <c r="F18" s="3">
-        <v>9600</v>
+        <v>7900</v>
       </c>
       <c r="G18" s="3">
         <v>9600</v>
       </c>
       <c r="H18" s="3">
+        <v>9600</v>
+      </c>
+      <c r="I18" s="3">
         <v>10600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>10200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>9300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>9800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>8900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>9600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>9000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>8800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>8300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>7300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>6700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>5900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>6000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>5500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>5300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>5500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>5400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>5500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>5100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>5200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>4700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>4400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>4500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>4400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>4700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>4500</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1782,88 +1815,89 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E20" s="3">
         <v>-5200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-5400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-5300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-3800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-4300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-4400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-2900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-4400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-3700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-4200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-3500</v>
-      </c>
-      <c r="O20" s="3">
-        <v>-4100</v>
       </c>
       <c r="P20" s="3">
         <v>-4100</v>
       </c>
       <c r="Q20" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="R20" s="3">
         <v>-3100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-3500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-2500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-3300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-2700</v>
-      </c>
-      <c r="V20" s="3">
-        <v>-3700</v>
       </c>
       <c r="W20" s="3">
         <v>-3700</v>
       </c>
       <c r="X20" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-3800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-3500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-3000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-2800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-3400</v>
-      </c>
-      <c r="AC20" s="3">
-        <v>-2900</v>
       </c>
       <c r="AD20" s="3">
         <v>-2900</v>
@@ -1872,64 +1906,67 @@
         <v>-2900</v>
       </c>
       <c r="AF20" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="AG20" s="3">
         <v>-2700</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-2500</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-2700</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E21" s="3">
         <v>2800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>4400</v>
       </c>
-      <c r="G21" s="3">
-        <v>5900</v>
-      </c>
       <c r="H21" s="3">
+        <v>5500</v>
+      </c>
+      <c r="I21" s="3">
         <v>6400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>5800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>6500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>5100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>5300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>5700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>5600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>4400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>4000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>4800</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>5</v>
       </c>
@@ -1972,14 +2009,17 @@
       <c r="AF21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AG21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH21" s="3">
         <v>2100</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2076,135 +2116,141 @@
       <c r="AH22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E23" s="3">
         <v>2700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>4300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>5800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>6300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>5700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>6400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>5400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>5200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>5400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>5500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>4700</v>
-      </c>
-      <c r="P23" s="3">
-        <v>4200</v>
       </c>
       <c r="Q23" s="3">
         <v>4200</v>
       </c>
       <c r="R23" s="3">
+        <v>4200</v>
+      </c>
+      <c r="S23" s="3">
         <v>3200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>3400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>2900</v>
-      </c>
-      <c r="V23" s="3">
-        <v>1700</v>
       </c>
       <c r="W23" s="3">
         <v>1700</v>
       </c>
       <c r="X23" s="3">
+        <v>1700</v>
+      </c>
+      <c r="Y23" s="3">
         <v>1600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>2000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>2100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>2400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1500</v>
-      </c>
-      <c r="AF23" s="3">
-        <v>2000</v>
       </c>
       <c r="AG23" s="3">
         <v>2000</v>
       </c>
       <c r="AH23" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AI23" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>600</v>
+      </c>
+      <c r="E24" s="3">
         <v>800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1700</v>
-      </c>
-      <c r="H24" s="3">
-        <v>1800</v>
       </c>
       <c r="I24" s="3">
         <v>1800</v>
       </c>
       <c r="J24" s="3">
+        <v>1800</v>
+      </c>
+      <c r="K24" s="3">
         <v>1900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1500</v>
-      </c>
-      <c r="L24" s="3">
-        <v>1600</v>
       </c>
       <c r="M24" s="3">
         <v>1600</v>
@@ -2213,67 +2259,70 @@
         <v>1600</v>
       </c>
       <c r="O24" s="3">
+        <v>1600</v>
+      </c>
+      <c r="P24" s="3">
         <v>1400</v>
-      </c>
-      <c r="P24" s="3">
-        <v>1200</v>
       </c>
       <c r="Q24" s="3">
         <v>1200</v>
       </c>
       <c r="R24" s="3">
+        <v>1200</v>
+      </c>
+      <c r="S24" s="3">
         <v>900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1000</v>
-      </c>
-      <c r="T24" s="3">
-        <v>800</v>
       </c>
       <c r="U24" s="3">
         <v>800</v>
       </c>
       <c r="V24" s="3">
+        <v>800</v>
+      </c>
+      <c r="W24" s="3">
         <v>500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>300</v>
-      </c>
-      <c r="X24" s="3">
-        <v>500</v>
       </c>
       <c r="Y24" s="3">
         <v>500</v>
       </c>
       <c r="Z24" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AA24" s="3">
         <v>600</v>
       </c>
       <c r="AB24" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AC24" s="3">
         <v>500</v>
       </c>
       <c r="AD24" s="3">
+        <v>500</v>
+      </c>
+      <c r="AE24" s="3">
         <v>700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>600</v>
-      </c>
-      <c r="AF24" s="3">
-        <v>800</v>
       </c>
       <c r="AG24" s="3">
         <v>800</v>
       </c>
       <c r="AH24" s="3">
+        <v>800</v>
+      </c>
+      <c r="AI24" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2370,204 +2419,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E26" s="3">
         <v>1900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>3000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>4100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>4600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>4000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>4500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>3900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>3700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>3800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>3900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>3300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>3000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>2200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>2400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>2000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1100</v>
-      </c>
-      <c r="Y26" s="3">
-        <v>1500</v>
       </c>
       <c r="Z26" s="3">
         <v>1500</v>
       </c>
       <c r="AA26" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AB26" s="3">
         <v>1700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1000</v>
-      </c>
-      <c r="AD26" s="3">
-        <v>900</v>
       </c>
       <c r="AE26" s="3">
         <v>900</v>
       </c>
       <c r="AF26" s="3">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="AG26" s="3">
         <v>1200</v>
       </c>
       <c r="AH26" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AI26" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E27" s="3">
         <v>1900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>3000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>4100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>4600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>4000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>4500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>3900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>3700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>3800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>3900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>3300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>3000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>2200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>2000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1100</v>
-      </c>
-      <c r="Y27" s="3">
-        <v>1500</v>
       </c>
       <c r="Z27" s="3">
         <v>1500</v>
       </c>
       <c r="AA27" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AB27" s="3">
         <v>1700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1000</v>
-      </c>
-      <c r="AD27" s="3">
-        <v>900</v>
       </c>
       <c r="AE27" s="3">
         <v>900</v>
       </c>
       <c r="AF27" s="3">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="AG27" s="3">
         <v>1200</v>
       </c>
       <c r="AH27" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AI27" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2664,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2720,8 +2781,8 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>5</v>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>5</v>
@@ -2741,12 +2802,12 @@
       <c r="AA29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC29" s="3">
         <v>-300</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2762,8 +2823,11 @@
       <c r="AH29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,88 +3025,91 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E32" s="3">
         <v>5200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>5400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>5300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>3800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>4300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>4400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>2900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>4400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>3700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>4200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>3500</v>
-      </c>
-      <c r="O32" s="3">
-        <v>4100</v>
       </c>
       <c r="P32" s="3">
         <v>4100</v>
       </c>
       <c r="Q32" s="3">
+        <v>4100</v>
+      </c>
+      <c r="R32" s="3">
         <v>3100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>3500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>2500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>3300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>2700</v>
-      </c>
-      <c r="V32" s="3">
-        <v>3700</v>
       </c>
       <c r="W32" s="3">
         <v>3700</v>
       </c>
       <c r="X32" s="3">
+        <v>3700</v>
+      </c>
+      <c r="Y32" s="3">
         <v>3800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>3500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>3000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>2800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>3400</v>
-      </c>
-      <c r="AC32" s="3">
-        <v>2900</v>
       </c>
       <c r="AD32" s="3">
         <v>2900</v>
@@ -3048,114 +3118,120 @@
         <v>2900</v>
       </c>
       <c r="AF32" s="3">
+        <v>2900</v>
+      </c>
+      <c r="AG32" s="3">
         <v>2700</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>2500</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E33" s="3">
         <v>1900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>3000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>4100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>4600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>4000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>4500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>3900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>3700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>3800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>3900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>3300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>3000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>2200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>2000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1100</v>
-      </c>
-      <c r="Y33" s="3">
-        <v>1500</v>
       </c>
       <c r="Z33" s="3">
         <v>1500</v>
       </c>
       <c r="AA33" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AB33" s="3">
         <v>1700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1000</v>
-      </c>
-      <c r="AD33" s="3">
-        <v>900</v>
       </c>
       <c r="AE33" s="3">
         <v>900</v>
       </c>
       <c r="AF33" s="3">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="AG33" s="3">
         <v>1200</v>
       </c>
       <c r="AH33" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AI33" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,209 +3328,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E35" s="3">
         <v>1900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>3000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>4100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>4600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>4000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>4500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>3900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>3700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>3800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>3900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>3300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>3000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>2200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>2000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1100</v>
-      </c>
-      <c r="Y35" s="3">
-        <v>1500</v>
       </c>
       <c r="Z35" s="3">
         <v>1500</v>
       </c>
       <c r="AA35" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AB35" s="3">
         <v>1700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1000</v>
-      </c>
-      <c r="AD35" s="3">
-        <v>900</v>
       </c>
       <c r="AE35" s="3">
         <v>900</v>
       </c>
       <c r="AF35" s="3">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="AG35" s="3">
         <v>1200</v>
       </c>
       <c r="AH35" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AI35" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,135 +3611,139 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>37700</v>
+      </c>
+      <c r="E41" s="3">
         <v>57800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>86600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>112400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>116600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>77600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>42800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>36600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>65900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>40700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>37800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>56100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>46900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>30800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>24300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>68000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>36500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>38300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>37000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>12100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>18600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>21700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>20900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>23700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>18900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>68800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>20400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>20200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>20800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>24200</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>20100</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>21800</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>13900</v>
+        <v>13700</v>
       </c>
       <c r="E42" s="3">
         <v>13900</v>
       </c>
       <c r="F42" s="3">
+        <v>13900</v>
+      </c>
+      <c r="G42" s="3">
         <v>14100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>13500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>13600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>13700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>13800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>13500</v>
-      </c>
-      <c r="L42" s="3">
-        <v>4300</v>
       </c>
       <c r="M42" s="3">
         <v>4300</v>
@@ -3662,7 +3752,7 @@
         <v>4300</v>
       </c>
       <c r="O42" s="3">
-        <v>3400</v>
+        <v>4300</v>
       </c>
       <c r="P42" s="3">
         <v>3400</v>
@@ -3674,7 +3764,7 @@
         <v>3400</v>
       </c>
       <c r="S42" s="3">
-        <v>3300</v>
+        <v>3400</v>
       </c>
       <c r="T42" s="3">
         <v>3300</v>
@@ -3686,7 +3776,7 @@
         <v>3300</v>
       </c>
       <c r="W42" s="3">
-        <v>3100</v>
+        <v>3300</v>
       </c>
       <c r="X42" s="3">
         <v>3100</v>
@@ -3698,7 +3788,7 @@
         <v>3100</v>
       </c>
       <c r="AA42" s="3">
-        <v>5100</v>
+        <v>3100</v>
       </c>
       <c r="AB42" s="3">
         <v>5100</v>
@@ -3707,22 +3797,25 @@
         <v>5100</v>
       </c>
       <c r="AD42" s="3">
+        <v>5100</v>
+      </c>
+      <c r="AE42" s="3">
         <v>4800</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>5200</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>5300</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>4900</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3819,8 +3912,11 @@
       <c r="AH43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3917,8 +4013,11 @@
       <c r="AH44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4015,8 +4114,11 @@
       <c r="AH45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -4113,8 +4215,11 @@
       <c r="AH46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4211,58 +4316,61 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E48" s="3">
         <v>6200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>6400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>6600</v>
-      </c>
-      <c r="G48" s="3">
-        <v>6800</v>
       </c>
       <c r="H48" s="3">
         <v>6800</v>
       </c>
       <c r="I48" s="3">
+        <v>6800</v>
+      </c>
+      <c r="J48" s="3">
         <v>7000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>7000</v>
-      </c>
-      <c r="N48" s="3">
-        <v>7200</v>
       </c>
       <c r="O48" s="3">
         <v>7200</v>
       </c>
       <c r="P48" s="3">
+        <v>7200</v>
+      </c>
+      <c r="Q48" s="3">
         <v>7300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>7000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>6200</v>
-      </c>
-      <c r="S48" s="3">
-        <v>6300</v>
       </c>
       <c r="T48" s="3">
         <v>6300</v>
@@ -4274,43 +4382,46 @@
         <v>6300</v>
       </c>
       <c r="W48" s="3">
+        <v>6300</v>
+      </c>
+      <c r="X48" s="3">
         <v>6400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>5800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>5300</v>
-      </c>
-      <c r="Z48" s="3">
-        <v>5200</v>
       </c>
       <c r="AA48" s="3">
         <v>5200</v>
       </c>
       <c r="AB48" s="3">
-        <v>5300</v>
+        <v>5200</v>
       </c>
       <c r="AC48" s="3">
         <v>5300</v>
       </c>
       <c r="AD48" s="3">
+        <v>5300</v>
+      </c>
+      <c r="AE48" s="3">
         <v>5400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>5500</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>5400</v>
-      </c>
-      <c r="AG48" s="3">
-        <v>5500</v>
       </c>
       <c r="AH48" s="3">
         <v>5500</v>
       </c>
-    </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI48" s="3">
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4407,8 +4518,11 @@
       <c r="AH49" s="3">
         <v>4100</v>
       </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3">
+        <v>4100</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,8 +4720,11 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4701,8 +4821,11 @@
       <c r="AH52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,106 +4922,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1080200</v>
+      </c>
+      <c r="E54" s="3">
         <v>1122500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1142200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1161400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1147000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1115300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1043800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>980800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>982300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>958100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>922600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>901600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>886100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>865900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>833800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>850700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>721600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>696000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>680800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>635600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>626300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>622100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>595200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>586000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>577000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>610900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>539000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>537500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>524500</v>
-      </c>
-      <c r="AF54" s="3">
-        <v>513700</v>
       </c>
       <c r="AG54" s="3">
         <v>513700</v>
       </c>
       <c r="AH54" s="3">
+        <v>513700</v>
+      </c>
+      <c r="AI54" s="3">
         <v>518300</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,106 +5099,110 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E57" s="3">
         <v>4100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>6500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>7100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>11100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>4700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>4500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>6600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>5600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>4300</v>
-      </c>
-      <c r="T57" s="3">
-        <v>3300</v>
       </c>
       <c r="U57" s="3">
         <v>3300</v>
       </c>
       <c r="V57" s="3">
+        <v>3300</v>
+      </c>
+      <c r="W57" s="3">
         <v>3500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>3000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1900</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>3200</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>8100</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5165,56 +5299,59 @@
       <c r="AH58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E59" s="3">
         <v>1000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1400</v>
-      </c>
-      <c r="O59" s="3">
-        <v>1300</v>
       </c>
       <c r="P59" s="3">
         <v>1300</v>
       </c>
       <c r="Q59" s="3">
+        <v>1300</v>
+      </c>
+      <c r="R59" s="3">
         <v>900</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>5</v>
       </c>
@@ -5230,8 +5367,8 @@
       <c r="W59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X59" s="3">
-        <v>0</v>
+      <c r="X59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Y59" s="3">
         <v>0</v>
@@ -5263,8 +5400,11 @@
       <c r="AH59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5361,8 +5501,11 @@
       <c r="AH60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5424,7 +5567,7 @@
         <v>5900</v>
       </c>
       <c r="W61" s="3">
-        <v>0</v>
+        <v>5900</v>
       </c>
       <c r="X61" s="3">
         <v>0</v>
@@ -5459,8 +5602,11 @@
       <c r="AH61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5557,8 +5703,11 @@
       <c r="AH62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5753,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,106 +6006,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>982300</v>
+      </c>
+      <c r="E66" s="3">
         <v>1024800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1048700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1067000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1054400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1026800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>959400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>896100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>898600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>873800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>840600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>822700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>810600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>790200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>760400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>779400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>653400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>628600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>614300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>570900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>562900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>560600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>534700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>525800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>517300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>551200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>478500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>477000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>465200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>455100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>453400</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>458800</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6279,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,106 +6548,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>69500</v>
+      </c>
+      <c r="E72" s="3">
         <v>69000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>67900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>66800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>64700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>61400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>57600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>54500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>50800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>47600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>44800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>41700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>38500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>37500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>35300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>33100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>31600</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U72" s="3">
+      <c r="U72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V72" s="3">
         <v>28800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>27500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>27000</v>
       </c>
-      <c r="X72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y72" s="3">
+      <c r="Y72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z72" s="3">
         <v>25900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>25200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>24400</v>
       </c>
-      <c r="AB72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC72" s="3">
+      <c r="AC72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD72" s="3">
         <v>23600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>23300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>23100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>22800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>22200</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>21600</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,106 +6952,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>97900</v>
+      </c>
+      <c r="E76" s="3">
         <v>97700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>93400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>94400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>92700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>88500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>84400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>84700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>83700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>84300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>82000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>79000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>75500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>75600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>73400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>71200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>68200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>67300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>66500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>64700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>63400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>61500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>60500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>60200</v>
-      </c>
-      <c r="AA76" s="3">
-        <v>59700</v>
       </c>
       <c r="AB76" s="3">
         <v>59700</v>
       </c>
       <c r="AC76" s="3">
+        <v>59700</v>
+      </c>
+      <c r="AD76" s="3">
         <v>60500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>60400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>59300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>58600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>60300</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>59500</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,209 +7154,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E81" s="3">
         <v>1900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>3000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>4100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>4600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>4000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>4500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>3900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>3700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>3800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>3900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>3300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>3000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>2200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>2000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1100</v>
-      </c>
-      <c r="Y81" s="3">
-        <v>1500</v>
       </c>
       <c r="Z81" s="3">
         <v>1500</v>
       </c>
       <c r="AA81" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AB81" s="3">
         <v>1700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1000</v>
-      </c>
-      <c r="AD81" s="3">
-        <v>900</v>
       </c>
       <c r="AE81" s="3">
         <v>900</v>
       </c>
       <c r="AF81" s="3">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="AG81" s="3">
         <v>1200</v>
       </c>
       <c r="AH81" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AI81" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,13 +7400,14 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>100</v>
+      <c r="D83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E83" s="3">
         <v>100</v>
@@ -7217,10 +7416,10 @@
         <v>100</v>
       </c>
       <c r="G83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H83" s="3">
-        <v>100</v>
+        <v>-300</v>
       </c>
       <c r="I83" s="3">
         <v>100</v>
@@ -7229,29 +7428,29 @@
         <v>100</v>
       </c>
       <c r="K83" s="3">
+        <v>100</v>
+      </c>
+      <c r="L83" s="3">
         <v>-300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>-300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>-200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>600</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S83" s="3" t="s">
         <v>5</v>
       </c>
@@ -7264,8 +7463,8 @@
       <c r="V83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W83" s="3">
-        <v>0</v>
+      <c r="W83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="X83" s="3">
         <v>0</v>
@@ -7291,17 +7490,20 @@
       <c r="AE83" s="3">
         <v>0</v>
       </c>
-      <c r="AF83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG83" s="3">
-        <v>100</v>
+      <c r="AF83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AH83" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,56 +8004,59 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E89" s="3">
         <v>-900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-2400</v>
       </c>
-      <c r="F89" s="3">
-        <v>3700</v>
-      </c>
       <c r="G89" s="3">
-        <v>-2800</v>
+        <v>900</v>
       </c>
       <c r="H89" s="3">
+        <v>-16500</v>
+      </c>
+      <c r="I89" s="3">
         <v>7500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-50300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>34000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-29500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>46600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>5400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>2000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1700</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S89" s="3" t="s">
         <v>5</v>
       </c>
@@ -7852,8 +8069,8 @@
       <c r="V89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W89" s="3">
-        <v>0</v>
+      <c r="W89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="X89" s="3">
         <v>0</v>
@@ -7879,17 +8096,20 @@
       <c r="AE89" s="3">
         <v>0</v>
       </c>
-      <c r="AF89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG89" s="3">
+      <c r="AF89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH89" s="3">
         <v>1900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,8 +8144,9 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7951,29 +8172,29 @@
         <v>-100</v>
       </c>
       <c r="K91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
       </c>
       <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-400</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S91" s="3" t="s">
         <v>5</v>
       </c>
@@ -7986,8 +8207,8 @@
       <c r="V91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W91" s="3">
-        <v>0</v>
+      <c r="W91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="X91" s="3">
         <v>0</v>
@@ -8013,17 +8234,20 @@
       <c r="AE91" s="3">
         <v>0</v>
       </c>
-      <c r="AF91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG91" s="3">
-        <v>0</v>
+      <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AH91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,56 +8445,59 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E94" s="3">
         <v>-5900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-5200</v>
       </c>
-      <c r="F94" s="3">
-        <v>-16700</v>
-      </c>
       <c r="G94" s="3">
-        <v>7600</v>
+        <v>-9100</v>
       </c>
       <c r="H94" s="3">
+        <v>124800</v>
+      </c>
+      <c r="I94" s="3">
         <v>-33000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-59300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-8000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>102600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-74000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-45500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>161400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-25200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-143500</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S94" s="3" t="s">
         <v>5</v>
       </c>
@@ -8280,8 +8510,8 @@
       <c r="V94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W94" s="3">
-        <v>0</v>
+      <c r="W94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="X94" s="3">
         <v>0</v>
@@ -8307,17 +8537,20 @@
       <c r="AE94" s="3">
         <v>0</v>
       </c>
-      <c r="AF94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG94" s="3">
+      <c r="AF94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH94" s="3">
         <v>-2900</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>10700</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,13 +8585,14 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-800</v>
+        <v>0</v>
       </c>
       <c r="E96" s="3">
         <v>-800</v>
@@ -8367,10 +8601,10 @@
         <v>-800</v>
       </c>
       <c r="G96" s="3">
-        <v>-800</v>
+        <v>-1600</v>
       </c>
       <c r="H96" s="3">
-        <v>-800</v>
+        <v>2400</v>
       </c>
       <c r="I96" s="3">
         <v>-800</v>
@@ -8379,29 +8613,29 @@
         <v>-800</v>
       </c>
       <c r="K96" s="3">
+        <v>-800</v>
+      </c>
+      <c r="L96" s="3">
         <v>2200</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-800</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-2200</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-700</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>2200</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-700</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-2200</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
         <v>0</v>
       </c>
@@ -8445,13 +8679,16 @@
         <v>0</v>
       </c>
       <c r="AG96" s="3">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="AH96" s="3">
         <v>-600</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>-600</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,56 +8987,59 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E100" s="3">
         <v>-22000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-18300</v>
       </c>
-      <c r="F100" s="3">
-        <v>8800</v>
-      </c>
       <c r="G100" s="3">
-        <v>34200</v>
+        <v>43000</v>
       </c>
       <c r="H100" s="3">
+        <v>-106200</v>
+      </c>
+      <c r="I100" s="3">
         <v>60200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>63300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-57800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>30300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>47100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>10900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-137100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>29700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>127700</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>5</v>
       </c>
@@ -8806,8 +9052,8 @@
       <c r="V100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
+      <c r="W100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="X100" s="3">
         <v>0</v>
@@ -8833,17 +9079,20 @@
       <c r="AE100" s="3">
         <v>0</v>
       </c>
-      <c r="AF100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG100" s="3">
+      <c r="AF100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH100" s="3">
         <v>-1100</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-10700</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8940,56 +9189,59 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3">
+      <c r="D102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E102" s="3">
         <v>-28800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-25800</v>
       </c>
-      <c r="F102" s="3">
-        <v>-4200</v>
-      </c>
       <c r="G102" s="3">
-        <v>39000</v>
+        <v>34800</v>
       </c>
       <c r="H102" s="3">
+        <v>2100</v>
+      </c>
+      <c r="I102" s="3">
         <v>34700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>6200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-29300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>15300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>2900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>6900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>9200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>23600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>6600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-14000</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S102" s="3" t="s">
         <v>5</v>
       </c>
@@ -9002,8 +9254,8 @@
       <c r="V102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W102" s="3">
-        <v>0</v>
+      <c r="W102" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="X102" s="3">
         <v>0</v>
@@ -9029,13 +9281,16 @@
       <c r="AE102" s="3">
         <v>0</v>
       </c>
-      <c r="AF102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG102" s="3">
+      <c r="AF102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH102" s="3">
         <v>-2100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SSBI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SSBI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="92">
   <si>
     <t>SSBI</t>
   </si>
@@ -656,240 +656,248 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>14500</v>
+        <v>7000</v>
       </c>
       <c r="E8" s="3">
-        <v>15000</v>
+        <v>7900</v>
       </c>
       <c r="F8" s="3">
-        <v>14900</v>
+        <v>8400</v>
       </c>
       <c r="G8" s="3">
-        <v>15600</v>
+        <v>8200</v>
       </c>
       <c r="H8" s="3">
-        <v>14600</v>
+        <v>9400</v>
       </c>
       <c r="I8" s="3">
+        <v>11100</v>
+      </c>
+      <c r="J8" s="3">
+        <v>11600</v>
+      </c>
+      <c r="K8" s="3">
         <v>14200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>12500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>11300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>10900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>10900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>10600</v>
-      </c>
-      <c r="O8" s="3">
-        <v>10100</v>
-      </c>
-      <c r="P8" s="3">
-        <v>10400</v>
       </c>
       <c r="Q8" s="3">
         <v>10100</v>
       </c>
       <c r="R8" s="3">
+        <v>10400</v>
+      </c>
+      <c r="S8" s="3">
+        <v>10100</v>
+      </c>
+      <c r="T8" s="3">
         <v>9200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>8800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>8300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>8000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>7600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>7200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>7200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>6800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>6600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>6100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>6100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>5700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>5200</v>
-      </c>
-      <c r="AE8" s="3">
-        <v>5000</v>
-      </c>
-      <c r="AF8" s="3">
-        <v>4800</v>
       </c>
       <c r="AG8" s="3">
         <v>5000</v>
@@ -898,10 +906,16 @@
         <v>4800</v>
       </c>
       <c r="AI8" s="3">
+        <v>5000</v>
+      </c>
+      <c r="AJ8" s="3">
+        <v>4800</v>
+      </c>
+      <c r="AK8" s="3">
         <v>5100</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1001,31 +1015,37 @@
       <c r="AI9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>5</v>
+      <c r="D10" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>7900</v>
+      </c>
+      <c r="F10" s="3">
+        <v>8400</v>
+      </c>
+      <c r="G10" s="3">
+        <v>8200</v>
+      </c>
+      <c r="H10" s="3">
+        <v>9400</v>
+      </c>
+      <c r="I10" s="3">
+        <v>11100</v>
+      </c>
+      <c r="J10" s="3">
+        <v>11600</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>5</v>
@@ -1102,8 +1122,14 @@
       <c r="AI10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1139,8 +1165,10 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1240,8 +1268,14 @@
       <c r="AI12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1341,31 +1375,37 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1442,31 +1482,37 @@
       <c r="AI14" s="3">
         <v>0</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1543,8 +1589,14 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1577,210 +1629,224 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>7000</v>
+        <v>6200</v>
       </c>
       <c r="E17" s="3">
-        <v>7100</v>
+        <v>6600</v>
       </c>
       <c r="F17" s="3">
-        <v>7000</v>
+        <v>6400</v>
       </c>
       <c r="G17" s="3">
-        <v>6000</v>
+        <v>5500</v>
       </c>
       <c r="H17" s="3">
-        <v>5000</v>
+        <v>6900</v>
       </c>
       <c r="I17" s="3">
+        <v>6800</v>
+      </c>
+      <c r="J17" s="3">
+        <v>5800</v>
+      </c>
+      <c r="K17" s="3">
         <v>3600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>2300</v>
-      </c>
-      <c r="K17" s="3">
-        <v>2000</v>
-      </c>
-      <c r="L17" s="3">
-        <v>1100</v>
       </c>
       <c r="M17" s="3">
         <v>2000</v>
       </c>
       <c r="N17" s="3">
+        <v>1100</v>
+      </c>
+      <c r="O17" s="3">
+        <v>2000</v>
+      </c>
+      <c r="P17" s="3">
         <v>1000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>1100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>1600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>1800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>1900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>2100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>2400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>2000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>2100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>1900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>1800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>1400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>1100</v>
-      </c>
-      <c r="AA17" s="3">
-        <v>1000</v>
-      </c>
-      <c r="AB17" s="3">
-        <v>900</v>
       </c>
       <c r="AC17" s="3">
         <v>1000</v>
       </c>
       <c r="AD17" s="3">
+        <v>900</v>
+      </c>
+      <c r="AE17" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AF17" s="3">
         <v>800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>400</v>
-      </c>
-      <c r="AG17" s="3">
-        <v>300</v>
-      </c>
-      <c r="AH17" s="3">
-        <v>300</v>
       </c>
       <c r="AI17" s="3">
         <v>300</v>
       </c>
+      <c r="AJ17" s="3">
+        <v>300</v>
+      </c>
+      <c r="AK17" s="3">
+        <v>300</v>
+      </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>7500</v>
+        <v>800</v>
       </c>
       <c r="E18" s="3">
-        <v>7900</v>
+        <v>1300</v>
       </c>
       <c r="F18" s="3">
-        <v>7900</v>
+        <v>2000</v>
       </c>
       <c r="G18" s="3">
+        <v>2700</v>
+      </c>
+      <c r="H18" s="3">
+        <v>2500</v>
+      </c>
+      <c r="I18" s="3">
+        <v>4300</v>
+      </c>
+      <c r="J18" s="3">
+        <v>5800</v>
+      </c>
+      <c r="K18" s="3">
+        <v>10600</v>
+      </c>
+      <c r="L18" s="3">
+        <v>10200</v>
+      </c>
+      <c r="M18" s="3">
+        <v>9300</v>
+      </c>
+      <c r="N18" s="3">
+        <v>9800</v>
+      </c>
+      <c r="O18" s="3">
+        <v>8900</v>
+      </c>
+      <c r="P18" s="3">
         <v>9600</v>
       </c>
-      <c r="H18" s="3">
-        <v>9600</v>
-      </c>
-      <c r="I18" s="3">
-        <v>10600</v>
-      </c>
-      <c r="J18" s="3">
-        <v>10200</v>
-      </c>
-      <c r="K18" s="3">
-        <v>9300</v>
-      </c>
-      <c r="L18" s="3">
-        <v>9800</v>
-      </c>
-      <c r="M18" s="3">
-        <v>8900</v>
-      </c>
-      <c r="N18" s="3">
-        <v>9600</v>
-      </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>9000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>8800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>8300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>7300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>6700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>5900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>6000</v>
-      </c>
-      <c r="V18" s="3">
-        <v>5500</v>
-      </c>
-      <c r="W18" s="3">
-        <v>5300</v>
       </c>
       <c r="X18" s="3">
         <v>5500</v>
       </c>
       <c r="Y18" s="3">
-        <v>5400</v>
+        <v>5300</v>
       </c>
       <c r="Z18" s="3">
         <v>5500</v>
       </c>
       <c r="AA18" s="3">
+        <v>5400</v>
+      </c>
+      <c r="AB18" s="3">
+        <v>5500</v>
+      </c>
+      <c r="AC18" s="3">
         <v>5100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>5200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>4700</v>
-      </c>
-      <c r="AD18" s="3">
-        <v>4400</v>
-      </c>
-      <c r="AE18" s="3">
-        <v>4500</v>
       </c>
       <c r="AF18" s="3">
         <v>4400</v>
       </c>
       <c r="AG18" s="3">
+        <v>4500</v>
+      </c>
+      <c r="AH18" s="3">
+        <v>4400</v>
+      </c>
+      <c r="AI18" s="3">
         <v>4700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>4500</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1816,163 +1882,171 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>-5500</v>
-      </c>
-      <c r="E20" s="3">
-        <v>-5200</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-5400</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-5300</v>
-      </c>
-      <c r="H20" s="3">
-        <v>-3800</v>
-      </c>
-      <c r="I20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K20" s="3">
         <v>-4300</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-4400</v>
-      </c>
-      <c r="K20" s="3">
-        <v>-2900</v>
       </c>
       <c r="L20" s="3">
         <v>-4400</v>
       </c>
       <c r="M20" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="N20" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="O20" s="3">
         <v>-3700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-4200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-3500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-4100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-3100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-3500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-2500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-3300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-2700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-3700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-3700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>-3800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>-3500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>-3000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>-2800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>-3400</v>
-      </c>
-      <c r="AD20" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="AE20" s="3">
-        <v>-2900</v>
       </c>
       <c r="AF20" s="3">
         <v>-2900</v>
       </c>
       <c r="AG20" s="3">
-        <v>-2700</v>
+        <v>-2900</v>
       </c>
       <c r="AH20" s="3">
-        <v>-2500</v>
+        <v>-2900</v>
       </c>
       <c r="AI20" s="3">
         <v>-2700</v>
       </c>
+      <c r="AJ20" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="AK20" s="3">
+        <v>-2700</v>
+      </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>5</v>
+      <c r="D21" s="3">
+        <v>900</v>
       </c>
       <c r="E21" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F21" s="3">
+        <v>2100</v>
+      </c>
+      <c r="G21" s="3">
         <v>2800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>2600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>4400</v>
       </c>
-      <c r="H21" s="3">
-        <v>5500</v>
-      </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
+        <v>5900</v>
+      </c>
+      <c r="K21" s="3">
         <v>6400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>5800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>6500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>5100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>5300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>5700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>5600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>4400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>4000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>4800</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>5</v>
       </c>
@@ -2012,37 +2086,43 @@
       <c r="AG21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AH21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ21" s="3">
         <v>2100</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AK21" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -2119,210 +2199,228 @@
       <c r="AI22" s="3">
         <v>0</v>
       </c>
+      <c r="AJ22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>800</v>
+      </c>
+      <c r="E23" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F23" s="3">
         <v>2000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>2700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>2500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>4300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>5800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>6300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>5700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>6400</v>
-      </c>
-      <c r="L23" s="3">
-        <v>5400</v>
-      </c>
-      <c r="M23" s="3">
-        <v>5200</v>
       </c>
       <c r="N23" s="3">
         <v>5400</v>
       </c>
       <c r="O23" s="3">
+        <v>5200</v>
+      </c>
+      <c r="P23" s="3">
+        <v>5400</v>
+      </c>
+      <c r="Q23" s="3">
         <v>5500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>4700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>4200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>4200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>3200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>3400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>2600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>2900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>1700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>1700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>1600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>2000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>2100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>2400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>1300</v>
-      </c>
-      <c r="AD23" s="3">
-        <v>1500</v>
-      </c>
-      <c r="AE23" s="3">
-        <v>1600</v>
       </c>
       <c r="AF23" s="3">
         <v>1500</v>
       </c>
       <c r="AG23" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AH23" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AI23" s="3">
         <v>2000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>2000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>200</v>
+      </c>
+      <c r="E24" s="3">
+        <v>400</v>
+      </c>
+      <c r="F24" s="3">
         <v>600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>1300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>1700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>1800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>1800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>1900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>1500</v>
-      </c>
-      <c r="M24" s="3">
-        <v>1600</v>
-      </c>
-      <c r="N24" s="3">
-        <v>1600</v>
       </c>
       <c r="O24" s="3">
         <v>1600</v>
       </c>
       <c r="P24" s="3">
+        <v>1600</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>1600</v>
+      </c>
+      <c r="R24" s="3">
         <v>1400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>1200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>1200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>1000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>800</v>
-      </c>
-      <c r="W24" s="3">
-        <v>500</v>
-      </c>
-      <c r="X24" s="3">
-        <v>300</v>
       </c>
       <c r="Y24" s="3">
         <v>500</v>
       </c>
       <c r="Z24" s="3">
+        <v>300</v>
+      </c>
+      <c r="AA24" s="3">
         <v>500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
+        <v>500</v>
+      </c>
+      <c r="AC24" s="3">
         <v>600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>600</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AI24" s="3">
         <v>800</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AJ24" s="3">
         <v>800</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AK24" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2422,210 +2520,228 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>600</v>
+      </c>
+      <c r="E26" s="3">
+        <v>900</v>
+      </c>
+      <c r="F26" s="3">
         <v>1400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>1900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>1800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>3000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>4100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>4600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>4000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>4500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>3900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>3700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>3800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>3900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>3300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>2900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>3000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>2200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>2400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>1800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>2000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>1200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>1400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>1100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>1500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>1500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>1700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>1000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>900</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>1200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>1200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>600</v>
+      </c>
+      <c r="E27" s="3">
+        <v>900</v>
+      </c>
+      <c r="F27" s="3">
         <v>1400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>1900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>1800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>3000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>4100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>4600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>4000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>4500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>3900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>3700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>3800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>3900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>3300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>2900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>3000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>2200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>2400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>1800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>2000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>1200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>1400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>1100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>1500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>1500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>1700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>1000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>1200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>1200</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2725,8 +2841,14 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2784,11 +2906,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W29" s="3" t="s">
-        <v>5</v>
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>5</v>
@@ -2805,15 +2927,15 @@
       <c r="AB29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE29" s="3">
         <v>-300</v>
       </c>
-      <c r="AD29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AF29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2826,8 +2948,14 @@
       <c r="AI29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2927,8 +3055,14 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3028,210 +3162,228 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>5500</v>
-      </c>
-      <c r="E32" s="3">
-        <v>5200</v>
-      </c>
-      <c r="F32" s="3">
-        <v>5400</v>
-      </c>
-      <c r="G32" s="3">
-        <v>5300</v>
-      </c>
-      <c r="H32" s="3">
-        <v>3800</v>
-      </c>
-      <c r="I32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K32" s="3">
         <v>4300</v>
-      </c>
-      <c r="J32" s="3">
-        <v>4400</v>
-      </c>
-      <c r="K32" s="3">
-        <v>2900</v>
       </c>
       <c r="L32" s="3">
         <v>4400</v>
       </c>
       <c r="M32" s="3">
+        <v>2900</v>
+      </c>
+      <c r="N32" s="3">
+        <v>4400</v>
+      </c>
+      <c r="O32" s="3">
         <v>3700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>4200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>3500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>4100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>4100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>3100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>3500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>2500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>3300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>2700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>3700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>3700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>3800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>3500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>3000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>2800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>3400</v>
-      </c>
-      <c r="AD32" s="3">
-        <v>2900</v>
-      </c>
-      <c r="AE32" s="3">
-        <v>2900</v>
       </c>
       <c r="AF32" s="3">
         <v>2900</v>
       </c>
       <c r="AG32" s="3">
-        <v>2700</v>
+        <v>2900</v>
       </c>
       <c r="AH32" s="3">
-        <v>2500</v>
+        <v>2900</v>
       </c>
       <c r="AI32" s="3">
         <v>2700</v>
       </c>
+      <c r="AJ32" s="3">
+        <v>2500</v>
+      </c>
+      <c r="AK32" s="3">
+        <v>2700</v>
+      </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>600</v>
+      </c>
+      <c r="E33" s="3">
+        <v>900</v>
+      </c>
+      <c r="F33" s="3">
         <v>1400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>1900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>1800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>3000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>4100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>4600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>4000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>4500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>3900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>3700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>3800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>3900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>3300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>2900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>3000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>2200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>2400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>1800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>2000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>1200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>1400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>1100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>1500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>1500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>1700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>1000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>1200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>1200</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3331,215 +3483,233 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>600</v>
+      </c>
+      <c r="E35" s="3">
+        <v>900</v>
+      </c>
+      <c r="F35" s="3">
         <v>1400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>1900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>1800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>3000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>4100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>4600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>4000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>4500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>3900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>3700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>3800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>3900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>3300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>2900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>3000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>2200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>2400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>1800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>2000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>1200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>1400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>1100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>1500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>1500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>1700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>1000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>1200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>1200</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3575,8 +3745,10 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3612,153 +3784,161 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>80900</v>
+      </c>
+      <c r="E41" s="3">
+        <v>40100</v>
+      </c>
+      <c r="F41" s="3">
         <v>37700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>57800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>86600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>112400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>116600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>77600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>42800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>36600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>65900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>40700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>37800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>56100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>46900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>30800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>24300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>68000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>36500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>38300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>37000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>12100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>18600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>21700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>20900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>23700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>18900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>68800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>20400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>20200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>20800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>24200</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>20100</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AK41" s="3">
         <v>21800</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
+        <v>13600</v>
+      </c>
+      <c r="L42" s="3">
         <v>13700</v>
       </c>
-      <c r="E42" s="3">
-        <v>13900</v>
-      </c>
-      <c r="F42" s="3">
-        <v>13900</v>
-      </c>
-      <c r="G42" s="3">
-        <v>14100</v>
-      </c>
-      <c r="H42" s="3">
+      <c r="M42" s="3">
+        <v>13800</v>
+      </c>
+      <c r="N42" s="3">
         <v>13500</v>
-      </c>
-      <c r="I42" s="3">
-        <v>13600</v>
-      </c>
-      <c r="J42" s="3">
-        <v>13700</v>
-      </c>
-      <c r="K42" s="3">
-        <v>13800</v>
-      </c>
-      <c r="L42" s="3">
-        <v>13500</v>
-      </c>
-      <c r="M42" s="3">
-        <v>4300</v>
-      </c>
-      <c r="N42" s="3">
-        <v>4300</v>
       </c>
       <c r="O42" s="3">
         <v>4300</v>
       </c>
       <c r="P42" s="3">
-        <v>3400</v>
+        <v>4300</v>
       </c>
       <c r="Q42" s="3">
-        <v>3400</v>
+        <v>4300</v>
       </c>
       <c r="R42" s="3">
         <v>3400</v>
@@ -3767,10 +3947,10 @@
         <v>3400</v>
       </c>
       <c r="T42" s="3">
-        <v>3300</v>
+        <v>3400</v>
       </c>
       <c r="U42" s="3">
-        <v>3300</v>
+        <v>3400</v>
       </c>
       <c r="V42" s="3">
         <v>3300</v>
@@ -3779,10 +3959,10 @@
         <v>3300</v>
       </c>
       <c r="X42" s="3">
-        <v>3100</v>
+        <v>3300</v>
       </c>
       <c r="Y42" s="3">
-        <v>3100</v>
+        <v>3300</v>
       </c>
       <c r="Z42" s="3">
         <v>3100</v>
@@ -3791,54 +3971,60 @@
         <v>3100</v>
       </c>
       <c r="AB42" s="3">
-        <v>5100</v>
+        <v>3100</v>
       </c>
       <c r="AC42" s="3">
-        <v>5100</v>
+        <v>3100</v>
       </c>
       <c r="AD42" s="3">
         <v>5100</v>
       </c>
       <c r="AE42" s="3">
+        <v>5100</v>
+      </c>
+      <c r="AF42" s="3">
+        <v>5100</v>
+      </c>
+      <c r="AG42" s="3">
         <v>4800</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AH42" s="3">
         <v>5200</v>
-      </c>
-      <c r="AG42" s="3">
-        <v>5300</v>
-      </c>
-      <c r="AH42" s="3">
-        <v>4900</v>
       </c>
       <c r="AI42" s="3">
         <v>5300</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>4900</v>
+      </c>
+      <c r="AK42" s="3">
+        <v>5300</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>0</v>
-      </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
+      <c r="D43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -3915,31 +4101,37 @@
       <c r="AI43" s="3">
         <v>0</v>
       </c>
+      <c r="AJ43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>0</v>
+        <v>5100</v>
       </c>
       <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+        <v>5100</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -4016,31 +4208,37 @@
       <c r="AI44" s="3">
         <v>0</v>
       </c>
+      <c r="AJ44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>16200</v>
       </c>
       <c r="E45" s="3">
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="F45" s="3">
-        <v>0</v>
+        <v>3800</v>
       </c>
       <c r="G45" s="3">
-        <v>0</v>
+        <v>3700</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
+        <v>3800</v>
       </c>
       <c r="I45" s="3">
-        <v>0</v>
+        <v>3800</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>4100</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -4117,31 +4315,37 @@
       <c r="AI45" s="3">
         <v>0</v>
       </c>
+      <c r="AJ45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>102300</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>48900</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>41600</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>61500</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>90400</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>116200</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>120600</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -4218,31 +4422,37 @@
       <c r="AI46" s="3">
         <v>0</v>
       </c>
+      <c r="AJ46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
+        <v>89800</v>
       </c>
       <c r="E47" s="3">
-        <v>0</v>
+        <v>96900</v>
       </c>
       <c r="F47" s="3">
-        <v>0</v>
+        <v>97500</v>
       </c>
       <c r="G47" s="3">
-        <v>0</v>
+        <v>98500</v>
       </c>
       <c r="H47" s="3">
-        <v>0</v>
+        <v>94200</v>
       </c>
       <c r="I47" s="3">
-        <v>0</v>
+        <v>97700</v>
       </c>
       <c r="J47" s="3">
-        <v>0</v>
+        <v>98400</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -4319,8 +4529,14 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4328,55 +4544,55 @@
         <v>5300</v>
       </c>
       <c r="E48" s="3">
+        <v>6000</v>
+      </c>
+      <c r="F48" s="3">
+        <v>6100</v>
+      </c>
+      <c r="G48" s="3">
+        <v>6300</v>
+      </c>
+      <c r="H48" s="3">
+        <v>6400</v>
+      </c>
+      <c r="I48" s="3">
+        <v>6600</v>
+      </c>
+      <c r="J48" s="3">
+        <v>6800</v>
+      </c>
+      <c r="K48" s="3">
+        <v>6800</v>
+      </c>
+      <c r="L48" s="3">
+        <v>7000</v>
+      </c>
+      <c r="M48" s="3">
+        <v>6500</v>
+      </c>
+      <c r="N48" s="3">
+        <v>6700</v>
+      </c>
+      <c r="O48" s="3">
+        <v>6900</v>
+      </c>
+      <c r="P48" s="3">
+        <v>7000</v>
+      </c>
+      <c r="Q48" s="3">
+        <v>7200</v>
+      </c>
+      <c r="R48" s="3">
+        <v>7200</v>
+      </c>
+      <c r="S48" s="3">
+        <v>7300</v>
+      </c>
+      <c r="T48" s="3">
+        <v>7000</v>
+      </c>
+      <c r="U48" s="3">
         <v>6200</v>
-      </c>
-      <c r="F48" s="3">
-        <v>6400</v>
-      </c>
-      <c r="G48" s="3">
-        <v>6600</v>
-      </c>
-      <c r="H48" s="3">
-        <v>6800</v>
-      </c>
-      <c r="I48" s="3">
-        <v>6800</v>
-      </c>
-      <c r="J48" s="3">
-        <v>7000</v>
-      </c>
-      <c r="K48" s="3">
-        <v>6500</v>
-      </c>
-      <c r="L48" s="3">
-        <v>6700</v>
-      </c>
-      <c r="M48" s="3">
-        <v>6900</v>
-      </c>
-      <c r="N48" s="3">
-        <v>7000</v>
-      </c>
-      <c r="O48" s="3">
-        <v>7200</v>
-      </c>
-      <c r="P48" s="3">
-        <v>7200</v>
-      </c>
-      <c r="Q48" s="3">
-        <v>7300</v>
-      </c>
-      <c r="R48" s="3">
-        <v>7000</v>
-      </c>
-      <c r="S48" s="3">
-        <v>6200</v>
-      </c>
-      <c r="T48" s="3">
-        <v>6300</v>
-      </c>
-      <c r="U48" s="3">
-        <v>6300</v>
       </c>
       <c r="V48" s="3">
         <v>6300</v>
@@ -4385,31 +4601,31 @@
         <v>6300</v>
       </c>
       <c r="X48" s="3">
+        <v>6300</v>
+      </c>
+      <c r="Y48" s="3">
+        <v>6300</v>
+      </c>
+      <c r="Z48" s="3">
         <v>6400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>5800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>5300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>5200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>5200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>5300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>5300</v>
-      </c>
-      <c r="AE48" s="3">
-        <v>5400</v>
-      </c>
-      <c r="AF48" s="3">
-        <v>5500</v>
       </c>
       <c r="AG48" s="3">
         <v>5400</v>
@@ -4418,10 +4634,16 @@
         <v>5500</v>
       </c>
       <c r="AI48" s="3">
+        <v>5400</v>
+      </c>
+      <c r="AJ48" s="3">
         <v>5500</v>
       </c>
+      <c r="AK48" s="3">
+        <v>5500</v>
+      </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4521,8 +4743,14 @@
       <c r="AI49" s="3">
         <v>4100</v>
       </c>
+      <c r="AJ49" s="3">
+        <v>4100</v>
+      </c>
+      <c r="AK49" s="3">
+        <v>4100</v>
+      </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4622,8 +4850,14 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4723,31 +4957,37 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>0</v>
+      <c r="D52" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E52" s="3">
-        <v>0</v>
+        <v>12600</v>
       </c>
       <c r="F52" s="3">
-        <v>0</v>
+        <v>13200</v>
       </c>
       <c r="G52" s="3">
-        <v>0</v>
+        <v>10400</v>
       </c>
       <c r="H52" s="3">
-        <v>0</v>
+        <v>14800</v>
       </c>
       <c r="I52" s="3">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="J52" s="3">
-        <v>0</v>
+        <v>9500</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -4824,8 +5064,14 @@
       <c r="AI52" s="3">
         <v>0</v>
       </c>
+      <c r="AJ52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4925,109 +5171,121 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1118800</v>
+      </c>
+      <c r="E54" s="3">
+        <v>1082000</v>
+      </c>
+      <c r="F54" s="3">
         <v>1080200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>1122500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>1142200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>1161400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>1147000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>1115300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>1043800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>980800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>982300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>958100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>922600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>901600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>886100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>865900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>833800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>850700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>721600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>696000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>680800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>635600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>626300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>622100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>595200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>586000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>577000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>610900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>539000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>537500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>524500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>513700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>513700</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AK54" s="3">
         <v>518300</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5063,8 +5321,10 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5100,109 +5360,117 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1002800</v>
+      </c>
+      <c r="E57" s="3">
+        <v>966600</v>
+      </c>
+      <c r="F57" s="3">
+        <v>939200</v>
+      </c>
+      <c r="G57" s="3">
+        <v>1009700</v>
+      </c>
+      <c r="H57" s="3">
+        <v>1030800</v>
+      </c>
+      <c r="I57" s="3">
+        <v>1048300</v>
+      </c>
+      <c r="J57" s="3">
+        <v>1015700</v>
+      </c>
+      <c r="K57" s="3">
+        <v>11100</v>
+      </c>
+      <c r="L57" s="3">
+        <v>4600</v>
+      </c>
+      <c r="M57" s="3">
+        <v>4700</v>
+      </c>
+      <c r="N57" s="3">
         <v>4500</v>
       </c>
-      <c r="E57" s="3">
-        <v>4100</v>
-      </c>
-      <c r="F57" s="3">
-        <v>6500</v>
-      </c>
-      <c r="G57" s="3">
-        <v>7100</v>
-      </c>
-      <c r="H57" s="3">
-        <v>4000</v>
-      </c>
-      <c r="I57" s="3">
-        <v>11100</v>
-      </c>
-      <c r="J57" s="3">
-        <v>4600</v>
-      </c>
-      <c r="K57" s="3">
-        <v>4700</v>
-      </c>
-      <c r="L57" s="3">
-        <v>4500</v>
-      </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>6600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>4400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>2900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>2600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>3200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>4200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>5600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>4300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>3300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>3300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>3500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>3000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>2600</v>
-      </c>
-      <c r="Z57" s="3">
-        <v>2200</v>
-      </c>
-      <c r="AA57" s="3">
-        <v>1600</v>
       </c>
       <c r="AB57" s="3">
         <v>2200</v>
       </c>
       <c r="AC57" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AD57" s="3">
+        <v>2200</v>
+      </c>
+      <c r="AE57" s="3">
         <v>2700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>2100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>2000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>2300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>1900</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AJ57" s="3">
         <v>3200</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AK57" s="3">
         <v>8100</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5210,22 +5478,22 @@
         <v>0</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>3900</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -5302,62 +5570,68 @@
       <c r="AI58" s="3">
         <v>0</v>
       </c>
+      <c r="AJ58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E59" s="3">
+      <c r="E59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K59" s="3">
+        <v>1400</v>
+      </c>
+      <c r="L59" s="3">
+        <v>1500</v>
+      </c>
+      <c r="M59" s="3">
         <v>1000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="N59" s="3">
         <v>1100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="O59" s="3">
         <v>1200</v>
-      </c>
-      <c r="H59" s="3">
-        <v>1300</v>
-      </c>
-      <c r="I59" s="3">
-        <v>1400</v>
-      </c>
-      <c r="J59" s="3">
-        <v>1500</v>
-      </c>
-      <c r="K59" s="3">
-        <v>1000</v>
-      </c>
-      <c r="L59" s="3">
-        <v>1100</v>
-      </c>
-      <c r="M59" s="3">
-        <v>1200</v>
-      </c>
-      <c r="N59" s="3">
-        <v>1300</v>
-      </c>
-      <c r="O59" s="3">
-        <v>1400</v>
       </c>
       <c r="P59" s="3">
         <v>1300</v>
       </c>
       <c r="Q59" s="3">
+        <v>1400</v>
+      </c>
+      <c r="R59" s="3">
         <v>1300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
+        <v>1300</v>
+      </c>
+      <c r="T59" s="3">
         <v>900</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>5</v>
       </c>
@@ -5370,11 +5644,11 @@
       <c r="X59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y59" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z59" s="3">
-        <v>0</v>
+      <c r="Y59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AA59" s="3">
         <v>0</v>
@@ -5403,31 +5677,37 @@
       <c r="AI59" s="3">
         <v>0</v>
       </c>
+      <c r="AJ59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK59" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>1008100</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>973700</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>940100</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>1014400</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>1032600</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>1049700</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>1016900</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -5504,8 +5784,14 @@
       <c r="AI60" s="3">
         <v>0</v>
       </c>
+      <c r="AJ60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5513,22 +5799,22 @@
         <v>5900</v>
       </c>
       <c r="E61" s="3">
-        <v>5900</v>
+        <v>6300</v>
       </c>
       <c r="F61" s="3">
-        <v>5900</v>
+        <v>35100</v>
       </c>
       <c r="G61" s="3">
-        <v>5900</v>
+        <v>6400</v>
       </c>
       <c r="H61" s="3">
-        <v>5900</v>
+        <v>6500</v>
       </c>
       <c r="I61" s="3">
-        <v>5900</v>
+        <v>6600</v>
       </c>
       <c r="J61" s="3">
-        <v>5900</v>
+        <v>29700</v>
       </c>
       <c r="K61" s="3">
         <v>5900</v>
@@ -5570,10 +5856,10 @@
         <v>5900</v>
       </c>
       <c r="X61" s="3">
-        <v>0</v>
+        <v>5900</v>
       </c>
       <c r="Y61" s="3">
-        <v>0</v>
+        <v>5900</v>
       </c>
       <c r="Z61" s="3">
         <v>0</v>
@@ -5605,31 +5891,37 @@
       <c r="AI61" s="3">
         <v>0</v>
       </c>
+      <c r="AJ61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
+        <v>4100</v>
       </c>
       <c r="E62" s="3">
-        <v>0</v>
+        <v>4100</v>
       </c>
       <c r="F62" s="3">
-        <v>0</v>
+        <v>7100</v>
       </c>
       <c r="G62" s="3">
-        <v>0</v>
+        <v>4100</v>
       </c>
       <c r="H62" s="3">
-        <v>0</v>
+        <v>9600</v>
       </c>
       <c r="I62" s="3">
-        <v>0</v>
+        <v>10600</v>
       </c>
       <c r="J62" s="3">
-        <v>0</v>
+        <v>7700</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -5706,8 +5998,14 @@
       <c r="AI62" s="3">
         <v>0</v>
       </c>
+      <c r="AJ62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5807,8 +6105,14 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5908,8 +6212,14 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6009,109 +6319,121 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1018100</v>
+      </c>
+      <c r="E66" s="3">
+        <v>984100</v>
+      </c>
+      <c r="F66" s="3">
         <v>982300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>1024800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>1048700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>1067000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>1054400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>1026800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>959400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>896100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>898600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>873800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>840600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>822700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>810600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>790200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>760400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>779400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>653400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>628600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>614300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>570900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>562900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>560600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>534700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>525800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>517300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>551200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>478500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>477000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>465200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>455100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>453400</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AK66" s="3">
         <v>458800</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6147,8 +6469,10 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6248,8 +6572,14 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6349,8 +6679,14 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6450,8 +6786,14 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6551,109 +6893,121 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>70000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>69700</v>
+      </c>
+      <c r="F72" s="3">
         <v>69500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>69000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>67900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>66800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>64700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>61400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>57600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>54500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>50800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>47600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>44800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>41700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>38500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>37500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>35300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>33100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>31600</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X72" s="3">
         <v>28800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>27500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>27000</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB72" s="3">
         <v>25900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>25200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>24400</v>
       </c>
-      <c r="AC72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF72" s="3">
         <v>23600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>23300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>23100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>22800</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AJ72" s="3">
         <v>22200</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AK72" s="3">
         <v>21600</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6753,8 +7107,14 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6854,8 +7214,14 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6955,109 +7321,121 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>100700</v>
+      </c>
+      <c r="E76" s="3">
         <v>97900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
+        <v>97900</v>
+      </c>
+      <c r="G76" s="3">
         <v>97700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>93400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>94400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>92700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>88500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>84400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>84700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>83700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>84300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>82000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>79000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>75500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>75600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>73400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>71200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>68200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>67300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>66500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>64700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>63400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>61500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>60500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>60200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>59700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>59700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>60500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>60400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>59300</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>58600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>60300</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AK76" s="3">
         <v>59500</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7157,215 +7535,233 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>600</v>
+      </c>
+      <c r="E81" s="3">
+        <v>900</v>
+      </c>
+      <c r="F81" s="3">
         <v>1400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>1900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>1800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>3000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>4100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>4600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>4000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>4500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>3900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>3700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>3800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>3900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>3300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>2900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>3000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>2200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>2400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>1800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>2000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>1200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>1400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>1100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>1500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>1500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>1700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>1000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>1200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>1200</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7401,13 +7797,15 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>5</v>
+      <c r="D83" s="3">
+        <v>100</v>
       </c>
       <c r="E83" s="3">
         <v>100</v>
@@ -7416,10 +7814,10 @@
         <v>100</v>
       </c>
       <c r="G83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H83" s="3">
-        <v>-300</v>
+        <v>100</v>
       </c>
       <c r="I83" s="3">
         <v>100</v>
@@ -7431,32 +7829,32 @@
         <v>100</v>
       </c>
       <c r="L83" s="3">
-        <v>-300</v>
+        <v>100</v>
       </c>
       <c r="M83" s="3">
         <v>100</v>
       </c>
       <c r="N83" s="3">
-        <v>300</v>
+        <v>-300</v>
       </c>
       <c r="O83" s="3">
         <v>100</v>
       </c>
       <c r="P83" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q83" s="3">
+        <v>100</v>
+      </c>
+      <c r="R83" s="3">
         <v>-300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>-200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>600</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U83" s="3" t="s">
         <v>5</v>
       </c>
@@ -7466,11 +7864,11 @@
       <c r="W83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X83" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y83" s="3">
-        <v>0</v>
+      <c r="X83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Z83" s="3">
         <v>0</v>
@@ -7493,17 +7891,23 @@
       <c r="AF83" s="3">
         <v>0</v>
       </c>
-      <c r="AG83" s="3" t="s">
-        <v>5</v>
+      <c r="AG83" s="3">
+        <v>0</v>
       </c>
       <c r="AH83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ83" s="3">
         <v>100</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AK83" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7603,8 +8007,14 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7704,8 +8114,14 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7805,8 +8221,14 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7906,8 +8328,14 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8007,8 +8435,14 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -8016,53 +8450,53 @@
         <v>5</v>
       </c>
       <c r="E89" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F89" s="3">
+        <v>700</v>
+      </c>
+      <c r="G89" s="3">
         <v>-900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-2400</v>
       </c>
-      <c r="G89" s="3">
-        <v>900</v>
-      </c>
-      <c r="H89" s="3">
-        <v>-16500</v>
-      </c>
       <c r="I89" s="3">
+        <v>3700</v>
+      </c>
+      <c r="J89" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="K89" s="3">
         <v>7500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-50300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>34000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-29500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>46600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>5400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-1400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>2000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>1700</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>5</v>
       </c>
@@ -8072,11 +8506,11 @@
       <c r="W89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X89" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y89" s="3">
-        <v>0</v>
+      <c r="X89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Z89" s="3">
         <v>0</v>
@@ -8099,17 +8533,23 @@
       <c r="AF89" s="3">
         <v>0</v>
       </c>
-      <c r="AG89" s="3" t="s">
-        <v>5</v>
+      <c r="AG89" s="3">
+        <v>0</v>
       </c>
       <c r="AH89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ89" s="3">
         <v>1900</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AK89" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8145,28 +8585,30 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
       <c r="F91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G91" s="3">
         <v>-100</v>
       </c>
       <c r="H91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J91" s="3">
         <v>-100</v>
@@ -8175,32 +8617,32 @@
         <v>-100</v>
       </c>
       <c r="L91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
         <v>-100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-400</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U91" s="3" t="s">
         <v>5</v>
       </c>
@@ -8210,11 +8652,11 @@
       <c r="W91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y91" s="3">
-        <v>0</v>
+      <c r="X91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Z91" s="3">
         <v>0</v>
@@ -8237,17 +8679,23 @@
       <c r="AF91" s="3">
         <v>0</v>
       </c>
-      <c r="AG91" s="3" t="s">
-        <v>5</v>
+      <c r="AG91" s="3">
+        <v>0</v>
       </c>
       <c r="AH91" s="3">
         <v>0</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AI91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK91" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8347,8 +8795,14 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8448,8 +8902,14 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8457,53 +8917,53 @@
         <v>5</v>
       </c>
       <c r="E94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F94" s="3">
+        <v>21900</v>
+      </c>
+      <c r="G94" s="3">
         <v>-5900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-5200</v>
       </c>
-      <c r="G94" s="3">
-        <v>-9100</v>
-      </c>
-      <c r="H94" s="3">
-        <v>124800</v>
-      </c>
       <c r="I94" s="3">
+        <v>-16700</v>
+      </c>
+      <c r="J94" s="3">
+        <v>7600</v>
+      </c>
+      <c r="K94" s="3">
         <v>-33000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-59300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-8000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>102600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-74000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-45500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>161400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-25200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-143500</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U94" s="3" t="s">
         <v>5</v>
       </c>
@@ -8513,11 +8973,11 @@
       <c r="W94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y94" s="3">
-        <v>0</v>
+      <c r="X94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Z94" s="3">
         <v>0</v>
@@ -8540,17 +9000,23 @@
       <c r="AF94" s="3">
         <v>0</v>
       </c>
-      <c r="AG94" s="3" t="s">
-        <v>5</v>
+      <c r="AG94" s="3">
+        <v>0</v>
       </c>
       <c r="AH94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ94" s="3">
         <v>-2900</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AK94" s="3">
         <v>10700</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8586,62 +9052,64 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E96" s="3">
-        <v>-800</v>
+        <v>800</v>
       </c>
       <c r="F96" s="3">
-        <v>-800</v>
+        <v>800</v>
       </c>
       <c r="G96" s="3">
-        <v>-1600</v>
+        <v>800</v>
       </c>
       <c r="H96" s="3">
-        <v>2400</v>
+        <v>800</v>
       </c>
       <c r="I96" s="3">
-        <v>-800</v>
+        <v>800</v>
       </c>
       <c r="J96" s="3">
-        <v>-800</v>
+        <v>800</v>
       </c>
       <c r="K96" s="3">
         <v>-800</v>
       </c>
       <c r="L96" s="3">
-        <v>2200</v>
+        <v>-800</v>
       </c>
       <c r="M96" s="3">
         <v>-800</v>
       </c>
       <c r="N96" s="3">
+        <v>2200</v>
+      </c>
+      <c r="O96" s="3">
+        <v>-800</v>
+      </c>
+      <c r="P96" s="3">
         <v>-2200</v>
-      </c>
-      <c r="O96" s="3">
-        <v>-700</v>
-      </c>
-      <c r="P96" s="3">
-        <v>2200</v>
       </c>
       <c r="Q96" s="3">
         <v>-700</v>
       </c>
       <c r="R96" s="3">
+        <v>2200</v>
+      </c>
+      <c r="S96" s="3">
+        <v>-700</v>
+      </c>
+      <c r="T96" s="3">
         <v>-2200</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
         <v>0</v>
       </c>
@@ -8682,13 +9150,19 @@
         <v>0</v>
       </c>
       <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-600</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AK96" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8788,8 +9262,14 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8889,8 +9369,14 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8990,8 +9476,14 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8999,53 +9491,53 @@
         <v>5</v>
       </c>
       <c r="E100" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F100" s="3">
+        <v>-42700</v>
+      </c>
+      <c r="G100" s="3">
         <v>-22000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-18300</v>
       </c>
-      <c r="G100" s="3">
-        <v>43000</v>
-      </c>
-      <c r="H100" s="3">
-        <v>-106200</v>
-      </c>
       <c r="I100" s="3">
+        <v>8800</v>
+      </c>
+      <c r="J100" s="3">
+        <v>34200</v>
+      </c>
+      <c r="K100" s="3">
         <v>60200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>63300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-2700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-57800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>30300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>47100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>10900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-137100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>29700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>127700</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>5</v>
       </c>
@@ -9055,11 +9547,11 @@
       <c r="W100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y100" s="3">
-        <v>0</v>
+      <c r="X100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Z100" s="3">
         <v>0</v>
@@ -9082,40 +9574,46 @@
       <c r="AF100" s="3">
         <v>0</v>
       </c>
-      <c r="AG100" s="3" t="s">
-        <v>5</v>
+      <c r="AG100" s="3">
+        <v>0</v>
       </c>
       <c r="AH100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ100" s="3">
         <v>-1100</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AK100" s="3">
         <v>-10700</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -9192,62 +9690,68 @@
       <c r="AI101" s="3">
         <v>0</v>
       </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3" t="s">
-        <v>5</v>
+      <c r="D102" s="3">
+        <v>0</v>
       </c>
       <c r="E102" s="3">
+        <v>2400</v>
+      </c>
+      <c r="F102" s="3">
+        <v>-20100</v>
+      </c>
+      <c r="G102" s="3">
         <v>-28800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-25800</v>
       </c>
-      <c r="G102" s="3">
-        <v>34800</v>
-      </c>
-      <c r="H102" s="3">
-        <v>2100</v>
-      </c>
       <c r="I102" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="J102" s="3">
+        <v>39000</v>
+      </c>
+      <c r="K102" s="3">
         <v>34700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>6200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-29300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>15300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>2900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>6900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>9200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>23600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>6600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-14000</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U102" s="3" t="s">
         <v>5</v>
       </c>
@@ -9257,11 +9761,11 @@
       <c r="W102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X102" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y102" s="3">
-        <v>0</v>
+      <c r="X102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y102" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Z102" s="3">
         <v>0</v>
@@ -9284,13 +9788,19 @@
       <c r="AF102" s="3">
         <v>0</v>
       </c>
-      <c r="AG102" s="3" t="s">
-        <v>5</v>
+      <c r="AG102" s="3">
+        <v>0</v>
       </c>
       <c r="AH102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ102" s="3">
         <v>-2100</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AK102" s="3">
         <v>700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SSBI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SSBI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="92">
   <si>
     <t>SSBI</t>
   </si>
@@ -656,266 +656,272 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E8" s="3">
         <v>7000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>7900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>8400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>8200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>9400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>11100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>11600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>14200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>12500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>11300</v>
-      </c>
-      <c r="N8" s="3">
-        <v>10900</v>
       </c>
       <c r="O8" s="3">
         <v>10900</v>
       </c>
       <c r="P8" s="3">
+        <v>10900</v>
+      </c>
+      <c r="Q8" s="3">
         <v>10600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>10100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>10400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>10100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>9200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>8800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>8300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>8000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>7600</v>
-      </c>
-      <c r="Y8" s="3">
-        <v>7200</v>
       </c>
       <c r="Z8" s="3">
         <v>7200</v>
       </c>
       <c r="AA8" s="3">
+        <v>7200</v>
+      </c>
+      <c r="AB8" s="3">
         <v>6800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>6600</v>
-      </c>
-      <c r="AC8" s="3">
-        <v>6100</v>
       </c>
       <c r="AD8" s="3">
         <v>6100</v>
       </c>
       <c r="AE8" s="3">
+        <v>6100</v>
+      </c>
+      <c r="AF8" s="3">
         <v>5700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>5200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>5000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>4800</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>5000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>4800</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>5100</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1021,35 +1027,38 @@
       <c r="AK9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E10" s="3">
         <v>7000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>7900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>8400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>8200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>9400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>11100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>11600</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1128,8 +1137,11 @@
       <c r="AK10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1167,8 +1179,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1274,8 +1287,11 @@
       <c r="AK12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1381,13 +1397,16 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>5</v>
+      <c r="D14" s="3">
+        <v>4100</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>5</v>
@@ -1407,8 +1426,8 @@
       <c r="J14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1488,8 +1507,11 @@
       <c r="AK14" s="3">
         <v>0</v>
       </c>
+      <c r="AL14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1515,7 +1537,7 @@
         <v>100</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
@@ -1595,8 +1617,11 @@
       <c r="AK15" s="3">
         <v>0</v>
       </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1631,106 +1656,107 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E17" s="3">
         <v>6200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>6600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>6400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>5500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>6900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>6800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>5800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>400</v>
-      </c>
-      <c r="AI17" s="3">
-        <v>300</v>
       </c>
       <c r="AJ17" s="3">
         <v>300</v>
@@ -1738,115 +1764,121 @@
       <c r="AK17" s="3">
         <v>300</v>
       </c>
+      <c r="AL17" s="3">
+        <v>300</v>
+      </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E18" s="3">
         <v>800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>2700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>2500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>4300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>5800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>10600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>10200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>9300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>9800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>8900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>9600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>9000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>8800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>8300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>7300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>6700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>5900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>6000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>5500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>5300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>5500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>5400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>5500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>5100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>5200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>4700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>4400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>4500</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>4400</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>4700</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>4500</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1884,8 +1916,9 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1910,71 +1943,71 @@
       <c r="J20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L20" s="3">
         <v>-4300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-4400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-2900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-4400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-3700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-4200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-3500</v>
-      </c>
-      <c r="R20" s="3">
-        <v>-4100</v>
       </c>
       <c r="S20" s="3">
         <v>-4100</v>
       </c>
       <c r="T20" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="U20" s="3">
         <v>-3100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-3500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-2500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-3300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-2700</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>-3700</v>
       </c>
       <c r="Z20" s="3">
         <v>-3700</v>
       </c>
       <c r="AA20" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="AB20" s="3">
         <v>-3800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-3500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-3000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-2800</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-3400</v>
-      </c>
-      <c r="AF20" s="3">
-        <v>-2900</v>
       </c>
       <c r="AG20" s="3">
         <v>-2900</v>
@@ -1983,73 +2016,76 @@
         <v>-2900</v>
       </c>
       <c r="AI20" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="AJ20" s="3">
         <v>-2700</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-2500</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-2700</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="E21" s="3">
         <v>900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>2800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>2600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>4400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>5900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>6400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>5800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>6500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>5100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>5300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>5700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>5600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>4400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>4000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>4800</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>5</v>
       </c>
@@ -2092,14 +2128,17 @@
       <c r="AI21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AJ21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK21" s="3">
         <v>2100</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2124,8 +2163,8 @@
       <c r="J22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -2205,153 +2244,159 @@
       <c r="AK22" s="3">
         <v>0</v>
       </c>
+      <c r="AL22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="E23" s="3">
         <v>800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>4300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>5800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>6300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>5700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>6400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>5400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>5200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>5400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>5500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>4700</v>
-      </c>
-      <c r="S23" s="3">
-        <v>4200</v>
       </c>
       <c r="T23" s="3">
         <v>4200</v>
       </c>
       <c r="U23" s="3">
+        <v>4200</v>
+      </c>
+      <c r="V23" s="3">
         <v>3200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>3400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>2600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>2900</v>
-      </c>
-      <c r="Y23" s="3">
-        <v>1700</v>
       </c>
       <c r="Z23" s="3">
         <v>1700</v>
       </c>
       <c r="AA23" s="3">
+        <v>1700</v>
+      </c>
+      <c r="AB23" s="3">
         <v>1600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>2000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>2100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>2400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1500</v>
-      </c>
-      <c r="AI23" s="3">
-        <v>2000</v>
       </c>
       <c r="AJ23" s="3">
         <v>2000</v>
       </c>
       <c r="AK23" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AL23" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E24" s="3">
         <v>200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1700</v>
-      </c>
-      <c r="K24" s="3">
-        <v>1800</v>
       </c>
       <c r="L24" s="3">
         <v>1800</v>
       </c>
       <c r="M24" s="3">
+        <v>1800</v>
+      </c>
+      <c r="N24" s="3">
         <v>1900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1500</v>
-      </c>
-      <c r="O24" s="3">
-        <v>1600</v>
       </c>
       <c r="P24" s="3">
         <v>1600</v>
@@ -2360,67 +2405,70 @@
         <v>1600</v>
       </c>
       <c r="R24" s="3">
+        <v>1600</v>
+      </c>
+      <c r="S24" s="3">
         <v>1400</v>
-      </c>
-      <c r="S24" s="3">
-        <v>1200</v>
       </c>
       <c r="T24" s="3">
         <v>1200</v>
       </c>
       <c r="U24" s="3">
+        <v>1200</v>
+      </c>
+      <c r="V24" s="3">
         <v>900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1000</v>
-      </c>
-      <c r="W24" s="3">
-        <v>800</v>
       </c>
       <c r="X24" s="3">
         <v>800</v>
       </c>
       <c r="Y24" s="3">
+        <v>800</v>
+      </c>
+      <c r="Z24" s="3">
         <v>500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>300</v>
-      </c>
-      <c r="AA24" s="3">
-        <v>500</v>
       </c>
       <c r="AB24" s="3">
         <v>500</v>
       </c>
       <c r="AC24" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AD24" s="3">
         <v>600</v>
       </c>
       <c r="AE24" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AF24" s="3">
         <v>500</v>
       </c>
       <c r="AG24" s="3">
+        <v>500</v>
+      </c>
+      <c r="AH24" s="3">
         <v>700</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>600</v>
-      </c>
-      <c r="AI24" s="3">
-        <v>800</v>
       </c>
       <c r="AJ24" s="3">
         <v>800</v>
       </c>
       <c r="AK24" s="3">
+        <v>800</v>
+      </c>
+      <c r="AL24" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2526,222 +2574,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="E26" s="3">
         <v>600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>3000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>4100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>4600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>4000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>4500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>3900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>3700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>3800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>3900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>3300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>2900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>3000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>2200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>2400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>2000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1100</v>
-      </c>
-      <c r="AB26" s="3">
-        <v>1500</v>
       </c>
       <c r="AC26" s="3">
         <v>1500</v>
       </c>
       <c r="AD26" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AE26" s="3">
         <v>1700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1000</v>
-      </c>
-      <c r="AG26" s="3">
-        <v>900</v>
       </c>
       <c r="AH26" s="3">
         <v>900</v>
       </c>
       <c r="AI26" s="3">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="AJ26" s="3">
         <v>1200</v>
       </c>
       <c r="AK26" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AL26" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="E27" s="3">
         <v>600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>3000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>4100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>4600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>4000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>4500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>3900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>3700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>3800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>3900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>3300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>3000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>2200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>2400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>2000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1100</v>
-      </c>
-      <c r="AB27" s="3">
-        <v>1500</v>
       </c>
       <c r="AC27" s="3">
         <v>1500</v>
       </c>
       <c r="AD27" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AE27" s="3">
         <v>1700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1000</v>
-      </c>
-      <c r="AG27" s="3">
-        <v>900</v>
       </c>
       <c r="AH27" s="3">
         <v>900</v>
       </c>
       <c r="AI27" s="3">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="AJ27" s="3">
         <v>1200</v>
       </c>
       <c r="AK27" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AL27" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2847,8 +2904,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2912,8 +2972,8 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>5</v>
+      <c r="X29" s="3">
+        <v>0</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>5</v>
@@ -2933,12 +2993,12 @@
       <c r="AD29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AE29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF29" s="3">
         <v>-300</v>
       </c>
-      <c r="AF29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AG29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2954,8 +3014,11 @@
       <c r="AK29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3061,8 +3124,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3168,8 +3234,11 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3194,71 +3263,71 @@
       <c r="J32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L32" s="3">
         <v>4300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>4400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>2900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>4400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>3700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>4200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>3500</v>
-      </c>
-      <c r="R32" s="3">
-        <v>4100</v>
       </c>
       <c r="S32" s="3">
         <v>4100</v>
       </c>
       <c r="T32" s="3">
+        <v>4100</v>
+      </c>
+      <c r="U32" s="3">
         <v>3100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>3500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>2500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>3300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>2700</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>3700</v>
       </c>
       <c r="Z32" s="3">
         <v>3700</v>
       </c>
       <c r="AA32" s="3">
+        <v>3700</v>
+      </c>
+      <c r="AB32" s="3">
         <v>3800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>3500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>3000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>2800</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>3400</v>
-      </c>
-      <c r="AF32" s="3">
-        <v>2900</v>
       </c>
       <c r="AG32" s="3">
         <v>2900</v>
@@ -3267,123 +3336,129 @@
         <v>2900</v>
       </c>
       <c r="AI32" s="3">
+        <v>2900</v>
+      </c>
+      <c r="AJ32" s="3">
         <v>2700</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>2500</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="E33" s="3">
         <v>600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>3000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>4100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>4600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>4000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>4500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>3900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>3700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>3800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>3900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>3300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>3000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>2200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>2400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>2000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1100</v>
-      </c>
-      <c r="AB33" s="3">
-        <v>1500</v>
       </c>
       <c r="AC33" s="3">
         <v>1500</v>
       </c>
       <c r="AD33" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AE33" s="3">
         <v>1700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1000</v>
-      </c>
-      <c r="AG33" s="3">
-        <v>900</v>
       </c>
       <c r="AH33" s="3">
         <v>900</v>
       </c>
       <c r="AI33" s="3">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="AJ33" s="3">
         <v>1200</v>
       </c>
       <c r="AK33" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AL33" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3489,227 +3564,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="E35" s="3">
         <v>600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>3000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>4100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>4600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>4000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>4500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>3900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>3700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>3800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>3900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>3300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>3000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>2200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>2400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>2000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1100</v>
-      </c>
-      <c r="AB35" s="3">
-        <v>1500</v>
       </c>
       <c r="AC35" s="3">
         <v>1500</v>
       </c>
       <c r="AD35" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AE35" s="3">
         <v>1700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1000</v>
-      </c>
-      <c r="AG35" s="3">
-        <v>900</v>
       </c>
       <c r="AH35" s="3">
         <v>900</v>
       </c>
       <c r="AI35" s="3">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="AJ35" s="3">
         <v>1200</v>
       </c>
       <c r="AK35" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AL35" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3747,8 +3831,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3786,115 +3871,119 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>51400</v>
+      </c>
+      <c r="E41" s="3">
         <v>80900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>40100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>37700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>57800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>86600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>112400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>116600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>77600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>42800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>36600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>65900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>40700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>37800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>56100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>46900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>30800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>24300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>68000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>36500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>38300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>37000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>12100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>18600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>21700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>20900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>23700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>18900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>68800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>20400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>20200</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>20800</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>24200</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>20100</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>21800</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3920,19 +4009,19 @@
         <v>0</v>
       </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>13600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>13700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>13800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>13500</v>
-      </c>
-      <c r="O42" s="3">
-        <v>4300</v>
       </c>
       <c r="P42" s="3">
         <v>4300</v>
@@ -3941,7 +4030,7 @@
         <v>4300</v>
       </c>
       <c r="R42" s="3">
-        <v>3400</v>
+        <v>4300</v>
       </c>
       <c r="S42" s="3">
         <v>3400</v>
@@ -3953,7 +4042,7 @@
         <v>3400</v>
       </c>
       <c r="V42" s="3">
-        <v>3300</v>
+        <v>3400</v>
       </c>
       <c r="W42" s="3">
         <v>3300</v>
@@ -3965,7 +4054,7 @@
         <v>3300</v>
       </c>
       <c r="Z42" s="3">
-        <v>3100</v>
+        <v>3300</v>
       </c>
       <c r="AA42" s="3">
         <v>3100</v>
@@ -3977,7 +4066,7 @@
         <v>3100</v>
       </c>
       <c r="AD42" s="3">
-        <v>5100</v>
+        <v>3100</v>
       </c>
       <c r="AE42" s="3">
         <v>5100</v>
@@ -3986,22 +4075,25 @@
         <v>5100</v>
       </c>
       <c r="AG42" s="3">
+        <v>5100</v>
+      </c>
+      <c r="AH42" s="3">
         <v>4800</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>5200</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>5300</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>4900</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -4026,8 +4118,8 @@
       <c r="J43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
@@ -4107,8 +4199,11 @@
       <c r="AK43" s="3">
         <v>0</v>
       </c>
+      <c r="AL43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4118,8 +4213,8 @@
       <c r="E44" s="3">
         <v>5100</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>5</v>
+      <c r="F44" s="3">
+        <v>5100</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>5</v>
@@ -4133,8 +4228,8 @@
       <c r="J44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -4214,35 +4309,38 @@
       <c r="AK44" s="3">
         <v>0</v>
       </c>
+      <c r="AL44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>19300</v>
+      </c>
+      <c r="E45" s="3">
         <v>16200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>3600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3700</v>
-      </c>
-      <c r="H45" s="3">
-        <v>3800</v>
       </c>
       <c r="I45" s="3">
         <v>3800</v>
       </c>
       <c r="J45" s="3">
+        <v>3800</v>
+      </c>
+      <c r="K45" s="3">
         <v>4100</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
       <c r="L45" s="3">
         <v>0</v>
       </c>
@@ -4321,35 +4419,38 @@
       <c r="AK45" s="3">
         <v>0</v>
       </c>
+      <c r="AL45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>75800</v>
+      </c>
+      <c r="E46" s="3">
         <v>102300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>48900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>41600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>61500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>90400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>116200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>120600</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -4428,35 +4529,38 @@
       <c r="AK46" s="3">
         <v>0</v>
       </c>
+      <c r="AL46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>81600</v>
+      </c>
+      <c r="E47" s="3">
         <v>89800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>96900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>97500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>98500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>94200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>97700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>98400</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
       <c r="L47" s="3">
         <v>0</v>
       </c>
@@ -4535,67 +4639,70 @@
       <c r="AK47" s="3">
         <v>0</v>
       </c>
+      <c r="AL47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E48" s="3">
         <v>5300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>6000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>6100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>6300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>6400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6600</v>
-      </c>
-      <c r="J48" s="3">
-        <v>6800</v>
       </c>
       <c r="K48" s="3">
         <v>6800</v>
       </c>
       <c r="L48" s="3">
+        <v>6800</v>
+      </c>
+      <c r="M48" s="3">
         <v>7000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>6500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>6700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>6900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>7000</v>
-      </c>
-      <c r="Q48" s="3">
-        <v>7200</v>
       </c>
       <c r="R48" s="3">
         <v>7200</v>
       </c>
       <c r="S48" s="3">
+        <v>7200</v>
+      </c>
+      <c r="T48" s="3">
         <v>7300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>7000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>6200</v>
-      </c>
-      <c r="V48" s="3">
-        <v>6300</v>
       </c>
       <c r="W48" s="3">
         <v>6300</v>
@@ -4607,48 +4714,51 @@
         <v>6300</v>
       </c>
       <c r="Z48" s="3">
+        <v>6300</v>
+      </c>
+      <c r="AA48" s="3">
         <v>6400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>5800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>5300</v>
-      </c>
-      <c r="AC48" s="3">
-        <v>5200</v>
       </c>
       <c r="AD48" s="3">
         <v>5200</v>
       </c>
       <c r="AE48" s="3">
-        <v>5300</v>
+        <v>5200</v>
       </c>
       <c r="AF48" s="3">
         <v>5300</v>
       </c>
       <c r="AG48" s="3">
+        <v>5300</v>
+      </c>
+      <c r="AH48" s="3">
         <v>5400</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>5500</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>5400</v>
-      </c>
-      <c r="AJ48" s="3">
-        <v>5500</v>
       </c>
       <c r="AK48" s="3">
         <v>5500</v>
       </c>
+      <c r="AL48" s="3">
+        <v>5500</v>
+      </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>4100</v>
+        <v>0</v>
       </c>
       <c r="E49" s="3">
         <v>4100</v>
@@ -4749,8 +4859,11 @@
       <c r="AK49" s="3">
         <v>4100</v>
       </c>
+      <c r="AL49" s="3">
+        <v>4100</v>
+      </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4856,8 +4969,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4963,35 +5079,38 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E52" s="3">
+      <c r="E52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F52" s="3">
         <v>12600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>13200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>10400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>14800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>12000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>9500</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
-      </c>
       <c r="L52" s="3">
         <v>0</v>
       </c>
@@ -5070,8 +5189,11 @@
       <c r="AK52" s="3">
         <v>0</v>
       </c>
+      <c r="AL52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5177,115 +5299,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1067600</v>
+      </c>
+      <c r="E54" s="3">
         <v>1118800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1082000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1080200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1122500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1142200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1161400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1147000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1115300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1043800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>980800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>982300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>958100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>922600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>901600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>886100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>865900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>833800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>850700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>721600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>696000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>680800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>635600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>626300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>622100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>595200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>586000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>577000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>610900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>539000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>537500</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>524500</v>
-      </c>
-      <c r="AI54" s="3">
-        <v>513700</v>
       </c>
       <c r="AJ54" s="3">
         <v>513700</v>
       </c>
       <c r="AK54" s="3">
+        <v>513700</v>
+      </c>
+      <c r="AL54" s="3">
         <v>518300</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5323,8 +5451,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5362,115 +5491,119 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>962600</v>
+      </c>
+      <c r="E57" s="3">
         <v>1002800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>966600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>939200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1009700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1030800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1048300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1015700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>11100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>4500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>6600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>4200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>5600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>4300</v>
-      </c>
-      <c r="W57" s="3">
-        <v>3300</v>
       </c>
       <c r="X57" s="3">
         <v>3300</v>
       </c>
       <c r="Y57" s="3">
+        <v>3300</v>
+      </c>
+      <c r="Z57" s="3">
         <v>3500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>3000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>2100</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>2000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>2300</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1900</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>3200</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>8100</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5478,13 +5611,13 @@
         <v>0</v>
       </c>
       <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
         <v>3900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>400</v>
-      </c>
-      <c r="G58" s="3">
-        <v>500</v>
       </c>
       <c r="H58" s="3">
         <v>500</v>
@@ -5496,7 +5629,7 @@
         <v>500</v>
       </c>
       <c r="K58" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="L58" s="3">
         <v>0</v>
@@ -5576,8 +5709,11 @@
       <c r="AK58" s="3">
         <v>0</v>
       </c>
+      <c r="AL58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5602,39 +5738,39 @@
       <c r="J59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L59" s="3">
         <v>1400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1400</v>
-      </c>
-      <c r="R59" s="3">
-        <v>1300</v>
       </c>
       <c r="S59" s="3">
         <v>1300</v>
       </c>
       <c r="T59" s="3">
+        <v>1300</v>
+      </c>
+      <c r="U59" s="3">
         <v>900</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V59" s="3" t="s">
         <v>5</v>
       </c>
@@ -5650,8 +5786,8 @@
       <c r="Z59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA59" s="3">
-        <v>0</v>
+      <c r="AA59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AB59" s="3">
         <v>0</v>
@@ -5683,35 +5819,38 @@
       <c r="AK59" s="3">
         <v>0</v>
       </c>
+      <c r="AL59" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>968800</v>
+      </c>
+      <c r="E60" s="3">
         <v>1008100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>973700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>940100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1014400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1032600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1049700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1016900</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
@@ -5790,8 +5929,11 @@
       <c r="AK60" s="3">
         <v>0</v>
       </c>
+      <c r="AL60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5799,25 +5941,25 @@
         <v>5900</v>
       </c>
       <c r="E61" s="3">
+        <v>5900</v>
+      </c>
+      <c r="F61" s="3">
         <v>6300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>35100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>6400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>6500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>6600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>29700</v>
-      </c>
-      <c r="K61" s="3">
-        <v>5900</v>
       </c>
       <c r="L61" s="3">
         <v>5900</v>
@@ -5862,7 +6004,7 @@
         <v>5900</v>
       </c>
       <c r="Z61" s="3">
-        <v>0</v>
+        <v>5900</v>
       </c>
       <c r="AA61" s="3">
         <v>0</v>
@@ -5897,35 +6039,38 @@
       <c r="AK61" s="3">
         <v>0</v>
       </c>
+      <c r="AL61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>4100</v>
+        <v>600</v>
       </c>
       <c r="E62" s="3">
         <v>4100</v>
       </c>
       <c r="F62" s="3">
+        <v>4100</v>
+      </c>
+      <c r="G62" s="3">
         <v>7100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>4100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>9600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>10600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>7700</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
-      </c>
       <c r="L62" s="3">
         <v>0</v>
       </c>
@@ -6004,8 +6149,11 @@
       <c r="AK62" s="3">
         <v>0</v>
       </c>
+      <c r="AL62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6111,8 +6259,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6218,8 +6369,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6325,115 +6479,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>975300</v>
+      </c>
+      <c r="E66" s="3">
         <v>1018100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>984100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>982300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1024800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1048700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1067000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1054400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1026800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>959400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>896100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>898600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>873800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>840600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>822700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>810600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>790200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>760400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>779400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>653400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>628600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>614300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>570900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>562900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>560600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>534700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>525800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>517300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>551200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>478500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>477000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>465200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>455100</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>453400</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>458800</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6471,8 +6631,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6578,8 +6739,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6685,8 +6849,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6792,8 +6959,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6899,115 +7069,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E72" s="3">
         <v>70000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>69700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>69500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>69000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>67900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>66800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>64700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>61400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>57600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>54500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>50800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>47600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>44800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>41700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>38500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>37500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>35300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>33100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>31600</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X72" s="3">
+      <c r="X72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y72" s="3">
         <v>28800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>27500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>27000</v>
       </c>
-      <c r="AA72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB72" s="3">
+      <c r="AB72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC72" s="3">
         <v>25900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>25200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>24400</v>
       </c>
-      <c r="AE72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF72" s="3">
+      <c r="AF72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG72" s="3">
         <v>23600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>23300</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>23100</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>22800</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>22200</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>21600</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7113,8 +7289,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7220,8 +7399,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7327,115 +7509,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>92300</v>
+      </c>
+      <c r="E76" s="3">
         <v>100700</v>
-      </c>
-      <c r="E76" s="3">
-        <v>97900</v>
       </c>
       <c r="F76" s="3">
         <v>97900</v>
       </c>
       <c r="G76" s="3">
+        <v>97900</v>
+      </c>
+      <c r="H76" s="3">
         <v>97700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>93400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>94400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>92700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>88500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>84400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>84700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>83700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>84300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>82000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>79000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>75500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>75600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>73400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>71200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>68200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>67300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>66500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>64700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>63400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>61500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>60500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>60200</v>
-      </c>
-      <c r="AD76" s="3">
-        <v>59700</v>
       </c>
       <c r="AE76" s="3">
         <v>59700</v>
       </c>
       <c r="AF76" s="3">
+        <v>59700</v>
+      </c>
+      <c r="AG76" s="3">
         <v>60500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>60400</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>59300</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>58600</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>60300</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>59500</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7541,227 +7729,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="E81" s="3">
         <v>600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>3000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>4100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>4600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>4000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>4500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>3900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>3700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>3800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>3900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>3300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>3000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>2200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>2400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>2000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1100</v>
-      </c>
-      <c r="AB81" s="3">
-        <v>1500</v>
       </c>
       <c r="AC81" s="3">
         <v>1500</v>
       </c>
       <c r="AD81" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AE81" s="3">
         <v>1700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1000</v>
-      </c>
-      <c r="AG81" s="3">
-        <v>900</v>
       </c>
       <c r="AH81" s="3">
         <v>900</v>
       </c>
       <c r="AI81" s="3">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="AJ81" s="3">
         <v>1200</v>
       </c>
       <c r="AK81" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AL81" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7799,8 +7996,9 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7835,29 +8033,29 @@
         <v>100</v>
       </c>
       <c r="N83" s="3">
+        <v>100</v>
+      </c>
+      <c r="O83" s="3">
         <v>-300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>-300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>-200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>600</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V83" s="3" t="s">
         <v>5</v>
       </c>
@@ -7870,8 +8068,8 @@
       <c r="Y83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z83" s="3">
-        <v>0</v>
+      <c r="Z83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AA83" s="3">
         <v>0</v>
@@ -7897,17 +8095,20 @@
       <c r="AH83" s="3">
         <v>0</v>
       </c>
-      <c r="AI83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ83" s="3">
-        <v>100</v>
+      <c r="AI83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AK83" s="3">
         <v>100</v>
       </c>
+      <c r="AL83" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8013,8 +8214,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8120,8 +8324,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8227,8 +8434,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8334,8 +8544,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8441,65 +8654,68 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E89" s="3">
+      <c r="E89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F89" s="3">
         <v>1100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-2400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>3700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-2800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>7500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-50300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>34000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-29500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>46600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>5400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-1400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>2000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1700</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>5</v>
       </c>
@@ -8512,8 +8728,8 @@
       <c r="Y89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z89" s="3">
-        <v>0</v>
+      <c r="Z89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AA89" s="3">
         <v>0</v>
@@ -8539,17 +8755,20 @@
       <c r="AH89" s="3">
         <v>0</v>
       </c>
-      <c r="AI89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ89" s="3">
+      <c r="AI89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK89" s="3">
         <v>1900</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8587,16 +8806,17 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E91" s="3">
-        <v>-100</v>
+      <c r="E91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F91" s="3">
         <v>-100</v>
@@ -8605,13 +8825,13 @@
         <v>-100</v>
       </c>
       <c r="H91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I91" s="3">
         <v>0</v>
       </c>
       <c r="J91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K91" s="3">
         <v>-100</v>
@@ -8623,29 +8843,29 @@
         <v>-100</v>
       </c>
       <c r="N91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O91" s="3">
         <v>0</v>
       </c>
       <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-400</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V91" s="3" t="s">
         <v>5</v>
       </c>
@@ -8658,8 +8878,8 @@
       <c r="Y91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z91" s="3">
-        <v>0</v>
+      <c r="Z91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AA91" s="3">
         <v>0</v>
@@ -8685,17 +8905,20 @@
       <c r="AH91" s="3">
         <v>0</v>
       </c>
-      <c r="AI91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ91" s="3">
-        <v>0</v>
+      <c r="AI91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AK91" s="3">
         <v>0</v>
       </c>
+      <c r="AL91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8801,8 +9024,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8908,65 +9134,68 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E94" s="3">
+      <c r="E94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F94" s="3">
         <v>-200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>21900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-5900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-5200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-16700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>7600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-33000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-59300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-8000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>102600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-74000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-45500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>161400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-25200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-143500</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V94" s="3" t="s">
         <v>5</v>
       </c>
@@ -8979,8 +9208,8 @@
       <c r="Y94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z94" s="3">
-        <v>0</v>
+      <c r="Z94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AA94" s="3">
         <v>0</v>
@@ -9006,17 +9235,20 @@
       <c r="AH94" s="3">
         <v>0</v>
       </c>
-      <c r="AI94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ94" s="3">
+      <c r="AI94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK94" s="3">
         <v>-2900</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>10700</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9054,16 +9286,17 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E96" s="3">
-        <v>800</v>
+      <c r="E96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F96" s="3">
         <v>800</v>
@@ -9081,7 +9314,7 @@
         <v>800</v>
       </c>
       <c r="K96" s="3">
-        <v>-800</v>
+        <v>800</v>
       </c>
       <c r="L96" s="3">
         <v>-800</v>
@@ -9090,29 +9323,29 @@
         <v>-800</v>
       </c>
       <c r="N96" s="3">
+        <v>-800</v>
+      </c>
+      <c r="O96" s="3">
         <v>2200</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-800</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-700</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>2200</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-700</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-2200</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
       <c r="V96" s="3">
         <v>0</v>
       </c>
@@ -9156,13 +9389,16 @@
         <v>0</v>
       </c>
       <c r="AJ96" s="3">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="AK96" s="3">
         <v>-600</v>
       </c>
+      <c r="AL96" s="3">
+        <v>-600</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9268,8 +9504,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9375,8 +9614,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9482,65 +9724,68 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E100" s="3">
+      <c r="E100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F100" s="3">
         <v>1500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-42700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-22000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-18300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>8800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>34200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>60200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>63300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-57800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>30300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>47100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>10900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-137100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>29700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>127700</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V100" s="3" t="s">
         <v>5</v>
       </c>
@@ -9553,8 +9798,8 @@
       <c r="Y100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z100" s="3">
-        <v>0</v>
+      <c r="Z100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AA100" s="3">
         <v>0</v>
@@ -9580,17 +9825,20 @@
       <c r="AH100" s="3">
         <v>0</v>
       </c>
-      <c r="AI100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ100" s="3">
+      <c r="AI100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK100" s="3">
         <v>-1100</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-10700</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9615,8 +9863,8 @@
       <c r="J101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -9696,8 +9944,11 @@
       <c r="AK101" s="3">
         <v>0</v>
       </c>
+      <c r="AL101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -9705,56 +9956,56 @@
         <v>0</v>
       </c>
       <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
         <v>2400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-20100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-28800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-25800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-4200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>39000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>34700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>6200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-29300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>15300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>2900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>6900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>9200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>23600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>6600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-14000</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V102" s="3" t="s">
         <v>5</v>
       </c>
@@ -9767,8 +10018,8 @@
       <c r="Y102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z102" s="3">
-        <v>0</v>
+      <c r="Z102" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AA102" s="3">
         <v>0</v>
@@ -9794,13 +10045,16 @@
       <c r="AH102" s="3">
         <v>0</v>
       </c>
-      <c r="AI102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ102" s="3">
+      <c r="AI102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK102" s="3">
         <v>-2100</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SSBI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SSBI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="92">
   <si>
     <t>SSBI</t>
   </si>
@@ -656,272 +656,279 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>2400</v>
+        <v>9400</v>
       </c>
       <c r="E8" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F8" s="3">
         <v>7000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>7900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>8400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>8200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>9400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>11100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>11600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>14200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>12500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>11300</v>
-      </c>
-      <c r="O8" s="3">
-        <v>10900</v>
       </c>
       <c r="P8" s="3">
         <v>10900</v>
       </c>
       <c r="Q8" s="3">
+        <v>10900</v>
+      </c>
+      <c r="R8" s="3">
         <v>10600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>10100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>10400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>10100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>9200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>8800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>8300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>8000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>7600</v>
-      </c>
-      <c r="Z8" s="3">
-        <v>7200</v>
       </c>
       <c r="AA8" s="3">
         <v>7200</v>
       </c>
       <c r="AB8" s="3">
+        <v>7200</v>
+      </c>
+      <c r="AC8" s="3">
         <v>6800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>6600</v>
-      </c>
-      <c r="AD8" s="3">
-        <v>6100</v>
       </c>
       <c r="AE8" s="3">
         <v>6100</v>
       </c>
       <c r="AF8" s="3">
+        <v>6100</v>
+      </c>
+      <c r="AG8" s="3">
         <v>5700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>5200</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>5000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>4800</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>5000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>4800</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>5100</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1030,38 +1037,41 @@
       <c r="AL9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>2400</v>
+        <v>9400</v>
       </c>
       <c r="E10" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F10" s="3">
         <v>7000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>7900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>8400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>8200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>9400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>11100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>11600</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1140,8 +1150,11 @@
       <c r="AL10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1180,8 +1193,9 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1290,8 +1304,11 @@
       <c r="AL12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1400,17 +1417,20 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3">
         <v>4100</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1429,8 +1449,8 @@
       <c r="K14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1510,8 +1530,11 @@
       <c r="AL14" s="3">
         <v>0</v>
       </c>
+      <c r="AM14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1540,7 +1563,7 @@
         <v>100</v>
       </c>
       <c r="L15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1620,8 +1643,11 @@
       <c r="AL15" s="3">
         <v>0</v>
       </c>
+      <c r="AM15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1657,109 +1683,110 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E17" s="3">
         <v>6100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>6200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>6600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>6400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>5500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>6900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>6800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>500</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>400</v>
-      </c>
-      <c r="AJ17" s="3">
-        <v>300</v>
       </c>
       <c r="AK17" s="3">
         <v>300</v>
@@ -1767,118 +1794,124 @@
       <c r="AL17" s="3">
         <v>300</v>
       </c>
+      <c r="AM17" s="3">
+        <v>300</v>
+      </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-3700</v>
+        <v>3100</v>
       </c>
       <c r="E18" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="F18" s="3">
         <v>800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>2000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>2700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>4300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>5800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>10600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>10200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>9300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>9800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>8900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>9600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>9000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>8800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>8300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>7300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>6700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>5900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>6000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>5500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>5300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>5500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>5400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>5500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>5100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>5200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>4700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>4400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>4500</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>4400</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>4700</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>4500</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1917,8 +1950,9 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1946,71 +1980,71 @@
       <c r="K20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M20" s="3">
         <v>-4300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-4400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-2900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-4400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-3700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-4200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-3500</v>
-      </c>
-      <c r="S20" s="3">
-        <v>-4100</v>
       </c>
       <c r="T20" s="3">
         <v>-4100</v>
       </c>
       <c r="U20" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="V20" s="3">
         <v>-3100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-3500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-2500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-3300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-2700</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>-3700</v>
       </c>
       <c r="AA20" s="3">
         <v>-3700</v>
       </c>
       <c r="AB20" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="AC20" s="3">
         <v>-3800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-3500</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-3000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-2800</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-3400</v>
-      </c>
-      <c r="AG20" s="3">
-        <v>-2900</v>
       </c>
       <c r="AH20" s="3">
         <v>-2900</v>
@@ -2019,76 +2053,79 @@
         <v>-2900</v>
       </c>
       <c r="AJ20" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="AK20" s="3">
         <v>-2700</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-2500</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-2700</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-3600</v>
+        <v>3200</v>
       </c>
       <c r="E21" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="F21" s="3">
         <v>900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>2100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>2800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>4400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>5900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>6400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>5800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>6500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>5100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>5300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>5700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>5600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>4400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>4000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>4800</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>5</v>
       </c>
@@ -2131,14 +2168,17 @@
       <c r="AJ21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AK21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL21" s="3">
         <v>2100</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2166,8 +2206,8 @@
       <c r="K22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -2247,159 +2287,165 @@
       <c r="AL22" s="3">
         <v>0</v>
       </c>
+      <c r="AM22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-7800</v>
+        <v>3100</v>
       </c>
       <c r="E23" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="F23" s="3">
         <v>800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>4300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>5800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>6300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>5700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>6400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>5400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>5200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>5400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>5500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>4700</v>
-      </c>
-      <c r="T23" s="3">
-        <v>4200</v>
       </c>
       <c r="U23" s="3">
         <v>4200</v>
       </c>
       <c r="V23" s="3">
+        <v>4200</v>
+      </c>
+      <c r="W23" s="3">
         <v>3200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>3400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>2600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>2900</v>
-      </c>
-      <c r="Z23" s="3">
-        <v>1700</v>
       </c>
       <c r="AA23" s="3">
         <v>1700</v>
       </c>
       <c r="AB23" s="3">
+        <v>1700</v>
+      </c>
+      <c r="AC23" s="3">
         <v>1600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>2000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>2100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>2400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1600</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1500</v>
-      </c>
-      <c r="AJ23" s="3">
-        <v>2000</v>
       </c>
       <c r="AK23" s="3">
         <v>2000</v>
       </c>
       <c r="AL23" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AM23" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-1200</v>
+        <v>600</v>
       </c>
       <c r="E24" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="F24" s="3">
         <v>200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1700</v>
-      </c>
-      <c r="L24" s="3">
-        <v>1800</v>
       </c>
       <c r="M24" s="3">
         <v>1800</v>
       </c>
       <c r="N24" s="3">
+        <v>1800</v>
+      </c>
+      <c r="O24" s="3">
         <v>1900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1500</v>
-      </c>
-      <c r="P24" s="3">
-        <v>1600</v>
       </c>
       <c r="Q24" s="3">
         <v>1600</v>
@@ -2408,67 +2454,70 @@
         <v>1600</v>
       </c>
       <c r="S24" s="3">
+        <v>1600</v>
+      </c>
+      <c r="T24" s="3">
         <v>1400</v>
-      </c>
-      <c r="T24" s="3">
-        <v>1200</v>
       </c>
       <c r="U24" s="3">
         <v>1200</v>
       </c>
       <c r="V24" s="3">
+        <v>1200</v>
+      </c>
+      <c r="W24" s="3">
         <v>900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1000</v>
-      </c>
-      <c r="X24" s="3">
-        <v>800</v>
       </c>
       <c r="Y24" s="3">
         <v>800</v>
       </c>
       <c r="Z24" s="3">
+        <v>800</v>
+      </c>
+      <c r="AA24" s="3">
         <v>500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>300</v>
-      </c>
-      <c r="AB24" s="3">
-        <v>500</v>
       </c>
       <c r="AC24" s="3">
         <v>500</v>
       </c>
       <c r="AD24" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AE24" s="3">
         <v>600</v>
       </c>
       <c r="AF24" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AG24" s="3">
         <v>500</v>
       </c>
       <c r="AH24" s="3">
+        <v>500</v>
+      </c>
+      <c r="AI24" s="3">
         <v>700</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>600</v>
-      </c>
-      <c r="AJ24" s="3">
-        <v>800</v>
       </c>
       <c r="AK24" s="3">
         <v>800</v>
       </c>
       <c r="AL24" s="3">
+        <v>800</v>
+      </c>
+      <c r="AM24" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2577,228 +2626,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-6600</v>
+        <v>2500</v>
       </c>
       <c r="E26" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="F26" s="3">
         <v>600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>3000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>4100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>4600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>4000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>4500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>3900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>3700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>3800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>3900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>3300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>2900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>3000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>2200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>2400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>2000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1100</v>
-      </c>
-      <c r="AC26" s="3">
-        <v>1500</v>
       </c>
       <c r="AD26" s="3">
         <v>1500</v>
       </c>
       <c r="AE26" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AF26" s="3">
         <v>1700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>1000</v>
-      </c>
-      <c r="AH26" s="3">
-        <v>900</v>
       </c>
       <c r="AI26" s="3">
         <v>900</v>
       </c>
       <c r="AJ26" s="3">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="AK26" s="3">
         <v>1200</v>
       </c>
       <c r="AL26" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AM26" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-6600</v>
+        <v>2500</v>
       </c>
       <c r="E27" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="F27" s="3">
         <v>600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>3000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>4100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>4600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>4000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>4500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>3900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>3700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>3800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>3900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>3300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>2900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>3000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>2200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>2400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>2000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1100</v>
-      </c>
-      <c r="AC27" s="3">
-        <v>1500</v>
       </c>
       <c r="AD27" s="3">
         <v>1500</v>
       </c>
       <c r="AE27" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AF27" s="3">
         <v>1700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>1000</v>
-      </c>
-      <c r="AH27" s="3">
-        <v>900</v>
       </c>
       <c r="AI27" s="3">
         <v>900</v>
       </c>
       <c r="AJ27" s="3">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="AK27" s="3">
         <v>1200</v>
       </c>
       <c r="AL27" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AM27" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2907,8 +2965,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2975,8 +3036,8 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>5</v>
+      <c r="Y29" s="3">
+        <v>0</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>5</v>
@@ -2996,12 +3057,12 @@
       <c r="AE29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AF29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG29" s="3">
         <v>-300</v>
       </c>
-      <c r="AG29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH29" s="3" t="s">
         <v>5</v>
       </c>
@@ -3017,8 +3078,11 @@
       <c r="AL29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3127,8 +3191,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3237,8 +3304,11 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3266,71 +3336,71 @@
       <c r="K32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M32" s="3">
         <v>4300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>4400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>2900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>4400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>3700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>4200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>3500</v>
-      </c>
-      <c r="S32" s="3">
-        <v>4100</v>
       </c>
       <c r="T32" s="3">
         <v>4100</v>
       </c>
       <c r="U32" s="3">
+        <v>4100</v>
+      </c>
+      <c r="V32" s="3">
         <v>3100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>3500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>2500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>3300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>2700</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>3700</v>
       </c>
       <c r="AA32" s="3">
         <v>3700</v>
       </c>
       <c r="AB32" s="3">
+        <v>3700</v>
+      </c>
+      <c r="AC32" s="3">
         <v>3800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>3500</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>3000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>2800</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>3400</v>
-      </c>
-      <c r="AG32" s="3">
-        <v>2900</v>
       </c>
       <c r="AH32" s="3">
         <v>2900</v>
@@ -3339,126 +3409,132 @@
         <v>2900</v>
       </c>
       <c r="AJ32" s="3">
+        <v>2900</v>
+      </c>
+      <c r="AK32" s="3">
         <v>2700</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>2500</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-6600</v>
+        <v>2500</v>
       </c>
       <c r="E33" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="F33" s="3">
         <v>600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>3000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>4100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>4600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>4000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>4500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>3900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>3700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>3800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>3900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>3300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>2900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>3000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>2200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>2400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>2000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1100</v>
-      </c>
-      <c r="AC33" s="3">
-        <v>1500</v>
       </c>
       <c r="AD33" s="3">
         <v>1500</v>
       </c>
       <c r="AE33" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AF33" s="3">
         <v>1700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>1000</v>
-      </c>
-      <c r="AH33" s="3">
-        <v>900</v>
       </c>
       <c r="AI33" s="3">
         <v>900</v>
       </c>
       <c r="AJ33" s="3">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="AK33" s="3">
         <v>1200</v>
       </c>
       <c r="AL33" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AM33" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3567,233 +3643,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-6600</v>
+        <v>2500</v>
       </c>
       <c r="E35" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="F35" s="3">
         <v>600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>3000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>4100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>4600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>4000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>4500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>3900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>3700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>3800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>3900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>3300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>2900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>3000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>2200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>2400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>2000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1100</v>
-      </c>
-      <c r="AC35" s="3">
-        <v>1500</v>
       </c>
       <c r="AD35" s="3">
         <v>1500</v>
       </c>
       <c r="AE35" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AF35" s="3">
         <v>1700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>1000</v>
-      </c>
-      <c r="AH35" s="3">
-        <v>900</v>
       </c>
       <c r="AI35" s="3">
         <v>900</v>
       </c>
       <c r="AJ35" s="3">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="AK35" s="3">
         <v>1200</v>
       </c>
       <c r="AL35" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AM35" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3832,8 +3917,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3872,118 +3958,122 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>72400</v>
+      </c>
+      <c r="E41" s="3">
         <v>51400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>80900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>40100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>37700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>57800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>86600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>112400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>116600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>77600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>42800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>36600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>65900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>40700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>37800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>56100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>46900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>30800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>24300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>68000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>36500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>38300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>37000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>12100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>18600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>21700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>20900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>23700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>18900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>68800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>20400</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>20200</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>20800</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>24200</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>20100</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>21800</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4012,19 +4102,19 @@
         <v>0</v>
       </c>
       <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
         <v>13600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>13700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>13800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>13500</v>
-      </c>
-      <c r="P42" s="3">
-        <v>4300</v>
       </c>
       <c r="Q42" s="3">
         <v>4300</v>
@@ -4033,7 +4123,7 @@
         <v>4300</v>
       </c>
       <c r="S42" s="3">
-        <v>3400</v>
+        <v>4300</v>
       </c>
       <c r="T42" s="3">
         <v>3400</v>
@@ -4045,7 +4135,7 @@
         <v>3400</v>
       </c>
       <c r="W42" s="3">
-        <v>3300</v>
+        <v>3400</v>
       </c>
       <c r="X42" s="3">
         <v>3300</v>
@@ -4057,7 +4147,7 @@
         <v>3300</v>
       </c>
       <c r="AA42" s="3">
-        <v>3100</v>
+        <v>3300</v>
       </c>
       <c r="AB42" s="3">
         <v>3100</v>
@@ -4069,7 +4159,7 @@
         <v>3100</v>
       </c>
       <c r="AE42" s="3">
-        <v>5100</v>
+        <v>3100</v>
       </c>
       <c r="AF42" s="3">
         <v>5100</v>
@@ -4078,22 +4168,25 @@
         <v>5100</v>
       </c>
       <c r="AH42" s="3">
+        <v>5100</v>
+      </c>
+      <c r="AI42" s="3">
         <v>4800</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>5200</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>5300</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>4900</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -4121,8 +4214,8 @@
       <c r="K43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
+      <c r="L43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M43" s="3">
         <v>0</v>
@@ -4202,22 +4295,25 @@
       <c r="AL43" s="3">
         <v>0</v>
       </c>
+      <c r="AM43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>5100</v>
+        <v>4400</v>
       </c>
       <c r="E44" s="3">
-        <v>5100</v>
+        <v>4400</v>
       </c>
       <c r="F44" s="3">
         <v>5100</v>
       </c>
-      <c r="G44" s="3" t="s">
-        <v>5</v>
+      <c r="G44" s="3">
+        <v>5100</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>5</v>
@@ -4231,8 +4327,8 @@
       <c r="K44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -4312,38 +4408,41 @@
       <c r="AL44" s="3">
         <v>0</v>
       </c>
+      <c r="AM44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>19300</v>
+        <v>22300</v>
       </c>
       <c r="E45" s="3">
+        <v>3500</v>
+      </c>
+      <c r="F45" s="3">
         <v>16200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3700</v>
-      </c>
-      <c r="I45" s="3">
-        <v>3800</v>
       </c>
       <c r="J45" s="3">
         <v>3800</v>
       </c>
       <c r="K45" s="3">
+        <v>3800</v>
+      </c>
+      <c r="L45" s="3">
         <v>4100</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
-      </c>
       <c r="M45" s="3">
         <v>0</v>
       </c>
@@ -4422,38 +4521,41 @@
       <c r="AL45" s="3">
         <v>0</v>
       </c>
+      <c r="AM45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>75800</v>
+        <v>99100</v>
       </c>
       <c r="E46" s="3">
+        <v>59300</v>
+      </c>
+      <c r="F46" s="3">
         <v>102300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>48900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>41600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>61500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>90400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>116200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>120600</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -4532,38 +4634,41 @@
       <c r="AL46" s="3">
         <v>0</v>
       </c>
+      <c r="AM46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>81600</v>
+        <v>81800</v>
       </c>
       <c r="E47" s="3">
+        <v>81500</v>
+      </c>
+      <c r="F47" s="3">
         <v>89800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>96900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>97500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>98500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>94200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>97700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>98400</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
       <c r="M47" s="3">
         <v>0</v>
       </c>
@@ -4642,70 +4747,73 @@
       <c r="AL47" s="3">
         <v>0</v>
       </c>
+      <c r="AM47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>5200</v>
+        <v>5100</v>
       </c>
       <c r="E48" s="3">
+        <v>6400</v>
+      </c>
+      <c r="F48" s="3">
         <v>5300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>6000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>6100</v>
       </c>
-      <c r="H48" s="3">
-        <v>6300</v>
-      </c>
       <c r="I48" s="3">
+        <v>6200</v>
+      </c>
+      <c r="J48" s="3">
         <v>6400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6600</v>
-      </c>
-      <c r="K48" s="3">
-        <v>6800</v>
       </c>
       <c r="L48" s="3">
         <v>6800</v>
       </c>
       <c r="M48" s="3">
+        <v>6800</v>
+      </c>
+      <c r="N48" s="3">
         <v>7000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>6500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>6700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>6900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>7000</v>
-      </c>
-      <c r="R48" s="3">
-        <v>7200</v>
       </c>
       <c r="S48" s="3">
         <v>7200</v>
       </c>
       <c r="T48" s="3">
+        <v>7200</v>
+      </c>
+      <c r="U48" s="3">
         <v>7300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>7000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>6200</v>
-      </c>
-      <c r="W48" s="3">
-        <v>6300</v>
       </c>
       <c r="X48" s="3">
         <v>6300</v>
@@ -4717,43 +4825,46 @@
         <v>6300</v>
       </c>
       <c r="AA48" s="3">
+        <v>6300</v>
+      </c>
+      <c r="AB48" s="3">
         <v>6400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>5800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>5300</v>
-      </c>
-      <c r="AD48" s="3">
-        <v>5200</v>
       </c>
       <c r="AE48" s="3">
         <v>5200</v>
       </c>
       <c r="AF48" s="3">
-        <v>5300</v>
+        <v>5200</v>
       </c>
       <c r="AG48" s="3">
         <v>5300</v>
       </c>
       <c r="AH48" s="3">
+        <v>5300</v>
+      </c>
+      <c r="AI48" s="3">
         <v>5400</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>5500</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>5400</v>
-      </c>
-      <c r="AK48" s="3">
-        <v>5500</v>
       </c>
       <c r="AL48" s="3">
         <v>5500</v>
       </c>
+      <c r="AM48" s="3">
+        <v>5500</v>
+      </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4761,7 +4872,7 @@
         <v>0</v>
       </c>
       <c r="E49" s="3">
-        <v>4100</v>
+        <v>0</v>
       </c>
       <c r="F49" s="3">
         <v>4100</v>
@@ -4862,8 +4973,11 @@
       <c r="AL49" s="3">
         <v>4100</v>
       </c>
+      <c r="AM49" s="3">
+        <v>4100</v>
+      </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4972,8 +5086,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5082,38 +5199,41 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F52" s="3">
+      <c r="E52" s="3">
+        <v>11200</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G52" s="3">
         <v>12600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>13200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>10400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>14800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>12000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>9500</v>
       </c>
-      <c r="L52" s="3">
-        <v>0</v>
-      </c>
       <c r="M52" s="3">
         <v>0</v>
       </c>
@@ -5192,8 +5312,11 @@
       <c r="AL52" s="3">
         <v>0</v>
       </c>
+      <c r="AM52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5302,118 +5425,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1067600</v>
+        <v>1063400</v>
       </c>
       <c r="E54" s="3">
+        <v>1067100</v>
+      </c>
+      <c r="F54" s="3">
         <v>1118800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1082000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1080200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1122500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1142200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1161400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1147000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1115300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1043800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>980800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>982300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>958100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>922600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>901600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>886100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>865900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>833800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>850700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>721600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>696000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>680800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>635600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>626300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>622100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>595200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>586000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>577000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>610900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>539000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>537500</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>524500</v>
-      </c>
-      <c r="AJ54" s="3">
-        <v>513700</v>
       </c>
       <c r="AK54" s="3">
         <v>513700</v>
       </c>
       <c r="AL54" s="3">
+        <v>513700</v>
+      </c>
+      <c r="AM54" s="3">
         <v>518300</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5452,8 +5581,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5492,118 +5622,122 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>957100</v>
+      </c>
+      <c r="E57" s="3">
         <v>962600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1002800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>966600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>939200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1009700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1030800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1048300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1015700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>11100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>4700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>6600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>4200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>5600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>4300</v>
-      </c>
-      <c r="X57" s="3">
-        <v>3300</v>
       </c>
       <c r="Y57" s="3">
         <v>3300</v>
       </c>
       <c r="Z57" s="3">
+        <v>3300</v>
+      </c>
+      <c r="AA57" s="3">
         <v>3500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>3000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>2700</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>2100</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>2000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>2300</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>1900</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>3200</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>8100</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5611,19 +5745,19 @@
         <v>0</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="F58" s="3">
+        <v>0</v>
+      </c>
+      <c r="G58" s="3">
         <v>3900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>400</v>
       </c>
-      <c r="H58" s="3">
-        <v>500</v>
-      </c>
       <c r="I58" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="J58" s="3">
         <v>500</v>
@@ -5632,7 +5766,7 @@
         <v>500</v>
       </c>
       <c r="L58" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
@@ -5712,8 +5846,11 @@
       <c r="AL58" s="3">
         <v>0</v>
       </c>
+      <c r="AM58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5741,39 +5878,39 @@
       <c r="K59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L59" s="3">
+      <c r="L59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M59" s="3">
         <v>1400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1400</v>
-      </c>
-      <c r="S59" s="3">
-        <v>1300</v>
       </c>
       <c r="T59" s="3">
         <v>1300</v>
       </c>
       <c r="U59" s="3">
+        <v>1300</v>
+      </c>
+      <c r="V59" s="3">
         <v>900</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W59" s="3" t="s">
         <v>5</v>
       </c>
@@ -5789,8 +5926,8 @@
       <c r="AA59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB59" s="3">
-        <v>0</v>
+      <c r="AB59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AC59" s="3">
         <v>0</v>
@@ -5822,38 +5959,41 @@
       <c r="AL59" s="3">
         <v>0</v>
       </c>
+      <c r="AM59" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>968800</v>
+        <v>961600</v>
       </c>
       <c r="E60" s="3">
+        <v>964700</v>
+      </c>
+      <c r="F60" s="3">
         <v>1008100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>973700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>940100</v>
       </c>
-      <c r="H60" s="3">
-        <v>1014400</v>
-      </c>
       <c r="I60" s="3">
+        <v>1010300</v>
+      </c>
+      <c r="J60" s="3">
         <v>1032600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1049700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1016900</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
@@ -5932,8 +6072,11 @@
       <c r="AL60" s="3">
         <v>0</v>
       </c>
+      <c r="AM60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5941,28 +6084,28 @@
         <v>5900</v>
       </c>
       <c r="E61" s="3">
+        <v>6800</v>
+      </c>
+      <c r="F61" s="3">
         <v>5900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>6300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>35100</v>
       </c>
-      <c r="H61" s="3">
-        <v>6400</v>
-      </c>
       <c r="I61" s="3">
+        <v>6900</v>
+      </c>
+      <c r="J61" s="3">
         <v>6500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>6600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>29700</v>
-      </c>
-      <c r="L61" s="3">
-        <v>5900</v>
       </c>
       <c r="M61" s="3">
         <v>5900</v>
@@ -6007,7 +6150,7 @@
         <v>5900</v>
       </c>
       <c r="AA61" s="3">
-        <v>0</v>
+        <v>5900</v>
       </c>
       <c r="AB61" s="3">
         <v>0</v>
@@ -6042,38 +6185,41 @@
       <c r="AL61" s="3">
         <v>0</v>
       </c>
+      <c r="AM61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="E62" s="3">
-        <v>4100</v>
+        <v>3900</v>
       </c>
       <c r="F62" s="3">
         <v>4100</v>
       </c>
       <c r="G62" s="3">
+        <v>4100</v>
+      </c>
+      <c r="H62" s="3">
         <v>7100</v>
       </c>
-      <c r="H62" s="3">
-        <v>4100</v>
-      </c>
       <c r="I62" s="3">
+        <v>7600</v>
+      </c>
+      <c r="J62" s="3">
         <v>9600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>10600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>7700</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
-      </c>
       <c r="M62" s="3">
         <v>0</v>
       </c>
@@ -6152,8 +6298,11 @@
       <c r="AL62" s="3">
         <v>0</v>
       </c>
+      <c r="AM62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6262,8 +6411,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6372,8 +6524,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6482,118 +6637,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>975300</v>
+        <v>968000</v>
       </c>
       <c r="E66" s="3">
+        <v>975400</v>
+      </c>
+      <c r="F66" s="3">
         <v>1018100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>984100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>982300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1024800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1048700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1067000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1054400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1026800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>959400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>896100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>898600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>873800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>840600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>822700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>810600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>790200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>760400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>779400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>653400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>628600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>614300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>570900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>562900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>560600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>534700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>525800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>517300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>551200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>478500</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>477000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>465200</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>455100</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>453400</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>458800</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6632,8 +6793,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6742,8 +6904,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6852,8 +7017,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6962,8 +7130,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7072,118 +7243,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>5</v>
+      <c r="D72" s="3">
+        <v>65400</v>
       </c>
       <c r="E72" s="3">
+        <v>62900</v>
+      </c>
+      <c r="F72" s="3">
         <v>70000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>69700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>69500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>69000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>67900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>66800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>64700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>61400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>57600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>54500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>50800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>47600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>44800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>41700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>38500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>37500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>35300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>33100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>31600</v>
       </c>
-      <c r="X72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y72" s="3">
+      <c r="Y72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z72" s="3">
         <v>28800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>27500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>27000</v>
       </c>
-      <c r="AB72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC72" s="3">
+      <c r="AC72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD72" s="3">
         <v>25900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>25200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>24400</v>
       </c>
-      <c r="AF72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG72" s="3">
+      <c r="AG72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH72" s="3">
         <v>23600</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>23300</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>23100</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>22800</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>22200</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>21600</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7292,8 +7469,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7402,8 +7582,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7512,118 +7695,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>92300</v>
+        <v>95300</v>
       </c>
       <c r="E76" s="3">
+        <v>91700</v>
+      </c>
+      <c r="F76" s="3">
         <v>100700</v>
-      </c>
-      <c r="F76" s="3">
-        <v>97900</v>
       </c>
       <c r="G76" s="3">
         <v>97900</v>
       </c>
       <c r="H76" s="3">
+        <v>97900</v>
+      </c>
+      <c r="I76" s="3">
         <v>97700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>93400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>94400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>92700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>88500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>84400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>84700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>83700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>84300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>82000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>79000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>75500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>75600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>73400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>71200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>68200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>67300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>66500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>64700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>63400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>61500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>60500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>60200</v>
-      </c>
-      <c r="AE76" s="3">
-        <v>59700</v>
       </c>
       <c r="AF76" s="3">
         <v>59700</v>
       </c>
       <c r="AG76" s="3">
+        <v>59700</v>
+      </c>
+      <c r="AH76" s="3">
         <v>60500</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>60400</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>59300</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>58600</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>60300</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>59500</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7732,233 +7921,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-6600</v>
+        <v>2500</v>
       </c>
       <c r="E81" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="F81" s="3">
         <v>600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>3000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>4100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>4600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>4000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>4500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>3900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>3700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>3800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>3900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>3300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>2900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>3000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>2200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>2400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>2000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1100</v>
-      </c>
-      <c r="AC81" s="3">
-        <v>1500</v>
       </c>
       <c r="AD81" s="3">
         <v>1500</v>
       </c>
       <c r="AE81" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AF81" s="3">
         <v>1700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>1000</v>
-      </c>
-      <c r="AH81" s="3">
-        <v>900</v>
       </c>
       <c r="AI81" s="3">
         <v>900</v>
       </c>
       <c r="AJ81" s="3">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="AK81" s="3">
         <v>1200</v>
       </c>
       <c r="AL81" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AM81" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7997,8 +8195,9 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8036,29 +8235,29 @@
         <v>100</v>
       </c>
       <c r="O83" s="3">
+        <v>100</v>
+      </c>
+      <c r="P83" s="3">
         <v>-300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>-300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>-200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>600</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W83" s="3" t="s">
         <v>5</v>
       </c>
@@ -8071,8 +8270,8 @@
       <c r="Z83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA83" s="3">
-        <v>0</v>
+      <c r="AA83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AB83" s="3">
         <v>0</v>
@@ -8098,17 +8297,20 @@
       <c r="AI83" s="3">
         <v>0</v>
       </c>
-      <c r="AJ83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK83" s="3">
-        <v>100</v>
+      <c r="AJ83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AL83" s="3">
         <v>100</v>
       </c>
+      <c r="AM83" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8217,8 +8419,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8327,8 +8532,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8437,8 +8645,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8547,8 +8758,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8657,8 +8871,11 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -8668,57 +8885,57 @@
       <c r="E89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F89" s="3">
+      <c r="F89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G89" s="3">
         <v>1100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-2400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>3700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-2800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>7500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-50300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>34000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-29500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>46600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>5400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-1400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>2000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1700</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W89" s="3" t="s">
         <v>5</v>
       </c>
@@ -8731,8 +8948,8 @@
       <c r="Z89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA89" s="3">
-        <v>0</v>
+      <c r="AA89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AB89" s="3">
         <v>0</v>
@@ -8758,17 +8975,20 @@
       <c r="AI89" s="3">
         <v>0</v>
       </c>
-      <c r="AJ89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK89" s="3">
+      <c r="AJ89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL89" s="3">
         <v>1900</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8807,8 +9027,9 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8818,8 +9039,8 @@
       <c r="E91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F91" s="3">
-        <v>-100</v>
+      <c r="F91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G91" s="3">
         <v>-100</v>
@@ -8828,13 +9049,13 @@
         <v>-100</v>
       </c>
       <c r="I91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J91" s="3">
         <v>0</v>
       </c>
       <c r="K91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L91" s="3">
         <v>-100</v>
@@ -8846,29 +9067,29 @@
         <v>-100</v>
       </c>
       <c r="O91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="P91" s="3">
         <v>0</v>
       </c>
       <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
         <v>-100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-400</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W91" s="3" t="s">
         <v>5</v>
       </c>
@@ -8881,8 +9102,8 @@
       <c r="Z91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA91" s="3">
-        <v>0</v>
+      <c r="AA91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AB91" s="3">
         <v>0</v>
@@ -8908,17 +9129,20 @@
       <c r="AI91" s="3">
         <v>0</v>
       </c>
-      <c r="AJ91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK91" s="3">
-        <v>0</v>
+      <c r="AJ91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AL91" s="3">
         <v>0</v>
       </c>
+      <c r="AM91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9027,8 +9251,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9137,8 +9364,11 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -9148,57 +9378,57 @@
       <c r="E94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F94" s="3">
+      <c r="F94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G94" s="3">
         <v>-200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>21900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-5900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-5200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-16700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>7600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-33000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-59300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-8000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>102600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-74000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-45500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>161400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-25200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-143500</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W94" s="3" t="s">
         <v>5</v>
       </c>
@@ -9211,8 +9441,8 @@
       <c r="Z94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA94" s="3">
-        <v>0</v>
+      <c r="AA94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AB94" s="3">
         <v>0</v>
@@ -9238,17 +9468,20 @@
       <c r="AI94" s="3">
         <v>0</v>
       </c>
-      <c r="AJ94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK94" s="3">
+      <c r="AJ94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL94" s="3">
         <v>-2900</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>10700</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9287,8 +9520,9 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9298,8 +9532,8 @@
       <c r="E96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F96" s="3">
-        <v>800</v>
+      <c r="F96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G96" s="3">
         <v>800</v>
@@ -9317,7 +9551,7 @@
         <v>800</v>
       </c>
       <c r="L96" s="3">
-        <v>-800</v>
+        <v>800</v>
       </c>
       <c r="M96" s="3">
         <v>-800</v>
@@ -9326,29 +9560,29 @@
         <v>-800</v>
       </c>
       <c r="O96" s="3">
+        <v>-800</v>
+      </c>
+      <c r="P96" s="3">
         <v>2200</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-800</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-2200</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-700</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>2200</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-700</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-2200</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
         <v>0</v>
       </c>
@@ -9392,13 +9626,16 @@
         <v>0</v>
       </c>
       <c r="AK96" s="3">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="AL96" s="3">
         <v>-600</v>
       </c>
+      <c r="AM96" s="3">
+        <v>-600</v>
+      </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9507,8 +9744,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9617,8 +9857,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9727,8 +9970,11 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -9738,57 +9984,57 @@
       <c r="E100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F100" s="3">
+      <c r="F100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G100" s="3">
         <v>1500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-42700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-22000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-18300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>8800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>34200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>60200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>63300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-57800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>30300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>47100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>10900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-137100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>29700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>127700</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W100" s="3" t="s">
         <v>5</v>
       </c>
@@ -9801,8 +10047,8 @@
       <c r="Z100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA100" s="3">
-        <v>0</v>
+      <c r="AA100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AB100" s="3">
         <v>0</v>
@@ -9828,17 +10074,20 @@
       <c r="AI100" s="3">
         <v>0</v>
       </c>
-      <c r="AJ100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK100" s="3">
+      <c r="AJ100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL100" s="3">
         <v>-1100</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-10700</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9866,8 +10115,8 @@
       <c r="K101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -9947,8 +10196,11 @@
       <c r="AL101" s="3">
         <v>0</v>
       </c>
+      <c r="AM101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -9959,56 +10211,56 @@
         <v>0</v>
       </c>
       <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
         <v>2400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-20100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-28800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-25800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-4200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>39000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>34700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>6200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-29300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>15300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>2900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>6900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>9200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>23600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>6600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-14000</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W102" s="3" t="s">
         <v>5</v>
       </c>
@@ -10021,8 +10273,8 @@
       <c r="Z102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA102" s="3">
-        <v>0</v>
+      <c r="AA102" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AB102" s="3">
         <v>0</v>
@@ -10048,13 +10300,16 @@
       <c r="AI102" s="3">
         <v>0</v>
       </c>
-      <c r="AJ102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK102" s="3">
+      <c r="AJ102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL102" s="3">
         <v>-2100</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SSBI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SSBI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="92">
   <si>
     <t>SSBI</t>
   </si>
@@ -656,279 +656,286 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AM102"/>
+  <dimension ref="A5:AN102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="3">
         <v>9400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>7000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>7900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>8400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>8200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>9400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>11100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>11600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>14200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>12500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>11300</v>
-      </c>
-      <c r="P8" s="3">
-        <v>10900</v>
       </c>
       <c r="Q8" s="3">
         <v>10900</v>
       </c>
       <c r="R8" s="3">
+        <v>10900</v>
+      </c>
+      <c r="S8" s="3">
         <v>10600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>10100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>10400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>10100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>9200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>8800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>8300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>8000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>7600</v>
-      </c>
-      <c r="AA8" s="3">
-        <v>7200</v>
       </c>
       <c r="AB8" s="3">
         <v>7200</v>
       </c>
       <c r="AC8" s="3">
+        <v>7200</v>
+      </c>
+      <c r="AD8" s="3">
         <v>6800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>6600</v>
-      </c>
-      <c r="AE8" s="3">
-        <v>6100</v>
       </c>
       <c r="AF8" s="3">
         <v>6100</v>
       </c>
       <c r="AG8" s="3">
+        <v>6100</v>
+      </c>
+      <c r="AH8" s="3">
         <v>5700</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>5200</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>5000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>4800</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>5000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>4800</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>5100</v>
       </c>
     </row>
-    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1040,41 +1047,44 @@
       <c r="AM9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AN9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E10" s="3">
         <v>9400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>7000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>7900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>8400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>8200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>9400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>11100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>11600</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1153,8 +1163,11 @@
       <c r="AM10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AN10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1194,8 +1207,9 @@
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
+      <c r="AN11" s="3"/>
     </row>
-    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1307,8 +1321,11 @@
       <c r="AM12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AN12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1420,20 +1437,23 @@
       <c r="AM13" s="3">
         <v>0</v>
       </c>
+      <c r="AN13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3">
         <v>4100</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1452,8 +1472,8 @@
       <c r="L14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1533,13 +1553,16 @@
       <c r="AM14" s="3">
         <v>0</v>
       </c>
+      <c r="AN14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E15" s="3">
         <v>100</v>
@@ -1566,7 +1589,7 @@
         <v>100</v>
       </c>
       <c r="M15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
@@ -1646,8 +1669,11 @@
       <c r="AM15" s="3">
         <v>0</v>
       </c>
+      <c r="AN15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1684,112 +1710,113 @@
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
+      <c r="AN16" s="3"/>
     </row>
-    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E17" s="3">
         <v>6300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>6100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>6200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>6600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>6400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>5500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>6900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>6800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>900</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>800</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>500</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>400</v>
-      </c>
-      <c r="AK17" s="3">
-        <v>300</v>
       </c>
       <c r="AL17" s="3">
         <v>300</v>
@@ -1797,121 +1824,127 @@
       <c r="AM17" s="3">
         <v>300</v>
       </c>
+      <c r="AN17" s="3">
+        <v>300</v>
+      </c>
     </row>
-    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E18" s="3">
         <v>3100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-4400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>2000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>4300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>5800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>10600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>10200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>9300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>9800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>8900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>9600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>9000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>8800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>8300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>7300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>6700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>5900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>6000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>5500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>5300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>5500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>5400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>5500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>5100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>5200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>4700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>4400</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>4500</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>4400</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>4700</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>4500</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1951,8 +1984,9 @@
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
+      <c r="AN19" s="3"/>
     </row>
-    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1983,71 +2017,71 @@
       <c r="L20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N20" s="3">
         <v>-4300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-4400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-2900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-4400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-3700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-4200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-3500</v>
-      </c>
-      <c r="T20" s="3">
-        <v>-4100</v>
       </c>
       <c r="U20" s="3">
         <v>-4100</v>
       </c>
       <c r="V20" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="W20" s="3">
         <v>-3100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-3500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-3300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-2700</v>
-      </c>
-      <c r="AA20" s="3">
-        <v>-3700</v>
       </c>
       <c r="AB20" s="3">
         <v>-3700</v>
       </c>
       <c r="AC20" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="AD20" s="3">
         <v>-3800</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-3500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-3000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-2800</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-3400</v>
-      </c>
-      <c r="AH20" s="3">
-        <v>-2900</v>
       </c>
       <c r="AI20" s="3">
         <v>-2900</v>
@@ -2056,79 +2090,82 @@
         <v>-2900</v>
       </c>
       <c r="AK20" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="AL20" s="3">
         <v>-2700</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-2500</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-2700</v>
       </c>
     </row>
-    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3">
         <v>3200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-4300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>2100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>4400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>5900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>6400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>5800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>6500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>5100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>5300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>5700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>5600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>4400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>4000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>4800</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X21" s="3" t="s">
         <v>5</v>
       </c>
@@ -2171,14 +2208,17 @@
       <c r="AK21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AL21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM21" s="3">
         <v>2100</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2209,8 +2249,8 @@
       <c r="L22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -2290,165 +2330,171 @@
       <c r="AM22" s="3">
         <v>0</v>
       </c>
+      <c r="AN22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E23" s="3">
         <v>3100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-8500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>4300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>5800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>6300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>5700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>6400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>5400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>5200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>5400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>5500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>4700</v>
-      </c>
-      <c r="U23" s="3">
-        <v>4200</v>
       </c>
       <c r="V23" s="3">
         <v>4200</v>
       </c>
       <c r="W23" s="3">
+        <v>4200</v>
+      </c>
+      <c r="X23" s="3">
         <v>3200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>3400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>2600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>2900</v>
-      </c>
-      <c r="AA23" s="3">
-        <v>1700</v>
       </c>
       <c r="AB23" s="3">
         <v>1700</v>
       </c>
       <c r="AC23" s="3">
+        <v>1700</v>
+      </c>
+      <c r="AD23" s="3">
         <v>1600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>2000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>2100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>2400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1600</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>1500</v>
-      </c>
-      <c r="AK23" s="3">
-        <v>2000</v>
       </c>
       <c r="AL23" s="3">
         <v>2000</v>
       </c>
       <c r="AM23" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AN23" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E24" s="3">
         <v>600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-1400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1700</v>
-      </c>
-      <c r="M24" s="3">
-        <v>1800</v>
       </c>
       <c r="N24" s="3">
         <v>1800</v>
       </c>
       <c r="O24" s="3">
+        <v>1800</v>
+      </c>
+      <c r="P24" s="3">
         <v>1900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1500</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>1600</v>
       </c>
       <c r="R24" s="3">
         <v>1600</v>
@@ -2457,67 +2503,70 @@
         <v>1600</v>
       </c>
       <c r="T24" s="3">
+        <v>1600</v>
+      </c>
+      <c r="U24" s="3">
         <v>1400</v>
-      </c>
-      <c r="U24" s="3">
-        <v>1200</v>
       </c>
       <c r="V24" s="3">
         <v>1200</v>
       </c>
       <c r="W24" s="3">
+        <v>1200</v>
+      </c>
+      <c r="X24" s="3">
         <v>900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1000</v>
-      </c>
-      <c r="Y24" s="3">
-        <v>800</v>
       </c>
       <c r="Z24" s="3">
         <v>800</v>
       </c>
       <c r="AA24" s="3">
+        <v>800</v>
+      </c>
+      <c r="AB24" s="3">
         <v>500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>300</v>
-      </c>
-      <c r="AC24" s="3">
-        <v>500</v>
       </c>
       <c r="AD24" s="3">
         <v>500</v>
       </c>
       <c r="AE24" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AF24" s="3">
         <v>600</v>
       </c>
       <c r="AG24" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AH24" s="3">
         <v>500</v>
       </c>
       <c r="AI24" s="3">
+        <v>500</v>
+      </c>
+      <c r="AJ24" s="3">
         <v>700</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>600</v>
-      </c>
-      <c r="AK24" s="3">
-        <v>800</v>
       </c>
       <c r="AL24" s="3">
         <v>800</v>
       </c>
       <c r="AM24" s="3">
+        <v>800</v>
+      </c>
+      <c r="AN24" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2629,234 +2678,243 @@
       <c r="AM25" s="3">
         <v>0</v>
       </c>
+      <c r="AN25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E26" s="3">
         <v>2500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-7100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>3000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>4100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>4600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>4000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>4500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>3900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>3700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>3800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>3900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>3300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>2900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>3000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>2200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>2400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>2000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1100</v>
-      </c>
-      <c r="AD26" s="3">
-        <v>1500</v>
       </c>
       <c r="AE26" s="3">
         <v>1500</v>
       </c>
       <c r="AF26" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AG26" s="3">
         <v>1700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>1000</v>
-      </c>
-      <c r="AI26" s="3">
-        <v>900</v>
       </c>
       <c r="AJ26" s="3">
         <v>900</v>
       </c>
       <c r="AK26" s="3">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="AL26" s="3">
         <v>1200</v>
       </c>
       <c r="AM26" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AN26" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E27" s="3">
         <v>2500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-7100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>3000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>4100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>4600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>4000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>4500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>3900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>3700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>3800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>3900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>3300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>2900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>3000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>2200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>2400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>2000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1100</v>
-      </c>
-      <c r="AD27" s="3">
-        <v>1500</v>
       </c>
       <c r="AE27" s="3">
         <v>1500</v>
       </c>
       <c r="AF27" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AG27" s="3">
         <v>1700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>1000</v>
-      </c>
-      <c r="AI27" s="3">
-        <v>900</v>
       </c>
       <c r="AJ27" s="3">
         <v>900</v>
       </c>
       <c r="AK27" s="3">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="AL27" s="3">
         <v>1200</v>
       </c>
       <c r="AM27" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AN27" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2968,8 +3026,11 @@
       <c r="AM28" s="3">
         <v>0</v>
       </c>
+      <c r="AN28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3039,8 +3100,8 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>5</v>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>5</v>
@@ -3060,12 +3121,12 @@
       <c r="AF29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH29" s="3">
         <v>-300</v>
       </c>
-      <c r="AH29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AI29" s="3" t="s">
         <v>5</v>
       </c>
@@ -3081,8 +3142,11 @@
       <c r="AM29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AN29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3194,8 +3258,11 @@
       <c r="AM30" s="3">
         <v>0</v>
       </c>
+      <c r="AN30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3307,8 +3374,11 @@
       <c r="AM31" s="3">
         <v>0</v>
       </c>
+      <c r="AN31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3339,71 +3409,71 @@
       <c r="L32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N32" s="3">
         <v>4300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>4400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>2900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>4400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>3700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>4200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>3500</v>
-      </c>
-      <c r="T32" s="3">
-        <v>4100</v>
       </c>
       <c r="U32" s="3">
         <v>4100</v>
       </c>
       <c r="V32" s="3">
+        <v>4100</v>
+      </c>
+      <c r="W32" s="3">
         <v>3100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>3500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>2500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>3300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>2700</v>
-      </c>
-      <c r="AA32" s="3">
-        <v>3700</v>
       </c>
       <c r="AB32" s="3">
         <v>3700</v>
       </c>
       <c r="AC32" s="3">
+        <v>3700</v>
+      </c>
+      <c r="AD32" s="3">
         <v>3800</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>3500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>3000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>2800</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>3400</v>
-      </c>
-      <c r="AH32" s="3">
-        <v>2900</v>
       </c>
       <c r="AI32" s="3">
         <v>2900</v>
@@ -3412,129 +3482,135 @@
         <v>2900</v>
       </c>
       <c r="AK32" s="3">
+        <v>2900</v>
+      </c>
+      <c r="AL32" s="3">
         <v>2700</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>2500</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E33" s="3">
         <v>2500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-7100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>3000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>4100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>4600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>4000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>4500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>3900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>3700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>3800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>3900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>3300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>2900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>3000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>2200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>2400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>2000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1100</v>
-      </c>
-      <c r="AD33" s="3">
-        <v>1500</v>
       </c>
       <c r="AE33" s="3">
         <v>1500</v>
       </c>
       <c r="AF33" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AG33" s="3">
         <v>1700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>500</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>1000</v>
-      </c>
-      <c r="AI33" s="3">
-        <v>900</v>
       </c>
       <c r="AJ33" s="3">
         <v>900</v>
       </c>
       <c r="AK33" s="3">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="AL33" s="3">
         <v>1200</v>
       </c>
       <c r="AM33" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AN33" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3646,239 +3722,248 @@
       <c r="AM34" s="3">
         <v>0</v>
       </c>
+      <c r="AN34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E35" s="3">
         <v>2500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-7100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>3000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>4100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>4600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>4000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>4500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>3900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>3700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>3800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>3900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>3300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>2900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>3000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>2200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>2400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>2000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1100</v>
-      </c>
-      <c r="AD35" s="3">
-        <v>1500</v>
       </c>
       <c r="AE35" s="3">
         <v>1500</v>
       </c>
       <c r="AF35" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AG35" s="3">
         <v>1700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>500</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>1000</v>
-      </c>
-      <c r="AI35" s="3">
-        <v>900</v>
       </c>
       <c r="AJ35" s="3">
         <v>900</v>
       </c>
       <c r="AK35" s="3">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="AL35" s="3">
         <v>1200</v>
       </c>
       <c r="AM35" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AN35" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3918,8 +4003,9 @@
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
+      <c r="AN39" s="3"/>
     </row>
-    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3959,121 +4045,125 @@
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
+      <c r="AN40" s="3"/>
     </row>
-    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3">
+      <c r="D41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E41" s="3">
         <v>72400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>51400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>80900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>40100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>37700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>57800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>86600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>112400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>116600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>77600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>42800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>36600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>65900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>40700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>37800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>56100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>46900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>30800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>24300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>68000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>36500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>38300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>37000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>12100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>18600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>21700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>20900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>23700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>18900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>68800</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>20400</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>20200</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>20800</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>24200</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>20100</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>21800</v>
       </c>
     </row>
-    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4105,19 +4195,19 @@
         <v>0</v>
       </c>
       <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>13600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>13700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>13800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>13500</v>
-      </c>
-      <c r="Q42" s="3">
-        <v>4300</v>
       </c>
       <c r="R42" s="3">
         <v>4300</v>
@@ -4126,7 +4216,7 @@
         <v>4300</v>
       </c>
       <c r="T42" s="3">
-        <v>3400</v>
+        <v>4300</v>
       </c>
       <c r="U42" s="3">
         <v>3400</v>
@@ -4138,7 +4228,7 @@
         <v>3400</v>
       </c>
       <c r="X42" s="3">
-        <v>3300</v>
+        <v>3400</v>
       </c>
       <c r="Y42" s="3">
         <v>3300</v>
@@ -4150,7 +4240,7 @@
         <v>3300</v>
       </c>
       <c r="AB42" s="3">
-        <v>3100</v>
+        <v>3300</v>
       </c>
       <c r="AC42" s="3">
         <v>3100</v>
@@ -4162,7 +4252,7 @@
         <v>3100</v>
       </c>
       <c r="AF42" s="3">
-        <v>5100</v>
+        <v>3100</v>
       </c>
       <c r="AG42" s="3">
         <v>5100</v>
@@ -4171,22 +4261,25 @@
         <v>5100</v>
       </c>
       <c r="AI42" s="3">
+        <v>5100</v>
+      </c>
+      <c r="AJ42" s="3">
         <v>4800</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>5200</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>5300</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>4900</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -4217,8 +4310,8 @@
       <c r="L43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
+      <c r="M43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N43" s="3">
         <v>0</v>
@@ -4298,25 +4391,28 @@
       <c r="AM43" s="3">
         <v>0</v>
       </c>
+      <c r="AN43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>4400</v>
+      <c r="D44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E44" s="3">
         <v>4400</v>
       </c>
       <c r="F44" s="3">
-        <v>5100</v>
+        <v>4400</v>
       </c>
       <c r="G44" s="3">
         <v>5100</v>
       </c>
-      <c r="H44" s="3" t="s">
-        <v>5</v>
+      <c r="H44" s="3">
+        <v>5100</v>
       </c>
       <c r="I44" s="3" t="s">
         <v>5</v>
@@ -4330,8 +4426,8 @@
       <c r="L44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -4411,41 +4507,44 @@
       <c r="AM44" s="3">
         <v>0</v>
       </c>
+      <c r="AN44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>22300</v>
+      <c r="D45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E45" s="3">
+        <v>3700</v>
+      </c>
+      <c r="F45" s="3">
         <v>3500</v>
-      </c>
-      <c r="F45" s="3">
-        <v>16200</v>
       </c>
       <c r="G45" s="3">
         <v>3600</v>
       </c>
       <c r="H45" s="3">
+        <v>3600</v>
+      </c>
+      <c r="I45" s="3">
         <v>3800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3700</v>
-      </c>
-      <c r="J45" s="3">
-        <v>3800</v>
       </c>
       <c r="K45" s="3">
         <v>3800</v>
       </c>
       <c r="L45" s="3">
+        <v>3800</v>
+      </c>
+      <c r="M45" s="3">
         <v>4100</v>
       </c>
-      <c r="M45" s="3">
-        <v>0</v>
-      </c>
       <c r="N45" s="3">
         <v>0</v>
       </c>
@@ -4524,41 +4623,44 @@
       <c r="AM45" s="3">
         <v>0</v>
       </c>
+      <c r="AN45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3">
-        <v>99100</v>
+      <c r="D46" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E46" s="3">
+        <v>80600</v>
+      </c>
+      <c r="F46" s="3">
         <v>59300</v>
       </c>
-      <c r="F46" s="3">
-        <v>102300</v>
-      </c>
       <c r="G46" s="3">
+        <v>89600</v>
+      </c>
+      <c r="H46" s="3">
         <v>48900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>41600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>61500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>90400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>116200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>120600</v>
       </c>
-      <c r="M46" s="3">
-        <v>0</v>
-      </c>
       <c r="N46" s="3">
         <v>0</v>
       </c>
@@ -4637,41 +4739,44 @@
       <c r="AM46" s="3">
         <v>0</v>
       </c>
+      <c r="AN46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E47" s="3">
         <v>81800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>81500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>89800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>96900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>97500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>98500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>94200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>97700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>98400</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
-      </c>
       <c r="N47" s="3">
         <v>0</v>
       </c>
@@ -4750,73 +4855,76 @@
       <c r="AM47" s="3">
         <v>0</v>
       </c>
+      <c r="AN47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
-        <v>5100</v>
+      <c r="D48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E48" s="3">
+        <v>6200</v>
+      </c>
+      <c r="F48" s="3">
         <v>6400</v>
       </c>
-      <c r="F48" s="3">
-        <v>5300</v>
-      </c>
       <c r="G48" s="3">
+        <v>6200</v>
+      </c>
+      <c r="H48" s="3">
         <v>6000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>6100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6600</v>
-      </c>
-      <c r="L48" s="3">
-        <v>6800</v>
       </c>
       <c r="M48" s="3">
         <v>6800</v>
       </c>
       <c r="N48" s="3">
+        <v>6800</v>
+      </c>
+      <c r="O48" s="3">
         <v>7000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>6500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>6700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>6900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>7000</v>
-      </c>
-      <c r="S48" s="3">
-        <v>7200</v>
       </c>
       <c r="T48" s="3">
         <v>7200</v>
       </c>
       <c r="U48" s="3">
+        <v>7200</v>
+      </c>
+      <c r="V48" s="3">
         <v>7300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>7000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>6200</v>
-      </c>
-      <c r="X48" s="3">
-        <v>6300</v>
       </c>
       <c r="Y48" s="3">
         <v>6300</v>
@@ -4828,54 +4936,57 @@
         <v>6300</v>
       </c>
       <c r="AB48" s="3">
+        <v>6300</v>
+      </c>
+      <c r="AC48" s="3">
         <v>6400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>5800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>5300</v>
-      </c>
-      <c r="AE48" s="3">
-        <v>5200</v>
       </c>
       <c r="AF48" s="3">
         <v>5200</v>
       </c>
       <c r="AG48" s="3">
-        <v>5300</v>
+        <v>5200</v>
       </c>
       <c r="AH48" s="3">
         <v>5300</v>
       </c>
       <c r="AI48" s="3">
+        <v>5300</v>
+      </c>
+      <c r="AJ48" s="3">
         <v>5400</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>5500</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>5400</v>
-      </c>
-      <c r="AL48" s="3">
-        <v>5500</v>
       </c>
       <c r="AM48" s="3">
         <v>5500</v>
       </c>
+      <c r="AN48" s="3">
+        <v>5500</v>
+      </c>
     </row>
-    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3">
-        <v>0</v>
+      <c r="D49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E49" s="3">
         <v>0</v>
       </c>
       <c r="F49" s="3">
-        <v>4100</v>
+        <v>0</v>
       </c>
       <c r="G49" s="3">
         <v>4100</v>
@@ -4976,8 +5087,11 @@
       <c r="AM49" s="3">
         <v>4100</v>
       </c>
+      <c r="AN49" s="3">
+        <v>4100</v>
+      </c>
     </row>
-    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5089,8 +5203,11 @@
       <c r="AM50" s="3">
         <v>0</v>
       </c>
+      <c r="AN50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5202,8 +5319,11 @@
       <c r="AM51" s="3">
         <v>0</v>
       </c>
+      <c r="AN51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -5211,32 +5331,32 @@
         <v>5</v>
       </c>
       <c r="E52" s="3">
+        <v>17400</v>
+      </c>
+      <c r="F52" s="3">
         <v>11200</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G52" s="3">
+        <v>11700</v>
+      </c>
+      <c r="H52" s="3">
         <v>12600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>13200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>10400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>14800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>12000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>9500</v>
       </c>
-      <c r="M52" s="3">
-        <v>0</v>
-      </c>
       <c r="N52" s="3">
         <v>0</v>
       </c>
@@ -5315,8 +5435,11 @@
       <c r="AM52" s="3">
         <v>0</v>
       </c>
+      <c r="AN52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5428,121 +5551,127 @@
       <c r="AM53" s="3">
         <v>0</v>
       </c>
+      <c r="AN53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3">
+      <c r="D54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E54" s="3">
         <v>1063400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1067100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1118800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1082000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1080200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1122500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1142200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1161400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1147000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1115300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1043800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>980800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>982300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>958100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>922600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>901600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>886100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>865900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>833800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>850700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>721600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>696000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>680800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>635600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>626300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>622100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>595200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>586000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>577000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>610900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>539000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>537500</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>524500</v>
-      </c>
-      <c r="AK54" s="3">
-        <v>513700</v>
       </c>
       <c r="AL54" s="3">
         <v>513700</v>
       </c>
       <c r="AM54" s="3">
+        <v>513700</v>
+      </c>
+      <c r="AN54" s="3">
         <v>518300</v>
       </c>
     </row>
-    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5582,8 +5711,9 @@
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
+      <c r="AN55" s="3"/>
     </row>
-    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5623,144 +5753,148 @@
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
+      <c r="AN56" s="3"/>
     </row>
-    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
+      <c r="D57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E57" s="3">
         <v>957100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>962600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1002800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>966600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>939200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1009700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1030800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1048300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1015700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>11100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>4600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>6600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>4400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>4200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>5600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>4300</v>
-      </c>
-      <c r="Y57" s="3">
-        <v>3300</v>
       </c>
       <c r="Z57" s="3">
         <v>3300</v>
       </c>
       <c r="AA57" s="3">
+        <v>3300</v>
+      </c>
+      <c r="AB57" s="3">
         <v>3500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>3000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>2200</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>2700</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>2100</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>2000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>2300</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>1900</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>3200</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>8100</v>
       </c>
     </row>
-    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
-        <v>0</v>
+      <c r="D58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E58" s="3">
         <v>400</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="G58" s="3">
+        <v>400</v>
+      </c>
+      <c r="H58" s="3">
         <v>3900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>400</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="K58" s="3">
         <v>500</v>
@@ -5769,7 +5903,7 @@
         <v>500</v>
       </c>
       <c r="M58" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="N58" s="3">
         <v>0</v>
@@ -5849,8 +5983,11 @@
       <c r="AM58" s="3">
         <v>0</v>
       </c>
+      <c r="AN58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5881,39 +6018,39 @@
       <c r="L59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N59" s="3">
         <v>1400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1400</v>
-      </c>
-      <c r="T59" s="3">
-        <v>1300</v>
       </c>
       <c r="U59" s="3">
         <v>1300</v>
       </c>
       <c r="V59" s="3">
+        <v>1300</v>
+      </c>
+      <c r="W59" s="3">
         <v>900</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>5</v>
       </c>
@@ -5929,8 +6066,8 @@
       <c r="AB59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC59" s="3">
-        <v>0</v>
+      <c r="AC59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AD59" s="3">
         <v>0</v>
@@ -5962,41 +6099,44 @@
       <c r="AM59" s="3">
         <v>0</v>
       </c>
+      <c r="AN59" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3">
-        <v>961600</v>
+      <c r="D60" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E60" s="3">
+        <v>957900</v>
+      </c>
+      <c r="F60" s="3">
         <v>964700</v>
       </c>
-      <c r="F60" s="3">
-        <v>1008100</v>
-      </c>
       <c r="G60" s="3">
+        <v>1004500</v>
+      </c>
+      <c r="H60" s="3">
         <v>973700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>940100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1010300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1032600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1049700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1016900</v>
       </c>
-      <c r="M60" s="3">
-        <v>0</v>
-      </c>
       <c r="N60" s="3">
         <v>0</v>
       </c>
@@ -6075,40 +6215,43 @@
       <c r="AM60" s="3">
         <v>0</v>
       </c>
+      <c r="AN60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>5900</v>
+        <v>0</v>
       </c>
       <c r="E61" s="3">
+        <v>6700</v>
+      </c>
+      <c r="F61" s="3">
         <v>6800</v>
       </c>
-      <c r="F61" s="3">
-        <v>5900</v>
-      </c>
       <c r="G61" s="3">
+        <v>6600</v>
+      </c>
+      <c r="H61" s="3">
         <v>6300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>35100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>6900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>6500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>6600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>29700</v>
-      </c>
-      <c r="M61" s="3">
-        <v>5900</v>
       </c>
       <c r="N61" s="3">
         <v>5900</v>
@@ -6153,7 +6296,7 @@
         <v>5900</v>
       </c>
       <c r="AB61" s="3">
-        <v>0</v>
+        <v>5900</v>
       </c>
       <c r="AC61" s="3">
         <v>0</v>
@@ -6188,41 +6331,44 @@
       <c r="AM61" s="3">
         <v>0</v>
       </c>
+      <c r="AN61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>500</v>
+      <c r="D62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E62" s="3">
+        <v>3400</v>
+      </c>
+      <c r="F62" s="3">
         <v>3900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
+        <v>7100</v>
+      </c>
+      <c r="H62" s="3">
         <v>4100</v>
       </c>
-      <c r="G62" s="3">
-        <v>4100</v>
-      </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>7100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>7600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>9600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>10600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>7700</v>
       </c>
-      <c r="M62" s="3">
-        <v>0</v>
-      </c>
       <c r="N62" s="3">
         <v>0</v>
       </c>
@@ -6301,8 +6447,11 @@
       <c r="AM62" s="3">
         <v>0</v>
       </c>
+      <c r="AN62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6414,8 +6563,11 @@
       <c r="AM63" s="3">
         <v>0</v>
       </c>
+      <c r="AN63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6527,8 +6679,11 @@
       <c r="AM64" s="3">
         <v>0</v>
       </c>
+      <c r="AN64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6640,121 +6795,127 @@
       <c r="AM65" s="3">
         <v>0</v>
       </c>
+      <c r="AN65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3">
+      <c r="D66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E66" s="3">
         <v>968000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>975400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1018100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>984100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>982300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1024800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1048700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1067000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1054400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1026800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>959400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>896100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>898600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>873800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>840600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>822700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>810600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>790200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>760400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>779400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>653400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>628600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>614300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>570900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>562900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>560600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>534700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>525800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>517300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>551200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>478500</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>477000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>465200</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>455100</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>453400</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>458800</v>
       </c>
     </row>
-    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6794,8 +6955,9 @@
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
+      <c r="AN67" s="3"/>
     </row>
-    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6907,8 +7069,11 @@
       <c r="AM68" s="3">
         <v>0</v>
       </c>
+      <c r="AN68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7020,8 +7185,11 @@
       <c r="AM69" s="3">
         <v>0</v>
       </c>
+      <c r="AN69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7133,8 +7301,11 @@
       <c r="AM70" s="3">
         <v>0</v>
       </c>
+      <c r="AN70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7246,121 +7417,127 @@
       <c r="AM71" s="3">
         <v>0</v>
       </c>
+      <c r="AN71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E72" s="3">
         <v>65400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>62900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>70000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>69700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>69500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>69000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>67900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>66800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>64700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>61400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>57600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>54500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>50800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>47600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>44800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>41700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>38500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>37500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>35300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>33100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>31600</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z72" s="3">
+      <c r="Z72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA72" s="3">
         <v>28800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>27500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>27000</v>
       </c>
-      <c r="AC72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD72" s="3">
+      <c r="AD72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE72" s="3">
         <v>25900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>25200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>24400</v>
       </c>
-      <c r="AG72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH72" s="3">
+      <c r="AH72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI72" s="3">
         <v>23600</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>23300</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>23100</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>22800</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>22200</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>21600</v>
       </c>
     </row>
-    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7472,8 +7649,11 @@
       <c r="AM73" s="3">
         <v>0</v>
       </c>
+      <c r="AN73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7585,8 +7765,11 @@
       <c r="AM74" s="3">
         <v>0</v>
       </c>
+      <c r="AN74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7698,121 +7881,127 @@
       <c r="AM75" s="3">
         <v>0</v>
       </c>
+      <c r="AN75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3">
+      <c r="D76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E76" s="3">
         <v>95300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>91700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>100700</v>
-      </c>
-      <c r="G76" s="3">
-        <v>97900</v>
       </c>
       <c r="H76" s="3">
         <v>97900</v>
       </c>
       <c r="I76" s="3">
+        <v>97900</v>
+      </c>
+      <c r="J76" s="3">
         <v>97700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>93400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>94400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>92700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>88500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>84400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>84700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>83700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>84300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>82000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>79000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>75500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>75600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>73400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>71200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>68200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>67300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>66500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>64700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>63400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>61500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>60500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>60200</v>
-      </c>
-      <c r="AF76" s="3">
-        <v>59700</v>
       </c>
       <c r="AG76" s="3">
         <v>59700</v>
       </c>
       <c r="AH76" s="3">
+        <v>59700</v>
+      </c>
+      <c r="AI76" s="3">
         <v>60500</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>60400</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>59300</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>58600</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>60300</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>59500</v>
       </c>
     </row>
-    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7924,239 +8113,248 @@
       <c r="AM77" s="3">
         <v>0</v>
       </c>
+      <c r="AN77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E81" s="3">
         <v>2500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-7100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>3000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>4100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>4600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>4000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>4500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>3900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>3700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>3800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>3900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>3300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>2900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>3000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>2200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>2400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>2000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1100</v>
-      </c>
-      <c r="AD81" s="3">
-        <v>1500</v>
       </c>
       <c r="AE81" s="3">
         <v>1500</v>
       </c>
       <c r="AF81" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AG81" s="3">
         <v>1700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>500</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>1000</v>
-      </c>
-      <c r="AI81" s="3">
-        <v>900</v>
       </c>
       <c r="AJ81" s="3">
         <v>900</v>
       </c>
       <c r="AK81" s="3">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="AL81" s="3">
         <v>1200</v>
       </c>
       <c r="AM81" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AN81" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8196,8 +8394,9 @@
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
+      <c r="AN82" s="3"/>
     </row>
-    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8238,29 +8437,29 @@
         <v>100</v>
       </c>
       <c r="P83" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q83" s="3">
         <v>-300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>-300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>-200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>600</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X83" s="3" t="s">
         <v>5</v>
       </c>
@@ -8273,8 +8472,8 @@
       <c r="AA83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB83" s="3">
-        <v>0</v>
+      <c r="AB83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AC83" s="3">
         <v>0</v>
@@ -8300,17 +8499,20 @@
       <c r="AJ83" s="3">
         <v>0</v>
       </c>
-      <c r="AK83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL83" s="3">
-        <v>100</v>
+      <c r="AK83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AM83" s="3">
         <v>100</v>
       </c>
+      <c r="AN83" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8422,8 +8624,11 @@
       <c r="AM84" s="3">
         <v>0</v>
       </c>
+      <c r="AN84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8535,8 +8740,11 @@
       <c r="AM85" s="3">
         <v>0</v>
       </c>
+      <c r="AN85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8648,8 +8856,11 @@
       <c r="AM86" s="3">
         <v>0</v>
       </c>
+      <c r="AN86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8761,8 +8972,11 @@
       <c r="AM87" s="3">
         <v>0</v>
       </c>
+      <c r="AN87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8874,71 +9088,74 @@
       <c r="AM88" s="3">
         <v>0</v>
       </c>
+      <c r="AN88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F89" s="3" t="s">
-        <v>5</v>
+      <c r="E89" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="F89" s="3">
+        <v>1700</v>
       </c>
       <c r="G89" s="3">
+        <v>2300</v>
+      </c>
+      <c r="H89" s="3">
         <v>1100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-2400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-2800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>7500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-50300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>34000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-29500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>46600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>5400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-1400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>2000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1700</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X89" s="3" t="s">
         <v>5</v>
       </c>
@@ -8951,8 +9168,8 @@
       <c r="AA89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB89" s="3">
-        <v>0</v>
+      <c r="AB89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AC89" s="3">
         <v>0</v>
@@ -8978,17 +9195,20 @@
       <c r="AJ89" s="3">
         <v>0</v>
       </c>
-      <c r="AK89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL89" s="3">
+      <c r="AK89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM89" s="3">
         <v>1900</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9028,22 +9248,23 @@
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
+      <c r="AN90" s="3"/>
     </row>
-    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F91" s="3" t="s">
-        <v>5</v>
+      <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
+        <v>0</v>
       </c>
       <c r="G91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="H91" s="3">
         <v>-100</v>
@@ -9052,13 +9273,13 @@
         <v>-100</v>
       </c>
       <c r="J91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
       </c>
       <c r="L91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M91" s="3">
         <v>-100</v>
@@ -9070,29 +9291,29 @@
         <v>-100</v>
       </c>
       <c r="P91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Q91" s="3">
         <v>0</v>
       </c>
       <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
         <v>-100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-400</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X91" s="3" t="s">
         <v>5</v>
       </c>
@@ -9105,8 +9326,8 @@
       <c r="AA91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB91" s="3">
-        <v>0</v>
+      <c r="AB91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AC91" s="3">
         <v>0</v>
@@ -9132,17 +9353,20 @@
       <c r="AJ91" s="3">
         <v>0</v>
       </c>
-      <c r="AK91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL91" s="3">
-        <v>0</v>
+      <c r="AK91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AM91" s="3">
         <v>0</v>
       </c>
+      <c r="AN91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9254,8 +9478,11 @@
       <c r="AM92" s="3">
         <v>0</v>
       </c>
+      <c r="AN92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9367,71 +9594,74 @@
       <c r="AM93" s="3">
         <v>0</v>
       </c>
+      <c r="AN93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F94" s="3" t="s">
-        <v>5</v>
+      <c r="E94" s="3">
+        <v>29700</v>
+      </c>
+      <c r="F94" s="3">
+        <v>9000</v>
       </c>
       <c r="G94" s="3">
+        <v>6000</v>
+      </c>
+      <c r="H94" s="3">
         <v>-200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>21900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-5900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-5200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-16700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>7600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-33000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-59300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-8000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>102600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-74000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-45500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>161400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-25200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-143500</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X94" s="3" t="s">
         <v>5</v>
       </c>
@@ -9444,8 +9674,8 @@
       <c r="AA94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB94" s="3">
-        <v>0</v>
+      <c r="AB94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AC94" s="3">
         <v>0</v>
@@ -9471,17 +9701,20 @@
       <c r="AJ94" s="3">
         <v>0</v>
       </c>
-      <c r="AK94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL94" s="3">
+      <c r="AK94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM94" s="3">
         <v>-2900</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>10700</v>
       </c>
     </row>
-    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9521,8 +9754,9 @@
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
+      <c r="AN95" s="3"/>
     </row>
-    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9532,11 +9766,11 @@
       <c r="E96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>5</v>
+      <c r="F96" s="3">
+        <v>0</v>
       </c>
       <c r="G96" s="3">
-        <v>800</v>
+        <v>300</v>
       </c>
       <c r="H96" s="3">
         <v>800</v>
@@ -9554,7 +9788,7 @@
         <v>800</v>
       </c>
       <c r="M96" s="3">
-        <v>-800</v>
+        <v>800</v>
       </c>
       <c r="N96" s="3">
         <v>-800</v>
@@ -9563,29 +9797,29 @@
         <v>-800</v>
       </c>
       <c r="P96" s="3">
+        <v>-800</v>
+      </c>
+      <c r="Q96" s="3">
         <v>2200</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-800</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-2200</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-700</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>2200</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-700</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-2200</v>
       </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
       <c r="X96" s="3">
         <v>0</v>
       </c>
@@ -9629,13 +9863,16 @@
         <v>0</v>
       </c>
       <c r="AL96" s="3">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="AM96" s="3">
         <v>-600</v>
       </c>
+      <c r="AN96" s="3">
+        <v>-600</v>
+      </c>
     </row>
-    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9747,8 +9984,11 @@
       <c r="AM97" s="3">
         <v>0</v>
       </c>
+      <c r="AN97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9860,8 +10100,11 @@
       <c r="AM98" s="3">
         <v>0</v>
       </c>
+      <c r="AN98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9973,71 +10216,74 @@
       <c r="AM99" s="3">
         <v>0</v>
       </c>
+      <c r="AN99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F100" s="3" t="s">
-        <v>5</v>
+      <c r="E100" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="F100" s="3">
+        <v>-40200</v>
       </c>
       <c r="G100" s="3">
+        <v>32400</v>
+      </c>
+      <c r="H100" s="3">
         <v>1500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-42700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-22000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-18300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>8800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>34200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>60200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>63300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-2700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-57800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>30300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>47100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>10900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-137100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>29700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>127700</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X100" s="3" t="s">
         <v>5</v>
       </c>
@@ -10050,8 +10296,8 @@
       <c r="AA100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB100" s="3">
-        <v>0</v>
+      <c r="AB100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AC100" s="3">
         <v>0</v>
@@ -10077,17 +10323,20 @@
       <c r="AJ100" s="3">
         <v>0</v>
       </c>
-      <c r="AK100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL100" s="3">
+      <c r="AK100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM100" s="3">
         <v>-1100</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-10700</v>
       </c>
     </row>
-    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10118,8 +10367,8 @@
       <c r="L101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -10199,8 +10448,11 @@
       <c r="AM101" s="3">
         <v>0</v>
       </c>
+      <c r="AN101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -10208,62 +10460,62 @@
         <v>0</v>
       </c>
       <c r="E102" s="3">
-        <v>0</v>
+        <v>21000</v>
       </c>
       <c r="F102" s="3">
-        <v>0</v>
+        <v>-29500</v>
       </c>
       <c r="G102" s="3">
+        <v>40800</v>
+      </c>
+      <c r="H102" s="3">
         <v>2400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-20100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-28800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-25800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-4200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>39000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>34700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>6200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-29300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>15300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>2900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>6900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>9200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>23600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>6600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-14000</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X102" s="3" t="s">
         <v>5</v>
       </c>
@@ -10276,8 +10528,8 @@
       <c r="AA102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB102" s="3">
-        <v>0</v>
+      <c r="AB102" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AC102" s="3">
         <v>0</v>
@@ -10303,13 +10555,16 @@
       <c r="AJ102" s="3">
         <v>0</v>
       </c>
-      <c r="AK102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL102" s="3">
+      <c r="AK102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM102" s="3">
         <v>-2100</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SSBI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SSBI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="92">
   <si>
     <t>SSBI</t>
   </si>
@@ -656,293 +656,299 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42916</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42825</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42643</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E8" s="3">
         <v>6800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>9500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>9400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>7000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>7900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>8400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>8200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>9400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>11100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>11600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>14200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>12500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>11300</v>
-      </c>
-      <c r="R8" s="3">
-        <v>10900</v>
       </c>
       <c r="S8" s="3">
         <v>10900</v>
       </c>
       <c r="T8" s="3">
+        <v>10900</v>
+      </c>
+      <c r="U8" s="3">
         <v>10600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>10100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>10400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>10100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>9200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>8800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>8300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>8000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>7600</v>
-      </c>
-      <c r="AC8" s="3">
-        <v>7200</v>
       </c>
       <c r="AD8" s="3">
         <v>7200</v>
       </c>
       <c r="AE8" s="3">
+        <v>7200</v>
+      </c>
+      <c r="AF8" s="3">
         <v>6800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>6600</v>
-      </c>
-      <c r="AG8" s="3">
-        <v>6100</v>
       </c>
       <c r="AH8" s="3">
         <v>6100</v>
       </c>
       <c r="AI8" s="3">
+        <v>6100</v>
+      </c>
+      <c r="AJ8" s="3">
         <v>5700</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>5200</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>5000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>4800</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>5000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>4800</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>5100</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1060,47 +1066,50 @@
       <c r="AO9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AP9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E10" s="3">
         <v>6800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>9500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>9400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>7000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>7900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>8400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>8200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>9400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>11100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>11600</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1179,8 +1188,11 @@
       <c r="AO10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AP10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1222,8 +1234,9 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1341,8 +1354,11 @@
       <c r="AO12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AP12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1460,8 +1476,11 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1474,12 +1493,12 @@
       <c r="F14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H14" s="3">
         <v>4100</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1498,8 +1517,8 @@
       <c r="N14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1579,8 +1598,11 @@
       <c r="AO14" s="3">
         <v>0</v>
       </c>
+      <c r="AP14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1618,7 +1640,7 @@
         <v>100</v>
       </c>
       <c r="O15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P15" s="3">
         <v>0</v>
@@ -1698,8 +1720,11 @@
       <c r="AO15" s="3">
         <v>0</v>
       </c>
+      <c r="AP15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1738,118 +1763,119 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E17" s="3">
         <v>5500</v>
-      </c>
-      <c r="E17" s="3">
-        <v>6300</v>
       </c>
       <c r="F17" s="3">
         <v>6300</v>
       </c>
       <c r="G17" s="3">
+        <v>6300</v>
+      </c>
+      <c r="H17" s="3">
         <v>6100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>6200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>6600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>6400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>6900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>6800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1100</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>900</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>800</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>500</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>400</v>
-      </c>
-      <c r="AM17" s="3">
-        <v>300</v>
       </c>
       <c r="AN17" s="3">
         <v>300</v>
@@ -1857,127 +1883,133 @@
       <c r="AO17" s="3">
         <v>300</v>
       </c>
+      <c r="AP17" s="3">
+        <v>300</v>
+      </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E18" s="3">
         <v>1300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>3200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>3100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-4400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>4300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>5800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>10600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>10200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>9300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>9800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>8900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>9600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>9000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>8800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>8300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>7300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>6700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>5900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>6000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>5500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>5300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>5500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>5400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>5500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>5100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>5200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>4700</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>4400</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>4500</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>4400</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>4700</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>4500</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2019,8 +2051,9 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2057,71 +2090,71 @@
       <c r="N20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P20" s="3">
         <v>-4300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-4400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-2900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-4400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-3700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-4200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-3500</v>
-      </c>
-      <c r="V20" s="3">
-        <v>-4100</v>
       </c>
       <c r="W20" s="3">
         <v>-4100</v>
       </c>
       <c r="X20" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-3100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-3500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-2500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-3300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-2700</v>
-      </c>
-      <c r="AC20" s="3">
-        <v>-3700</v>
       </c>
       <c r="AD20" s="3">
         <v>-3700</v>
       </c>
       <c r="AE20" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="AF20" s="3">
         <v>-3800</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-3500</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-3000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-2800</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-3400</v>
-      </c>
-      <c r="AJ20" s="3">
-        <v>-2900</v>
       </c>
       <c r="AK20" s="3">
         <v>-2900</v>
@@ -2130,16 +2163,19 @@
         <v>-2900</v>
       </c>
       <c r="AM20" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="AN20" s="3">
         <v>-2700</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-2500</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-2700</v>
       </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2147,68 +2183,68 @@
         <v>1400</v>
       </c>
       <c r="E21" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F21" s="3">
         <v>3300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>3200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-4300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>4400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>5900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>6400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>5800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>6500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>5100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>5300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>5700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>5600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>4400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>4000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>4800</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>5</v>
       </c>
@@ -2251,14 +2287,17 @@
       <c r="AM21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AN21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO21" s="3">
         <v>2100</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2295,8 +2334,8 @@
       <c r="N22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -2376,177 +2415,183 @@
       <c r="AO22" s="3">
         <v>0</v>
       </c>
+      <c r="AP22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E23" s="3">
         <v>1300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>3200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>3100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-8500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>4300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>5800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>6300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>5700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>6400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>5400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>5200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>5400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>5500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>4700</v>
-      </c>
-      <c r="W23" s="3">
-        <v>4200</v>
       </c>
       <c r="X23" s="3">
         <v>4200</v>
       </c>
       <c r="Y23" s="3">
+        <v>4200</v>
+      </c>
+      <c r="Z23" s="3">
         <v>3200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>3400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>2600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>2900</v>
-      </c>
-      <c r="AC23" s="3">
-        <v>1700</v>
       </c>
       <c r="AD23" s="3">
         <v>1700</v>
       </c>
       <c r="AE23" s="3">
+        <v>1700</v>
+      </c>
+      <c r="AF23" s="3">
         <v>1600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>2000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>2100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>2400</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1300</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>1500</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>1600</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>1500</v>
-      </c>
-      <c r="AM23" s="3">
-        <v>2000</v>
       </c>
       <c r="AN23" s="3">
         <v>2000</v>
       </c>
       <c r="AO23" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AP23" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>300</v>
+      </c>
+      <c r="E24" s="3">
         <v>500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-1400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1700</v>
-      </c>
-      <c r="O24" s="3">
-        <v>1800</v>
       </c>
       <c r="P24" s="3">
         <v>1800</v>
       </c>
       <c r="Q24" s="3">
+        <v>1800</v>
+      </c>
+      <c r="R24" s="3">
         <v>1900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1500</v>
-      </c>
-      <c r="S24" s="3">
-        <v>1600</v>
       </c>
       <c r="T24" s="3">
         <v>1600</v>
@@ -2555,67 +2600,70 @@
         <v>1600</v>
       </c>
       <c r="V24" s="3">
+        <v>1600</v>
+      </c>
+      <c r="W24" s="3">
         <v>1400</v>
-      </c>
-      <c r="W24" s="3">
-        <v>1200</v>
       </c>
       <c r="X24" s="3">
         <v>1200</v>
       </c>
       <c r="Y24" s="3">
+        <v>1200</v>
+      </c>
+      <c r="Z24" s="3">
         <v>900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1000</v>
-      </c>
-      <c r="AA24" s="3">
-        <v>800</v>
       </c>
       <c r="AB24" s="3">
         <v>800</v>
       </c>
       <c r="AC24" s="3">
+        <v>800</v>
+      </c>
+      <c r="AD24" s="3">
         <v>500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>300</v>
-      </c>
-      <c r="AE24" s="3">
-        <v>500</v>
       </c>
       <c r="AF24" s="3">
         <v>500</v>
       </c>
       <c r="AG24" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AH24" s="3">
         <v>600</v>
       </c>
       <c r="AI24" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AJ24" s="3">
         <v>500</v>
       </c>
       <c r="AK24" s="3">
+        <v>500</v>
+      </c>
+      <c r="AL24" s="3">
         <v>700</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>600</v>
-      </c>
-      <c r="AM24" s="3">
-        <v>800</v>
       </c>
       <c r="AN24" s="3">
         <v>800</v>
       </c>
       <c r="AO24" s="3">
+        <v>800</v>
+      </c>
+      <c r="AP24" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2733,246 +2781,255 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E26" s="3">
         <v>800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-7100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>3000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>4100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>4600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>4000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>4500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>3900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>3700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>3800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>3900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>3300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>2900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>3000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>2200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>2400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>2000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1100</v>
-      </c>
-      <c r="AF26" s="3">
-        <v>1500</v>
       </c>
       <c r="AG26" s="3">
         <v>1500</v>
       </c>
       <c r="AH26" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AI26" s="3">
         <v>1700</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>800</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>1000</v>
-      </c>
-      <c r="AK26" s="3">
-        <v>900</v>
       </c>
       <c r="AL26" s="3">
         <v>900</v>
       </c>
       <c r="AM26" s="3">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="AN26" s="3">
         <v>1200</v>
       </c>
       <c r="AO26" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AP26" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E27" s="3">
         <v>800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>2400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>2500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-7100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>3000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>4100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>4600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>4000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>4500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>3900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>3700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>3800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>3900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>3300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>2900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>3000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>2200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>2400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>2000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1100</v>
-      </c>
-      <c r="AF27" s="3">
-        <v>1500</v>
       </c>
       <c r="AG27" s="3">
         <v>1500</v>
       </c>
       <c r="AH27" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AI27" s="3">
         <v>1700</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>800</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>1000</v>
-      </c>
-      <c r="AK27" s="3">
-        <v>900</v>
       </c>
       <c r="AL27" s="3">
         <v>900</v>
       </c>
       <c r="AM27" s="3">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="AN27" s="3">
         <v>1200</v>
       </c>
       <c r="AO27" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AP27" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3090,8 +3147,11 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3167,8 +3227,8 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-      <c r="AB29" s="3" t="s">
-        <v>5</v>
+      <c r="AB29" s="3">
+        <v>0</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>5</v>
@@ -3188,12 +3248,12 @@
       <c r="AH29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AI29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ29" s="3">
         <v>-300</v>
       </c>
-      <c r="AJ29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AK29" s="3" t="s">
         <v>5</v>
       </c>
@@ -3209,8 +3269,11 @@
       <c r="AO29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AP29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3328,8 +3391,11 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3447,8 +3513,11 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3485,71 +3554,71 @@
       <c r="N32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P32" s="3">
         <v>4300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>4400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>2900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>4400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>3700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>4200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>3500</v>
-      </c>
-      <c r="V32" s="3">
-        <v>4100</v>
       </c>
       <c r="W32" s="3">
         <v>4100</v>
       </c>
       <c r="X32" s="3">
+        <v>4100</v>
+      </c>
+      <c r="Y32" s="3">
         <v>3100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>3500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>2500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>3300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>2700</v>
-      </c>
-      <c r="AC32" s="3">
-        <v>3700</v>
       </c>
       <c r="AD32" s="3">
         <v>3700</v>
       </c>
       <c r="AE32" s="3">
+        <v>3700</v>
+      </c>
+      <c r="AF32" s="3">
         <v>3800</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>3500</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>3000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>2800</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>3400</v>
-      </c>
-      <c r="AJ32" s="3">
-        <v>2900</v>
       </c>
       <c r="AK32" s="3">
         <v>2900</v>
@@ -3558,135 +3627,141 @@
         <v>2900</v>
       </c>
       <c r="AM32" s="3">
+        <v>2900</v>
+      </c>
+      <c r="AN32" s="3">
         <v>2700</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>2500</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E33" s="3">
         <v>800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>2400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>2500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-7100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>3000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>4100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>4600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>4000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>4500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>3900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>3700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>3800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>3900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>3300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>2900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>3000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>2200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>2400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>2000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1100</v>
-      </c>
-      <c r="AF33" s="3">
-        <v>1500</v>
       </c>
       <c r="AG33" s="3">
         <v>1500</v>
       </c>
       <c r="AH33" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AI33" s="3">
         <v>1700</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>500</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>1000</v>
-      </c>
-      <c r="AK33" s="3">
-        <v>900</v>
       </c>
       <c r="AL33" s="3">
         <v>900</v>
       </c>
       <c r="AM33" s="3">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="AN33" s="3">
         <v>1200</v>
       </c>
       <c r="AO33" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AP33" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3804,251 +3879,260 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E35" s="3">
         <v>800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>2400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>2500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-7100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>3000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>4100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>4600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>4000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>4500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>3900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>3700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>3800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>3900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>3300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>2900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>3000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>2200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>2400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>2000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1100</v>
-      </c>
-      <c r="AF35" s="3">
-        <v>1500</v>
       </c>
       <c r="AG35" s="3">
         <v>1500</v>
       </c>
       <c r="AH35" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AI35" s="3">
         <v>1700</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>500</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>1000</v>
-      </c>
-      <c r="AK35" s="3">
-        <v>900</v>
       </c>
       <c r="AL35" s="3">
         <v>900</v>
       </c>
       <c r="AM35" s="3">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="AN35" s="3">
         <v>1200</v>
       </c>
       <c r="AO35" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AP35" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42916</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42825</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42643</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4090,8 +4174,9 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4133,127 +4218,131 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>65500</v>
+      </c>
+      <c r="E41" s="3">
         <v>58000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>66400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>72400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>51400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>80900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>40100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>37700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>57800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>86600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>112400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>116600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>77600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>42800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>36600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>65900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>40700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>37800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>56100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>46900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>30800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>24300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>68000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>36500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>38300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>37000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>12100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>18600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>21700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>20900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>23700</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>18900</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>68800</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>20400</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>20200</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>20800</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>24200</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>20100</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>21800</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4291,19 +4380,19 @@
         <v>0</v>
       </c>
       <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
         <v>13600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>13700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>13800</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>13500</v>
-      </c>
-      <c r="S42" s="3">
-        <v>4300</v>
       </c>
       <c r="T42" s="3">
         <v>4300</v>
@@ -4312,7 +4401,7 @@
         <v>4300</v>
       </c>
       <c r="V42" s="3">
-        <v>3400</v>
+        <v>4300</v>
       </c>
       <c r="W42" s="3">
         <v>3400</v>
@@ -4324,7 +4413,7 @@
         <v>3400</v>
       </c>
       <c r="Z42" s="3">
-        <v>3300</v>
+        <v>3400</v>
       </c>
       <c r="AA42" s="3">
         <v>3300</v>
@@ -4336,7 +4425,7 @@
         <v>3300</v>
       </c>
       <c r="AD42" s="3">
-        <v>3100</v>
+        <v>3300</v>
       </c>
       <c r="AE42" s="3">
         <v>3100</v>
@@ -4348,7 +4437,7 @@
         <v>3100</v>
       </c>
       <c r="AH42" s="3">
-        <v>5100</v>
+        <v>3100</v>
       </c>
       <c r="AI42" s="3">
         <v>5100</v>
@@ -4357,22 +4446,25 @@
         <v>5100</v>
       </c>
       <c r="AK42" s="3">
+        <v>5100</v>
+      </c>
+      <c r="AL42" s="3">
         <v>4800</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>5200</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>5300</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>4900</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -4409,8 +4501,8 @@
       <c r="N43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
+      <c r="O43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P43" s="3">
         <v>0</v>
@@ -4490,13 +4582,16 @@
       <c r="AO43" s="3">
         <v>0</v>
       </c>
+      <c r="AP43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>4400</v>
+        <v>2300</v>
       </c>
       <c r="E44" s="3">
         <v>4400</v>
@@ -4508,13 +4603,13 @@
         <v>4400</v>
       </c>
       <c r="H44" s="3">
-        <v>5100</v>
+        <v>4400</v>
       </c>
       <c r="I44" s="3">
         <v>5100</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>5</v>
+      <c r="J44" s="3">
+        <v>5100</v>
       </c>
       <c r="K44" s="3" t="s">
         <v>5</v>
@@ -4528,8 +4623,8 @@
       <c r="N44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -4609,47 +4704,50 @@
       <c r="AO44" s="3">
         <v>0</v>
       </c>
+      <c r="AP44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E45" s="3">
         <v>2800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3500</v>
-      </c>
-      <c r="H45" s="3">
-        <v>3600</v>
       </c>
       <c r="I45" s="3">
         <v>3600</v>
       </c>
       <c r="J45" s="3">
+        <v>3600</v>
+      </c>
+      <c r="K45" s="3">
         <v>3800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3700</v>
-      </c>
-      <c r="L45" s="3">
-        <v>3800</v>
       </c>
       <c r="M45" s="3">
         <v>3800</v>
       </c>
       <c r="N45" s="3">
+        <v>3800</v>
+      </c>
+      <c r="O45" s="3">
         <v>4100</v>
       </c>
-      <c r="O45" s="3">
-        <v>0</v>
-      </c>
       <c r="P45" s="3">
         <v>0</v>
       </c>
@@ -4728,47 +4826,50 @@
       <c r="AO45" s="3">
         <v>0</v>
       </c>
+      <c r="AP45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>71200</v>
+      </c>
+      <c r="E46" s="3">
         <v>65200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>77500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>80600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>59300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>89600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>48900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>41600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>61500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>90400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>116200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>120600</v>
       </c>
-      <c r="O46" s="3">
-        <v>0</v>
-      </c>
       <c r="P46" s="3">
         <v>0</v>
       </c>
@@ -4847,47 +4948,50 @@
       <c r="AO46" s="3">
         <v>0</v>
       </c>
+      <c r="AP46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>78700</v>
+      </c>
+      <c r="E47" s="3">
         <v>79300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>80200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>81800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>81500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>89800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>96900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>97500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>98500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>94200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>97700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>98400</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
       <c r="P47" s="3">
         <v>0</v>
       </c>
@@ -4966,79 +5070,82 @@
       <c r="AO47" s="3">
         <v>0</v>
       </c>
+      <c r="AP47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E48" s="3">
         <v>6500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>6000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>6200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>6400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>6200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>6600</v>
-      </c>
-      <c r="N48" s="3">
-        <v>6800</v>
       </c>
       <c r="O48" s="3">
         <v>6800</v>
       </c>
       <c r="P48" s="3">
+        <v>6800</v>
+      </c>
+      <c r="Q48" s="3">
         <v>7000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>6500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>6700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>6900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>7000</v>
-      </c>
-      <c r="U48" s="3">
-        <v>7200</v>
       </c>
       <c r="V48" s="3">
         <v>7200</v>
       </c>
       <c r="W48" s="3">
+        <v>7200</v>
+      </c>
+      <c r="X48" s="3">
         <v>7300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>7000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>6200</v>
-      </c>
-      <c r="Z48" s="3">
-        <v>6300</v>
       </c>
       <c r="AA48" s="3">
         <v>6300</v>
@@ -5050,43 +5157,46 @@
         <v>6300</v>
       </c>
       <c r="AD48" s="3">
+        <v>6300</v>
+      </c>
+      <c r="AE48" s="3">
         <v>6400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>5800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>5300</v>
-      </c>
-      <c r="AG48" s="3">
-        <v>5200</v>
       </c>
       <c r="AH48" s="3">
         <v>5200</v>
       </c>
       <c r="AI48" s="3">
-        <v>5300</v>
+        <v>5200</v>
       </c>
       <c r="AJ48" s="3">
         <v>5300</v>
       </c>
       <c r="AK48" s="3">
+        <v>5300</v>
+      </c>
+      <c r="AL48" s="3">
         <v>5400</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>5500</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>5400</v>
-      </c>
-      <c r="AN48" s="3">
-        <v>5500</v>
       </c>
       <c r="AO48" s="3">
         <v>5500</v>
       </c>
+      <c r="AP48" s="3">
+        <v>5500</v>
+      </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -5103,7 +5213,7 @@
         <v>0</v>
       </c>
       <c r="H49" s="3">
-        <v>4100</v>
+        <v>0</v>
       </c>
       <c r="I49" s="3">
         <v>4100</v>
@@ -5204,8 +5314,11 @@
       <c r="AO49" s="3">
         <v>4100</v>
       </c>
+      <c r="AP49" s="3">
+        <v>4100</v>
+      </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5323,8 +5436,11 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5442,47 +5558,50 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>11500</v>
+      </c>
+      <c r="E52" s="3">
         <v>17200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>17500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>17400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>11200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>11700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>12600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>13200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>10400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>14800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>12000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>9500</v>
       </c>
-      <c r="O52" s="3">
-        <v>0</v>
-      </c>
       <c r="P52" s="3">
         <v>0</v>
       </c>
@@ -5561,8 +5680,11 @@
       <c r="AO52" s="3">
         <v>0</v>
       </c>
+      <c r="AP52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5680,127 +5802,133 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1004600</v>
+      </c>
+      <c r="E54" s="3">
         <v>1006500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1032500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1063400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1067100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1118800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1082000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1080200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1122500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1142200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1161400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1147000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1115300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1043800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>980800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>982300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>958100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>922600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>901600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>886100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>865900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>833800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>850700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>721600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>696000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>680800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>635600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>626300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>622100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>595200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>586000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>577000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>610900</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>539000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>537500</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>524500</v>
-      </c>
-      <c r="AM54" s="3">
-        <v>513700</v>
       </c>
       <c r="AN54" s="3">
         <v>513700</v>
       </c>
       <c r="AO54" s="3">
+        <v>513700</v>
+      </c>
+      <c r="AP54" s="3">
         <v>518300</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5842,8 +5970,9 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5885,127 +6014,131 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>891100</v>
+      </c>
+      <c r="E57" s="3">
         <v>888800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>922600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>957100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>962600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1002800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>966600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>939200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1009700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1030800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1048300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1015700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>11100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>4500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>6600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>4400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>3200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>4200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>5600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>4300</v>
-      </c>
-      <c r="AA57" s="3">
-        <v>3300</v>
       </c>
       <c r="AB57" s="3">
         <v>3300</v>
       </c>
       <c r="AC57" s="3">
+        <v>3300</v>
+      </c>
+      <c r="AD57" s="3">
         <v>3500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>3000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>2200</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1600</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>2200</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>2700</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>2100</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>2000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>2300</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>1900</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>3200</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>8100</v>
       </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -6022,19 +6155,19 @@
         <v>400</v>
       </c>
       <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
         <v>400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>400</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="M58" s="3">
         <v>500</v>
@@ -6043,7 +6176,7 @@
         <v>500</v>
       </c>
       <c r="O58" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="P58" s="3">
         <v>0</v>
@@ -6123,8 +6256,11 @@
       <c r="AO58" s="3">
         <v>0</v>
       </c>
+      <c r="AP58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -6161,39 +6297,39 @@
       <c r="N59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O59" s="3">
+      <c r="O59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P59" s="3">
         <v>1400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1400</v>
-      </c>
-      <c r="V59" s="3">
-        <v>1300</v>
       </c>
       <c r="W59" s="3">
         <v>1300</v>
       </c>
       <c r="X59" s="3">
+        <v>1300</v>
+      </c>
+      <c r="Y59" s="3">
         <v>900</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z59" s="3" t="s">
         <v>5</v>
       </c>
@@ -6209,8 +6345,8 @@
       <c r="AD59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE59" s="3">
-        <v>0</v>
+      <c r="AE59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AF59" s="3">
         <v>0</v>
@@ -6242,47 +6378,50 @@
       <c r="AO59" s="3">
         <v>0</v>
       </c>
+      <c r="AP59" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>891800</v>
+      </c>
+      <c r="E60" s="3">
         <v>893600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>923400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>957900</v>
       </c>
-      <c r="G60" s="3">
-        <v>964700</v>
-      </c>
       <c r="H60" s="3">
+        <v>964200</v>
+      </c>
+      <c r="I60" s="3">
         <v>1004500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>973700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>940100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1010300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1032600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1049700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1016900</v>
       </c>
-      <c r="O60" s="3">
-        <v>0</v>
-      </c>
       <c r="P60" s="3">
         <v>0</v>
       </c>
@@ -6361,46 +6500,49 @@
       <c r="AO60" s="3">
         <v>0</v>
       </c>
+      <c r="AP60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E61" s="3">
         <v>12700</v>
-      </c>
-      <c r="E61" s="3">
-        <v>6700</v>
       </c>
       <c r="F61" s="3">
         <v>6700</v>
       </c>
       <c r="G61" s="3">
-        <v>6800</v>
+        <v>6700</v>
       </c>
       <c r="H61" s="3">
+        <v>7200</v>
+      </c>
+      <c r="I61" s="3">
         <v>6600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>6300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>35100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>6900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>6500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>6600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>29700</v>
-      </c>
-      <c r="O61" s="3">
-        <v>5900</v>
       </c>
       <c r="P61" s="3">
         <v>5900</v>
@@ -6445,7 +6587,7 @@
         <v>5900</v>
       </c>
       <c r="AD61" s="3">
-        <v>0</v>
+        <v>5900</v>
       </c>
       <c r="AE61" s="3">
         <v>0</v>
@@ -6480,47 +6622,50 @@
       <c r="AO61" s="3">
         <v>0</v>
       </c>
+      <c r="AP61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E62" s="3">
         <v>500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>4300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>3400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>3900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>7100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>4100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>7100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>7600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>9600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>10600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>7700</v>
       </c>
-      <c r="O62" s="3">
-        <v>0</v>
-      </c>
       <c r="P62" s="3">
         <v>0</v>
       </c>
@@ -6599,8 +6744,11 @@
       <c r="AO62" s="3">
         <v>0</v>
       </c>
+      <c r="AP62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6718,8 +6866,11 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6837,8 +6988,11 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6956,127 +7110,133 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>903400</v>
+      </c>
+      <c r="E66" s="3">
         <v>906800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>934400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>968000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>975400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1018100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>984100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>982300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1024800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1048700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1067000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1054400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1026800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>959400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>896100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>898600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>873800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>840600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>822700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>810600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>790200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>760400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>779400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>653400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>628600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>614300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>570900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>562900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>560600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>534700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>525800</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>517300</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>551200</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>478500</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>477000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>465200</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>455100</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>453400</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>458800</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7118,8 +7278,9 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7237,8 +7398,11 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7356,8 +7520,11 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7475,8 +7642,11 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7594,127 +7764,133 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>69700</v>
+      </c>
+      <c r="E72" s="3">
         <v>68600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>67800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>65400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>62900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>70000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>69700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>69500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>69000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>67900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>66800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>64700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>61400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>57600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>54500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>50800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>47600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>44800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>41700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>38500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>37500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>35300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>33100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>31600</v>
       </c>
-      <c r="AA72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB72" s="3">
+      <c r="AB72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC72" s="3">
         <v>28800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>27500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>27000</v>
       </c>
-      <c r="AE72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF72" s="3">
+      <c r="AF72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG72" s="3">
         <v>25900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>25200</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>24400</v>
       </c>
-      <c r="AI72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ72" s="3">
+      <c r="AJ72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK72" s="3">
         <v>23600</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>23300</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>23100</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>22800</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>22200</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>21600</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7832,8 +8008,11 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7951,8 +8130,11 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8070,127 +8252,133 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>101200</v>
+      </c>
+      <c r="E76" s="3">
         <v>99700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>98100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>95300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>91700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>100700</v>
-      </c>
-      <c r="I76" s="3">
-        <v>97900</v>
       </c>
       <c r="J76" s="3">
         <v>97900</v>
       </c>
       <c r="K76" s="3">
+        <v>97900</v>
+      </c>
+      <c r="L76" s="3">
         <v>97700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>93400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>94400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>92700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>88500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>84400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>84700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>83700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>84300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>82000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>79000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>75500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>75600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>73400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>71200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>68200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>67300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>66500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>64700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>63400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>61500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>60500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>60200</v>
-      </c>
-      <c r="AH76" s="3">
-        <v>59700</v>
       </c>
       <c r="AI76" s="3">
         <v>59700</v>
       </c>
       <c r="AJ76" s="3">
+        <v>59700</v>
+      </c>
+      <c r="AK76" s="3">
         <v>60500</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>60400</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>59300</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>58600</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>60300</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>59500</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8308,251 +8496,260 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42916</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42825</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42643</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E81" s="3">
         <v>800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>2400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>2500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-7100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>3000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>4100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>4600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>4000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>4500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>3900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>3700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>3800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>3900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>3300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>2900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>3000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>2200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>2400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>2000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1100</v>
-      </c>
-      <c r="AF81" s="3">
-        <v>1500</v>
       </c>
       <c r="AG81" s="3">
         <v>1500</v>
       </c>
       <c r="AH81" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AI81" s="3">
         <v>1700</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>500</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>1000</v>
-      </c>
-      <c r="AK81" s="3">
-        <v>900</v>
       </c>
       <c r="AL81" s="3">
         <v>900</v>
       </c>
       <c r="AM81" s="3">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="AN81" s="3">
         <v>1200</v>
       </c>
       <c r="AO81" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AP81" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8594,8 +8791,9 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8642,29 +8840,29 @@
         <v>100</v>
       </c>
       <c r="R83" s="3">
+        <v>100</v>
+      </c>
+      <c r="S83" s="3">
         <v>-300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>-300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>-200</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>600</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z83" s="3" t="s">
         <v>5</v>
       </c>
@@ -8677,8 +8875,8 @@
       <c r="AC83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AD83" s="3">
-        <v>0</v>
+      <c r="AD83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AE83" s="3">
         <v>0</v>
@@ -8704,17 +8902,20 @@
       <c r="AL83" s="3">
         <v>0</v>
       </c>
-      <c r="AM83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN83" s="3">
-        <v>100</v>
+      <c r="AM83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AO83" s="3">
         <v>100</v>
       </c>
+      <c r="AP83" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8832,8 +9033,11 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8951,8 +9155,11 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9070,8 +9277,11 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9189,8 +9399,11 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9308,77 +9521,80 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E89" s="3">
         <v>7200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-3200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-2400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>3700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-2800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>7500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-50300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>34000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-29500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>46600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>5400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-1400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>2000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1700</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z89" s="3" t="s">
         <v>5</v>
       </c>
@@ -9391,8 +9607,8 @@
       <c r="AC89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AD89" s="3">
-        <v>0</v>
+      <c r="AD89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AE89" s="3">
         <v>0</v>
@@ -9418,17 +9634,20 @@
       <c r="AL89" s="3">
         <v>0</v>
       </c>
-      <c r="AM89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN89" s="3">
+      <c r="AM89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO89" s="3">
         <v>1900</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9470,8 +9689,9 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -9491,7 +9711,7 @@
         <v>0</v>
       </c>
       <c r="I91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J91" s="3">
         <v>-100</v>
@@ -9500,13 +9720,13 @@
         <v>-100</v>
       </c>
       <c r="L91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
       </c>
       <c r="N91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="O91" s="3">
         <v>-100</v>
@@ -9518,29 +9738,29 @@
         <v>-100</v>
       </c>
       <c r="R91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="S91" s="3">
         <v>0</v>
       </c>
       <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
         <v>-100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-400</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z91" s="3" t="s">
         <v>5</v>
       </c>
@@ -9553,8 +9773,8 @@
       <c r="AC91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AD91" s="3">
-        <v>0</v>
+      <c r="AD91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AE91" s="3">
         <v>0</v>
@@ -9580,17 +9800,20 @@
       <c r="AL91" s="3">
         <v>0</v>
       </c>
-      <c r="AM91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN91" s="3">
-        <v>0</v>
+      <c r="AM91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AO91" s="3">
         <v>0</v>
       </c>
+      <c r="AP91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9708,8 +9931,11 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9827,77 +10053,80 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E94" s="3">
         <v>12700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>28500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>29700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>9000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>6000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>21900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-5900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-5200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-16700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>7600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-33000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-59300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-8000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>102600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-74000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-45500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>161400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-25200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-143500</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z94" s="3" t="s">
         <v>5</v>
       </c>
@@ -9910,8 +10139,8 @@
       <c r="AC94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AD94" s="3">
-        <v>0</v>
+      <c r="AD94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AE94" s="3">
         <v>0</v>
@@ -9937,17 +10166,20 @@
       <c r="AL94" s="3">
         <v>0</v>
       </c>
-      <c r="AM94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN94" s="3">
+      <c r="AM94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO94" s="3">
         <v>-2900</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>10700</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9989,8 +10221,9 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10003,14 +10236,14 @@
       <c r="F96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G96" s="3">
-        <v>0</v>
+      <c r="G96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H96" s="3">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3">
         <v>300</v>
-      </c>
-      <c r="I96" s="3">
-        <v>800</v>
       </c>
       <c r="J96" s="3">
         <v>800</v>
@@ -10028,7 +10261,7 @@
         <v>800</v>
       </c>
       <c r="O96" s="3">
-        <v>-800</v>
+        <v>800</v>
       </c>
       <c r="P96" s="3">
         <v>-800</v>
@@ -10037,29 +10270,29 @@
         <v>-800</v>
       </c>
       <c r="R96" s="3">
+        <v>-800</v>
+      </c>
+      <c r="S96" s="3">
         <v>2200</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-800</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-2200</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-700</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>2200</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-700</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-2200</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
       <c r="Z96" s="3">
         <v>0</v>
       </c>
@@ -10103,13 +10336,16 @@
         <v>0</v>
       </c>
       <c r="AN96" s="3">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="AO96" s="3">
         <v>-600</v>
       </c>
+      <c r="AP96" s="3">
+        <v>-600</v>
+      </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10227,8 +10463,11 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10346,8 +10585,11 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10465,77 +10707,80 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-28300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-34500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-5500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-40200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>32400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-42700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-22000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-18300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>8800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>34200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>60200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>63300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-2700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-57800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>30300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>47100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>10900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-137100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>29700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>127700</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z100" s="3" t="s">
         <v>5</v>
       </c>
@@ -10548,8 +10793,8 @@
       <c r="AC100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AD100" s="3">
-        <v>0</v>
+      <c r="AD100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AE100" s="3">
         <v>0</v>
@@ -10575,17 +10820,20 @@
       <c r="AL100" s="3">
         <v>0</v>
       </c>
-      <c r="AM100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN100" s="3">
+      <c r="AM100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO100" s="3">
         <v>-1100</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-10700</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10622,8 +10870,8 @@
       <c r="N101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -10703,77 +10951,80 @@
       <c r="AO101" s="3">
         <v>0</v>
       </c>
+      <c r="AP101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-8500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-6000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>21000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-29500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>40800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>2400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-20100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-28800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-25800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-4200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>39000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>34700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>6200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-29300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>15300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>2900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>6900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>9200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>23600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>6600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-14000</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z102" s="3" t="s">
         <v>5</v>
       </c>
@@ -10786,8 +11037,8 @@
       <c r="AC102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AD102" s="3">
-        <v>0</v>
+      <c r="AD102" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AE102" s="3">
         <v>0</v>
@@ -10813,13 +11064,16 @@
       <c r="AL102" s="3">
         <v>0</v>
       </c>
-      <c r="AM102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN102" s="3">
+      <c r="AM102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO102" s="3">
         <v>-2100</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>700</v>
       </c>
     </row>
